--- a/data/scall.xlsx
+++ b/data/scall.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Velasco\Desktop\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Velasco\Desktop\202606 - Reclima FAO - ADEPRO\2. Monitoreo\reclima-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7EA415-FE02-4919-AAC0-6D5CA126DF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB20534-554C-4BFD-8944-19A349E2C192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9600" windowHeight="10200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12414" uniqueCount="1824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12627" uniqueCount="1846">
   <si>
     <t>start</t>
   </si>
@@ -5516,6 +5516,72 @@
   <si>
     <t>ML-944-4</t>
   </si>
+  <si>
+    <t>uuid:bfb76aeb-7385-4b84-823e-349c0aadc402</t>
+  </si>
+  <si>
+    <t>bfb76aeb-7385-4b84-823e-349c0aadc402</t>
+  </si>
+  <si>
+    <t>NO TIENE CELULAR</t>
+  </si>
+  <si>
+    <t>Lavar alimentos Higiene Huerto Animales</t>
+  </si>
+  <si>
+    <t>MARIA VICTORINA MARIBEL DELGADO</t>
+  </si>
+  <si>
+    <t>13.7399346 -88.0214653 603.4953002929688 4.635</t>
+  </si>
+  <si>
+    <t>Blanca Argelia</t>
+  </si>
+  <si>
+    <t>uuid:c9f421f1-5465-4bab-92f1-fc12946636ce</t>
+  </si>
+  <si>
+    <t>c9f421f1-5465-4bab-92f1-fc12946636ce</t>
+  </si>
+  <si>
+    <t>78806554</t>
+  </si>
+  <si>
+    <t>Tanque Filtros</t>
+  </si>
+  <si>
+    <t>Higiene Huerto</t>
+  </si>
+  <si>
+    <t>MARIA PAULA MARQUEZ</t>
+  </si>
+  <si>
+    <t>LOS TORILES</t>
+  </si>
+  <si>
+    <t>MARIA PAULA MARQUEZ DIAZ</t>
+  </si>
+  <si>
+    <t>uuid:d9721d7a-9f63-43be-898d-94091f52c299</t>
+  </si>
+  <si>
+    <t>d9721d7a-9f63-43be-898d-94091f52c299</t>
+  </si>
+  <si>
+    <t>69964810</t>
+  </si>
+  <si>
+    <t>DINORA DEL CARMEN HERNANDEZ</t>
+  </si>
+  <si>
+    <t>13.4583198 -88.1122902 105.0999984741211 20.0</t>
+  </si>
+  <si>
+    <t>LAS PENITAS</t>
+  </si>
+  <si>
+    <t>PAPALON</t>
+  </si>
 </sst>
 </file>
 
@@ -5524,7 +5590,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5860,8 +5926,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:HN147"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:HN150"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.08984375" bestFit="1" customWidth="1"/>
@@ -5874,7 +5940,7 @@
     <col min="218" max="218" width="28.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:222">
       <c r="A1" t="s">
         <v>1783</v>
       </c>
@@ -6539,7 +6605,7 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="2" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:222">
       <c r="A2" t="str">
         <f>"V"&amp;B2&amp;"-R"&amp;HN2</f>
         <v>V1-R1</v>
@@ -7082,7 +7148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:222">
       <c r="A3" t="str">
         <f t="shared" ref="A3:A66" si="0">"V"&amp;B3&amp;"-R"&amp;HN3</f>
         <v>V1-R2</v>
@@ -7604,7 +7670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:222">
       <c r="A4" t="str">
         <f t="shared" si="0"/>
         <v>V1-R3</v>
@@ -8114,7 +8180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:222">
       <c r="A5" t="str">
         <f t="shared" si="0"/>
         <v>V1-R4</v>
@@ -8663,7 +8729,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:222">
       <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>V1-R5</v>
@@ -9215,7 +9281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:222">
       <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>V1-R6</v>
@@ -9707,7 +9773,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:222">
       <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>V1-R7</v>
@@ -10253,7 +10319,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:222">
       <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>V1-R8</v>
@@ -10799,7 +10865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:222">
       <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>V1-R9</v>
@@ -11072,7 +11138,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:222">
       <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>V1-R10</v>
@@ -11651,7 +11717,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:222">
       <c r="A12" t="str">
         <f t="shared" si="0"/>
         <v>V1-R11</v>
@@ -12155,7 +12221,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:222">
       <c r="A13" t="str">
         <f t="shared" si="0"/>
         <v>V1-R12</v>
@@ -12686,7 +12752,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:222">
       <c r="A14" t="str">
         <f t="shared" si="0"/>
         <v>V1-R13</v>
@@ -13238,7 +13304,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:222">
       <c r="A15" t="str">
         <f t="shared" si="0"/>
         <v>V1-R14</v>
@@ -13787,7 +13853,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:222">
       <c r="A16" t="str">
         <f t="shared" si="0"/>
         <v>V1-R15</v>
@@ -14333,7 +14399,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:222">
       <c r="A17" t="str">
         <f t="shared" si="0"/>
         <v>V1-R16</v>
@@ -14801,7 +14867,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:222">
       <c r="A18" t="str">
         <f t="shared" si="0"/>
         <v>V1-R17</v>
@@ -15179,7 +15245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:222">
       <c r="A19" t="str">
         <f t="shared" si="0"/>
         <v>V1-R18</v>
@@ -15689,7 +15755,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:222">
       <c r="A20" t="str">
         <f t="shared" si="0"/>
         <v>V1-R19</v>
@@ -16187,7 +16253,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:222">
       <c r="A21" t="str">
         <f t="shared" si="0"/>
         <v>V1-R20</v>
@@ -16379,7 +16445,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:222">
       <c r="A22" t="str">
         <f t="shared" si="0"/>
         <v>V1-R21</v>
@@ -16922,7 +16988,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:222">
       <c r="A23" t="str">
         <f t="shared" si="0"/>
         <v>V1-R22</v>
@@ -17390,7 +17456,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:222">
       <c r="A24" t="str">
         <f t="shared" si="0"/>
         <v>V1-R23</v>
@@ -17942,7 +18008,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:222">
       <c r="A25" t="str">
         <f t="shared" si="0"/>
         <v>V1-R24</v>
@@ -18428,7 +18494,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:222">
       <c r="A26" t="str">
         <f t="shared" si="0"/>
         <v>V1-R25</v>
@@ -18968,7 +19034,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:222">
       <c r="A27" t="str">
         <f t="shared" si="0"/>
         <v>V1-R26</v>
@@ -19523,7 +19589,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:222">
       <c r="A28" t="str">
         <f t="shared" si="0"/>
         <v>V1-R27</v>
@@ -20078,7 +20144,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:222">
       <c r="A29" t="str">
         <f t="shared" si="0"/>
         <v>V1-R28</v>
@@ -20615,7 +20681,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:222">
       <c r="A30" t="str">
         <f t="shared" si="0"/>
         <v>V1-R29</v>
@@ -21146,7 +21212,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:222">
       <c r="A31" t="str">
         <f t="shared" si="0"/>
         <v>V1-R30</v>
@@ -21656,7 +21722,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:222">
       <c r="A32" t="str">
         <f t="shared" si="0"/>
         <v>V1-R31</v>
@@ -22205,7 +22271,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:222">
       <c r="A33" t="str">
         <f t="shared" si="0"/>
         <v>V1-R32</v>
@@ -22697,7 +22763,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:222">
       <c r="A34" t="str">
         <f t="shared" si="0"/>
         <v>V1-R33</v>
@@ -23252,7 +23318,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:222">
       <c r="A35" t="str">
         <f t="shared" si="0"/>
         <v>V1-R34</v>
@@ -23807,7 +23873,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:222">
       <c r="A36" t="str">
         <f t="shared" si="0"/>
         <v>V1-R35</v>
@@ -24320,7 +24386,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:222">
       <c r="A37" t="str">
         <f t="shared" si="0"/>
         <v>V1-R36</v>
@@ -24809,7 +24875,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:222">
       <c r="A38" t="str">
         <f t="shared" si="0"/>
         <v>V1-R37</v>
@@ -25364,7 +25430,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:222">
       <c r="A39" t="str">
         <f t="shared" si="0"/>
         <v>V1-R38</v>
@@ -25919,7 +25985,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:222">
       <c r="A40" t="str">
         <f t="shared" si="0"/>
         <v>V1-R39</v>
@@ -26471,7 +26537,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:222">
       <c r="A41" t="str">
         <f t="shared" si="0"/>
         <v>V1-R40</v>
@@ -27026,7 +27092,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:222">
       <c r="A42" t="str">
         <f t="shared" si="0"/>
         <v>V1-R41</v>
@@ -27533,7 +27599,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:222">
       <c r="A43" t="str">
         <f t="shared" si="0"/>
         <v>V1-R42</v>
@@ -28064,7 +28130,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:222">
       <c r="A44" t="str">
         <f t="shared" si="0"/>
         <v>V1-R43</v>
@@ -28616,7 +28682,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:222">
       <c r="A45" t="str">
         <f t="shared" si="0"/>
         <v>V1-R44</v>
@@ -29123,7 +29189,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:222">
       <c r="A46" t="str">
         <f t="shared" si="0"/>
         <v>V1-R45</v>
@@ -29636,7 +29702,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:222">
       <c r="A47" t="str">
         <f t="shared" si="0"/>
         <v>V1-R46</v>
@@ -30182,7 +30248,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:222">
       <c r="A48" t="str">
         <f t="shared" si="0"/>
         <v>V1-R47</v>
@@ -30728,7 +30794,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:222">
       <c r="A49" t="str">
         <f t="shared" si="0"/>
         <v>V1-R48</v>
@@ -31274,7 +31340,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:222">
       <c r="A50" t="str">
         <f t="shared" si="0"/>
         <v>V1-R49</v>
@@ -31826,7 +31892,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:222">
       <c r="A51" t="str">
         <f t="shared" si="0"/>
         <v>V1-R50</v>
@@ -32294,7 +32360,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:222">
       <c r="A52" t="str">
         <f t="shared" si="0"/>
         <v>V1-R51</v>
@@ -32786,7 +32852,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:222">
       <c r="A53" t="str">
         <f t="shared" si="0"/>
         <v>V1-R52</v>
@@ -33275,7 +33341,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:222">
       <c r="A54" t="str">
         <f t="shared" si="0"/>
         <v>V1-R53</v>
@@ -33749,7 +33815,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:222">
       <c r="A55" t="str">
         <f t="shared" si="0"/>
         <v>V1-R54</v>
@@ -34301,7 +34367,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:222">
       <c r="A56" t="str">
         <f t="shared" si="0"/>
         <v>V1-R55</v>
@@ -34856,7 +34922,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:222">
       <c r="A57" t="str">
         <f t="shared" si="0"/>
         <v>V1-R56</v>
@@ -35360,7 +35426,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:222">
       <c r="A58" t="str">
         <f t="shared" si="0"/>
         <v>V1-R57</v>
@@ -35831,7 +35897,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:222">
       <c r="A59" t="str">
         <f t="shared" si="0"/>
         <v>V1-R58</v>
@@ -36344,7 +36410,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:222">
       <c r="A60" t="str">
         <f t="shared" si="0"/>
         <v>V1-R59</v>
@@ -36833,7 +36899,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:222">
       <c r="A61" t="str">
         <f t="shared" si="0"/>
         <v>V1-R60</v>
@@ -37346,7 +37412,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:222">
       <c r="A62" t="str">
         <f t="shared" si="0"/>
         <v>V1-R61</v>
@@ -37880,7 +37946,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:222">
       <c r="A63" t="str">
         <f t="shared" si="0"/>
         <v>V1-R62</v>
@@ -38411,7 +38477,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:222">
       <c r="A64" t="str">
         <f t="shared" si="0"/>
         <v>V1-R63</v>
@@ -38945,7 +39011,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:222">
       <c r="A65" t="str">
         <f t="shared" si="0"/>
         <v>V1-R64</v>
@@ -39497,7 +39563,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:222">
       <c r="A66" t="str">
         <f t="shared" si="0"/>
         <v>V1-R65</v>
@@ -39761,7 +39827,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:222">
       <c r="A67" t="str">
         <f t="shared" ref="A67:A130" si="1">"V"&amp;B67&amp;"-R"&amp;HN67</f>
         <v>V1-R66</v>
@@ -40313,7 +40379,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:222">
       <c r="A68" t="str">
         <f t="shared" si="1"/>
         <v>V1-R67</v>
@@ -40799,7 +40865,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:222">
       <c r="A69" t="str">
         <f t="shared" si="1"/>
         <v>V1-R68</v>
@@ -41336,7 +41402,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:222">
       <c r="A70" t="str">
         <f t="shared" si="1"/>
         <v>V1-R69</v>
@@ -41834,7 +41900,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:222">
       <c r="A71" t="str">
         <f t="shared" si="1"/>
         <v>V1-R70</v>
@@ -42347,7 +42413,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:222">
       <c r="A72" t="str">
         <f t="shared" si="1"/>
         <v>V1-R71</v>
@@ -42902,7 +42968,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:222">
       <c r="A73" t="str">
         <f t="shared" si="1"/>
         <v>V1-R72</v>
@@ -43457,7 +43523,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:222">
       <c r="A74" t="str">
         <f t="shared" si="1"/>
         <v>V1-R73</v>
@@ -44015,7 +44081,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:222">
       <c r="A75" t="str">
         <f t="shared" si="1"/>
         <v>V1-R74</v>
@@ -44567,7 +44633,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:222">
       <c r="A76" t="str">
         <f t="shared" si="1"/>
         <v>V1-R75</v>
@@ -45122,7 +45188,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:222">
       <c r="A77" t="str">
         <f t="shared" si="1"/>
         <v>V1-R76</v>
@@ -45680,7 +45746,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:222">
       <c r="A78" t="str">
         <f t="shared" si="1"/>
         <v>V1-R77</v>
@@ -46175,7 +46241,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:222">
       <c r="A79" t="str">
         <f t="shared" si="1"/>
         <v>V1-R78</v>
@@ -46730,7 +46796,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:222">
       <c r="A80" t="str">
         <f t="shared" si="1"/>
         <v>V1-R79</v>
@@ -47243,7 +47309,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:222">
       <c r="A81" t="str">
         <f t="shared" si="1"/>
         <v>V1-R80</v>
@@ -47774,7 +47840,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:222">
       <c r="A82" t="str">
         <f t="shared" si="1"/>
         <v>V1-R81</v>
@@ -48326,7 +48392,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:222">
       <c r="A83" t="str">
         <f t="shared" si="1"/>
         <v>V1-R82</v>
@@ -48878,7 +48944,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:222">
       <c r="A84" t="str">
         <f t="shared" si="1"/>
         <v>V1-R83</v>
@@ -49415,7 +49481,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:222">
       <c r="A85" t="str">
         <f t="shared" si="1"/>
         <v>V1-R84</v>
@@ -49970,7 +50036,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:222">
       <c r="A86" t="str">
         <f t="shared" si="1"/>
         <v>V1-R85</v>
@@ -50504,7 +50570,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:222">
       <c r="A87" t="str">
         <f t="shared" si="1"/>
         <v>V1-R86</v>
@@ -51032,7 +51098,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:222">
       <c r="A88" t="str">
         <f t="shared" si="1"/>
         <v>V1-R87</v>
@@ -51566,7 +51632,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:222">
       <c r="A89" t="str">
         <f t="shared" si="1"/>
         <v>V1-R88</v>
@@ -52100,7 +52166,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:222">
       <c r="A90" t="str">
         <f t="shared" si="1"/>
         <v>V1-R89</v>
@@ -52613,7 +52679,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:222">
       <c r="A91" t="str">
         <f t="shared" si="1"/>
         <v>V1-R90</v>
@@ -53102,7 +53168,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:222">
       <c r="A92" t="str">
         <f t="shared" si="1"/>
         <v>V1-R91</v>
@@ -53615,7 +53681,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:222">
       <c r="A93" t="str">
         <f t="shared" si="1"/>
         <v>V1-R92</v>
@@ -54146,7 +54212,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:222">
       <c r="A94" t="str">
         <f t="shared" si="1"/>
         <v>V1-R93</v>
@@ -54656,7 +54722,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:222">
       <c r="A95" t="str">
         <f t="shared" si="1"/>
         <v>V1-R94</v>
@@ -55211,7 +55277,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:222">
       <c r="A96" t="str">
         <f t="shared" si="1"/>
         <v>V1-R95</v>
@@ -55766,7 +55832,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:222">
       <c r="A97" t="str">
         <f t="shared" si="1"/>
         <v>V1-R96</v>
@@ -56324,7 +56390,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:222">
       <c r="A98" t="str">
         <f t="shared" si="1"/>
         <v>V1-R97</v>
@@ -56855,7 +56921,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:222">
       <c r="A99" t="str">
         <f t="shared" si="1"/>
         <v>V1-R98</v>
@@ -57422,7 +57488,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:222">
       <c r="A100" t="str">
         <f t="shared" si="1"/>
         <v>V1-R99</v>
@@ -57656,7 +57722,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:222">
       <c r="A101" t="str">
         <f t="shared" si="1"/>
         <v>V1-R100</v>
@@ -58208,7 +58274,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:222">
       <c r="A102" t="str">
         <f t="shared" si="1"/>
         <v>V2-R1</v>
@@ -58328,7 +58394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:222">
       <c r="A103" t="str">
         <f t="shared" si="1"/>
         <v>V2-R2</v>
@@ -58898,7 +58964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:222">
       <c r="A104" t="str">
         <f t="shared" si="1"/>
         <v>V2-R3</v>
@@ -59018,7 +59084,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:222">
       <c r="A105" t="str">
         <f t="shared" si="1"/>
         <v>V2-R4</v>
@@ -59609,7 +59675,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:222">
       <c r="A106" t="str">
         <f t="shared" si="1"/>
         <v>V2-R5</v>
@@ -60203,7 +60269,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:222">
       <c r="A107" t="str">
         <f t="shared" si="1"/>
         <v>V2-R6</v>
@@ -60797,7 +60863,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:222">
       <c r="A108" t="str">
         <f t="shared" si="1"/>
         <v>V2-R7</v>
@@ -61376,7 +61442,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:222">
       <c r="A109" t="str">
         <f t="shared" si="1"/>
         <v>V2-R8</v>
@@ -61970,7 +62036,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:222">
       <c r="A110" t="str">
         <f t="shared" si="1"/>
         <v>V2-R9</v>
@@ -62540,7 +62606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:222">
       <c r="A111" t="str">
         <f t="shared" si="1"/>
         <v>V2-R10</v>
@@ -63113,7 +63179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:222">
       <c r="A112" t="str">
         <f t="shared" si="1"/>
         <v>V2-R11</v>
@@ -63644,7 +63710,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="113" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:222">
       <c r="A113" t="str">
         <f t="shared" si="1"/>
         <v>V2-R12</v>
@@ -64091,7 +64157,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:222">
       <c r="A114" t="str">
         <f t="shared" si="1"/>
         <v>V2-R13</v>
@@ -64673,7 +64739,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="115" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:222">
       <c r="A115" t="str">
         <f t="shared" si="1"/>
         <v>V2-R14</v>
@@ -65249,7 +65315,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="116" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:222">
       <c r="A116" t="str">
         <f t="shared" si="1"/>
         <v>V2-R15</v>
@@ -65831,7 +65897,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="117" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:222">
       <c r="A117" t="str">
         <f t="shared" si="1"/>
         <v>V2-R16</v>
@@ -66392,7 +66458,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="118" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:222">
       <c r="A118" t="str">
         <f t="shared" si="1"/>
         <v>V2-R17</v>
@@ -66698,7 +66764,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="119" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:222">
       <c r="A119" t="str">
         <f t="shared" si="1"/>
         <v>V2-R18</v>
@@ -67292,7 +67358,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:222">
       <c r="A120" t="str">
         <f t="shared" si="1"/>
         <v>V2-R19</v>
@@ -67865,7 +67931,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="121" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:222">
       <c r="A121" t="str">
         <f t="shared" si="1"/>
         <v>V2-R20</v>
@@ -68414,7 +68480,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="122" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:222">
       <c r="A122" t="str">
         <f t="shared" si="1"/>
         <v>V2-R21</v>
@@ -69011,7 +69077,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="123" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:222">
       <c r="A123" t="str">
         <f t="shared" si="1"/>
         <v>V2-R22</v>
@@ -69608,7 +69674,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="124" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:222">
       <c r="A124" t="str">
         <f t="shared" si="1"/>
         <v>V2-R23</v>
@@ -70166,7 +70232,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="125" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:222">
       <c r="A125" t="str">
         <f t="shared" si="1"/>
         <v>V2-R24</v>
@@ -70751,7 +70817,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="126" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:222">
       <c r="A126" t="str">
         <f t="shared" si="1"/>
         <v>V2-R25</v>
@@ -71330,7 +71396,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:222">
       <c r="A127" t="str">
         <f t="shared" si="1"/>
         <v>V2-R26</v>
@@ -71876,7 +71942,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="128" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:222">
       <c r="A128" t="str">
         <f t="shared" si="1"/>
         <v>V2-R27</v>
@@ -72473,7 +72539,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="129" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:222">
       <c r="A129" t="str">
         <f t="shared" si="1"/>
         <v>V2-R28</v>
@@ -73070,7 +73136,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:222">
       <c r="A130" t="str">
         <f t="shared" si="1"/>
         <v>V2-R29</v>
@@ -73667,7 +73733,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="131" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:222">
       <c r="A131" t="str">
         <f t="shared" ref="A131:A147" si="2">"V"&amp;B131&amp;"-R"&amp;HN131</f>
         <v>V2-R30</v>
@@ -74201,7 +74267,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="132" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:222">
       <c r="A132" t="str">
         <f t="shared" si="2"/>
         <v>V2-R31</v>
@@ -74777,7 +74843,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="133" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:222">
       <c r="A133" t="str">
         <f t="shared" si="2"/>
         <v>V2-R32</v>
@@ -75320,7 +75386,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="134" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:222">
       <c r="A134" t="str">
         <f t="shared" si="2"/>
         <v>V2-R33</v>
@@ -75899,7 +75965,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="135" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:222">
       <c r="A135" t="str">
         <f t="shared" si="2"/>
         <v>V2-R34</v>
@@ -76460,7 +76526,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="136" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:222">
       <c r="A136" t="str">
         <f t="shared" si="2"/>
         <v>V2-R35</v>
@@ -77048,7 +77114,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="137" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:222">
       <c r="A137" t="str">
         <f t="shared" si="2"/>
         <v>V2-R36</v>
@@ -77624,7 +77690,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="138" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:222">
       <c r="A138" t="str">
         <f t="shared" si="2"/>
         <v>V2-R37</v>
@@ -78197,7 +78263,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="139" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:222">
       <c r="A139" t="str">
         <f t="shared" si="2"/>
         <v>V2-R38</v>
@@ -78770,7 +78836,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="140" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:222">
       <c r="A140" t="str">
         <f t="shared" si="2"/>
         <v>V2-R39</v>
@@ -79301,7 +79367,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="141" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:222">
       <c r="A141" t="str">
         <f t="shared" si="2"/>
         <v>V2-R40</v>
@@ -79853,7 +79919,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="142" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:222">
       <c r="A142" t="str">
         <f t="shared" si="2"/>
         <v>V2-R41</v>
@@ -79973,7 +80039,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="143" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:222">
       <c r="A143" t="str">
         <f t="shared" si="2"/>
         <v>V2-R42</v>
@@ -80564,7 +80630,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="144" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:222">
       <c r="A144" t="str">
         <f t="shared" si="2"/>
         <v>V2-R43</v>
@@ -81149,7 +81215,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="145" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:222">
       <c r="A145" t="str">
         <f t="shared" si="2"/>
         <v>V2-R44</v>
@@ -81728,7 +81794,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="146" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:222">
       <c r="A146" t="str">
         <f t="shared" si="2"/>
         <v>V2-R45</v>
@@ -82310,7 +82376,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="147" spans="1:222" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:222">
       <c r="A147" t="str">
         <f t="shared" si="2"/>
         <v>V2-R46</v>
@@ -82902,6 +82968,1308 @@
       </c>
       <c r="HN147">
         <v>46</v>
+      </c>
+    </row>
+    <row r="148" spans="1:222">
+      <c r="A148" t="str">
+        <f t="shared" ref="A148:A150" si="3">"V"&amp;B148&amp;"-R"&amp;HN148</f>
+        <v>V2-R47</v>
+      </c>
+      <c r="B148">
+        <v>2</v>
+      </c>
+      <c r="C148" s="1">
+        <v>46218.745523495367</v>
+      </c>
+      <c r="D148" s="1">
+        <v>46224.424864108798</v>
+      </c>
+      <c r="E148" s="1">
+        <v>46218</v>
+      </c>
+      <c r="G148" t="s">
+        <v>1830</v>
+      </c>
+      <c r="H148" t="s">
+        <v>452</v>
+      </c>
+      <c r="I148" s="1">
+        <v>46218</v>
+      </c>
+      <c r="K148" t="s">
+        <v>1842</v>
+      </c>
+      <c r="L148">
+        <v>47</v>
+      </c>
+      <c r="M148" t="s">
+        <v>271</v>
+      </c>
+      <c r="O148" t="s">
+        <v>816</v>
+      </c>
+      <c r="P148" t="s">
+        <v>1700</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>816</v>
+      </c>
+      <c r="R148" t="s">
+        <v>1845</v>
+      </c>
+      <c r="S148" t="s">
+        <v>1844</v>
+      </c>
+      <c r="U148" t="s">
+        <v>1843</v>
+      </c>
+      <c r="V148">
+        <v>13.4583198</v>
+      </c>
+      <c r="W148">
+        <v>-88.112290200000004</v>
+      </c>
+      <c r="X148">
+        <v>105.09999847412109</v>
+      </c>
+      <c r="Y148">
+        <v>20</v>
+      </c>
+      <c r="AA148" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AB148" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD148" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG148" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ148" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK148" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL148" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN148" t="s">
+        <v>1842</v>
+      </c>
+      <c r="AO148" t="s">
+        <v>271</v>
+      </c>
+      <c r="AP148">
+        <v>47</v>
+      </c>
+      <c r="AQ148" t="s">
+        <v>429</v>
+      </c>
+      <c r="AR148" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU148">
+        <v>2</v>
+      </c>
+      <c r="AV148">
+        <v>1</v>
+      </c>
+      <c r="AW148" t="s">
+        <v>1317</v>
+      </c>
+      <c r="AX148">
+        <v>1</v>
+      </c>
+      <c r="AY148">
+        <v>0</v>
+      </c>
+      <c r="AZ148">
+        <v>2</v>
+      </c>
+      <c r="BA148" t="s">
+        <v>1318</v>
+      </c>
+      <c r="BB148" t="s">
+        <v>306</v>
+      </c>
+      <c r="BD148" t="s">
+        <v>404</v>
+      </c>
+      <c r="BE148" t="s">
+        <v>279</v>
+      </c>
+      <c r="BF148" t="s">
+        <v>789</v>
+      </c>
+      <c r="BG148" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH148" t="s">
+        <v>232</v>
+      </c>
+      <c r="BI148" t="s">
+        <v>233</v>
+      </c>
+      <c r="BJ148" t="s">
+        <v>234</v>
+      </c>
+      <c r="FT148" t="s">
+        <v>226</v>
+      </c>
+      <c r="FU148">
+        <v>1</v>
+      </c>
+      <c r="FV148" t="s">
+        <v>261</v>
+      </c>
+      <c r="FW148">
+        <v>1</v>
+      </c>
+      <c r="FX148">
+        <v>0</v>
+      </c>
+      <c r="FY148">
+        <v>0</v>
+      </c>
+      <c r="FZ148">
+        <v>0</v>
+      </c>
+      <c r="GB148">
+        <v>1</v>
+      </c>
+      <c r="GC148" t="s">
+        <v>262</v>
+      </c>
+      <c r="GD148">
+        <v>1</v>
+      </c>
+      <c r="GE148">
+        <v>0</v>
+      </c>
+      <c r="GF148">
+        <v>0</v>
+      </c>
+      <c r="GG148">
+        <v>0</v>
+      </c>
+      <c r="GJ148" t="s">
+        <v>226</v>
+      </c>
+      <c r="GK148" t="s">
+        <v>263</v>
+      </c>
+      <c r="GL148" t="s">
+        <v>263</v>
+      </c>
+      <c r="GM148" t="s">
+        <v>226</v>
+      </c>
+      <c r="GN148" t="s">
+        <v>226</v>
+      </c>
+      <c r="GO148" t="s">
+        <v>263</v>
+      </c>
+      <c r="GP148" t="s">
+        <v>263</v>
+      </c>
+      <c r="GQ148" t="s">
+        <v>226</v>
+      </c>
+      <c r="GR148" t="s">
+        <v>263</v>
+      </c>
+      <c r="GZ148" t="s">
+        <v>1841</v>
+      </c>
+      <c r="HD148">
+        <v>22557740</v>
+      </c>
+      <c r="HE148" t="s">
+        <v>1840</v>
+      </c>
+      <c r="HF148" s="1">
+        <v>46224.675509259258</v>
+      </c>
+      <c r="HI148" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ148" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK148" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM148" t="s">
+        <v>1839</v>
+      </c>
+      <c r="HN148">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="149" spans="1:222">
+      <c r="A149" t="str">
+        <f t="shared" si="3"/>
+        <v>V2-R48</v>
+      </c>
+      <c r="B149">
+        <v>2</v>
+      </c>
+      <c r="C149" s="1">
+        <v>46220.591535474538</v>
+      </c>
+      <c r="D149" s="1">
+        <v>46224.425246932871</v>
+      </c>
+      <c r="E149" s="1">
+        <v>46220</v>
+      </c>
+      <c r="G149" t="s">
+        <v>1830</v>
+      </c>
+      <c r="H149" t="s">
+        <v>452</v>
+      </c>
+      <c r="I149" s="1">
+        <v>46220</v>
+      </c>
+      <c r="K149" t="s">
+        <v>1838</v>
+      </c>
+      <c r="L149">
+        <v>77</v>
+      </c>
+      <c r="M149" t="s">
+        <v>271</v>
+      </c>
+      <c r="O149" t="s">
+        <v>348</v>
+      </c>
+      <c r="P149" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>685</v>
+      </c>
+      <c r="R149" t="s">
+        <v>686</v>
+      </c>
+      <c r="S149" t="s">
+        <v>1837</v>
+      </c>
+      <c r="AA149" t="s">
+        <v>1836</v>
+      </c>
+      <c r="AB149" t="s">
+        <v>226</v>
+      </c>
+      <c r="AG149" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ149" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK149" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL149" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN149" t="s">
+        <v>1836</v>
+      </c>
+      <c r="AO149" t="s">
+        <v>271</v>
+      </c>
+      <c r="AP149">
+        <v>77</v>
+      </c>
+      <c r="AQ149" t="s">
+        <v>255</v>
+      </c>
+      <c r="AR149" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU149">
+        <v>2</v>
+      </c>
+      <c r="AV149">
+        <v>2</v>
+      </c>
+      <c r="AW149" t="s">
+        <v>1088</v>
+      </c>
+      <c r="AX149">
+        <v>0</v>
+      </c>
+      <c r="AY149">
+        <v>0</v>
+      </c>
+      <c r="BA149" t="s">
+        <v>1404</v>
+      </c>
+      <c r="BB149" t="s">
+        <v>306</v>
+      </c>
+      <c r="BD149" t="s">
+        <v>228</v>
+      </c>
+      <c r="BE149" t="s">
+        <v>279</v>
+      </c>
+      <c r="BF149" t="s">
+        <v>230</v>
+      </c>
+      <c r="BG149" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH149" t="s">
+        <v>282</v>
+      </c>
+      <c r="BI149" t="s">
+        <v>233</v>
+      </c>
+      <c r="BJ149" t="s">
+        <v>234</v>
+      </c>
+      <c r="BK149" t="s">
+        <v>263</v>
+      </c>
+      <c r="BM149" t="s">
+        <v>235</v>
+      </c>
+      <c r="BO149" t="s">
+        <v>332</v>
+      </c>
+      <c r="BP149" t="s">
+        <v>235</v>
+      </c>
+      <c r="BR149" t="s">
+        <v>236</v>
+      </c>
+      <c r="BS149" t="s">
+        <v>226</v>
+      </c>
+      <c r="BT149">
+        <v>30</v>
+      </c>
+      <c r="BU149" t="s">
+        <v>643</v>
+      </c>
+      <c r="BV149" t="s">
+        <v>238</v>
+      </c>
+      <c r="BX149">
+        <v>30</v>
+      </c>
+      <c r="BY149" t="s">
+        <v>239</v>
+      </c>
+      <c r="CA149">
+        <v>9999</v>
+      </c>
+      <c r="CB149">
+        <v>99</v>
+      </c>
+      <c r="CC149" t="s">
+        <v>1835</v>
+      </c>
+      <c r="CD149">
+        <v>0</v>
+      </c>
+      <c r="CE149">
+        <v>0</v>
+      </c>
+      <c r="CF149">
+        <v>0</v>
+      </c>
+      <c r="CG149">
+        <v>1</v>
+      </c>
+      <c r="CH149">
+        <v>0</v>
+      </c>
+      <c r="CI149">
+        <v>1</v>
+      </c>
+      <c r="CJ149">
+        <v>0</v>
+      </c>
+      <c r="CK149">
+        <v>1</v>
+      </c>
+      <c r="CL149">
+        <v>0</v>
+      </c>
+      <c r="CM149">
+        <v>9999</v>
+      </c>
+      <c r="CN149" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO149" t="s">
+        <v>242</v>
+      </c>
+      <c r="CP149">
+        <v>0</v>
+      </c>
+      <c r="CQ149">
+        <v>0</v>
+      </c>
+      <c r="CR149">
+        <v>0</v>
+      </c>
+      <c r="CS149">
+        <v>0</v>
+      </c>
+      <c r="CT149">
+        <v>0</v>
+      </c>
+      <c r="CU149">
+        <v>0</v>
+      </c>
+      <c r="CV149">
+        <v>1</v>
+      </c>
+      <c r="CX149" t="s">
+        <v>226</v>
+      </c>
+      <c r="CY149" t="s">
+        <v>1012</v>
+      </c>
+      <c r="CZ149">
+        <v>1</v>
+      </c>
+      <c r="DA149">
+        <v>1</v>
+      </c>
+      <c r="DB149">
+        <v>0</v>
+      </c>
+      <c r="DC149">
+        <v>0</v>
+      </c>
+      <c r="DD149" t="s">
+        <v>336</v>
+      </c>
+      <c r="DE149">
+        <v>1</v>
+      </c>
+      <c r="DF149">
+        <v>0</v>
+      </c>
+      <c r="DG149">
+        <v>0</v>
+      </c>
+      <c r="DH149">
+        <v>0</v>
+      </c>
+      <c r="DI149">
+        <v>0</v>
+      </c>
+      <c r="DJ149">
+        <v>0</v>
+      </c>
+      <c r="DK149" t="s">
+        <v>391</v>
+      </c>
+      <c r="DL149" t="s">
+        <v>361</v>
+      </c>
+      <c r="DM149">
+        <v>0</v>
+      </c>
+      <c r="DN149" t="s">
+        <v>316</v>
+      </c>
+      <c r="DO149" t="s">
+        <v>248</v>
+      </c>
+      <c r="DP149">
+        <v>1</v>
+      </c>
+      <c r="DQ149">
+        <v>1</v>
+      </c>
+      <c r="DR149">
+        <v>1</v>
+      </c>
+      <c r="DS149">
+        <v>1</v>
+      </c>
+      <c r="DT149">
+        <v>1</v>
+      </c>
+      <c r="DU149">
+        <v>1</v>
+      </c>
+      <c r="DV149">
+        <v>1</v>
+      </c>
+      <c r="DW149">
+        <v>1</v>
+      </c>
+      <c r="DX149">
+        <v>1</v>
+      </c>
+      <c r="DY149">
+        <v>1</v>
+      </c>
+      <c r="DZ149">
+        <v>1</v>
+      </c>
+      <c r="EA149">
+        <v>1</v>
+      </c>
+      <c r="EB149" t="s">
+        <v>245</v>
+      </c>
+      <c r="EC149" t="s">
+        <v>249</v>
+      </c>
+      <c r="ED149" t="s">
+        <v>253</v>
+      </c>
+      <c r="EE149" t="s">
+        <v>363</v>
+      </c>
+      <c r="EF149">
+        <v>1</v>
+      </c>
+      <c r="EG149">
+        <v>0</v>
+      </c>
+      <c r="EH149">
+        <v>0</v>
+      </c>
+      <c r="EI149">
+        <v>0</v>
+      </c>
+      <c r="EJ149">
+        <v>0</v>
+      </c>
+      <c r="EK149">
+        <v>0</v>
+      </c>
+      <c r="EL149" t="s">
+        <v>778</v>
+      </c>
+      <c r="EM149">
+        <v>0</v>
+      </c>
+      <c r="EN149">
+        <v>1</v>
+      </c>
+      <c r="EO149">
+        <v>0</v>
+      </c>
+      <c r="EP149">
+        <v>0</v>
+      </c>
+      <c r="EQ149" t="s">
+        <v>253</v>
+      </c>
+      <c r="ER149" t="s">
+        <v>338</v>
+      </c>
+      <c r="ES149" t="s">
+        <v>255</v>
+      </c>
+      <c r="ET149">
+        <v>0</v>
+      </c>
+      <c r="EU149">
+        <v>0</v>
+      </c>
+      <c r="EV149">
+        <v>0</v>
+      </c>
+      <c r="EW149">
+        <v>0</v>
+      </c>
+      <c r="EX149">
+        <v>1</v>
+      </c>
+      <c r="EY149" t="s">
+        <v>339</v>
+      </c>
+      <c r="EZ149" t="s">
+        <v>257</v>
+      </c>
+      <c r="FA149" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB149" t="s">
+        <v>411</v>
+      </c>
+      <c r="FC149" t="s">
+        <v>259</v>
+      </c>
+      <c r="FD149">
+        <v>1</v>
+      </c>
+      <c r="FE149">
+        <v>0</v>
+      </c>
+      <c r="FF149">
+        <v>0</v>
+      </c>
+      <c r="FG149">
+        <v>0</v>
+      </c>
+      <c r="FH149">
+        <v>0</v>
+      </c>
+      <c r="FI149">
+        <v>0</v>
+      </c>
+      <c r="FJ149" t="s">
+        <v>226</v>
+      </c>
+      <c r="FK149" t="s">
+        <v>226</v>
+      </c>
+      <c r="FM149" t="s">
+        <v>1834</v>
+      </c>
+      <c r="FN149">
+        <v>0</v>
+      </c>
+      <c r="FO149">
+        <v>0</v>
+      </c>
+      <c r="FP149">
+        <v>1</v>
+      </c>
+      <c r="FQ149">
+        <v>0</v>
+      </c>
+      <c r="FR149">
+        <v>1</v>
+      </c>
+      <c r="FS149">
+        <v>0</v>
+      </c>
+      <c r="FT149" t="s">
+        <v>263</v>
+      </c>
+      <c r="GJ149" t="s">
+        <v>226</v>
+      </c>
+      <c r="GK149" t="s">
+        <v>263</v>
+      </c>
+      <c r="GL149" t="s">
+        <v>263</v>
+      </c>
+      <c r="GM149" t="s">
+        <v>263</v>
+      </c>
+      <c r="GN149" t="s">
+        <v>263</v>
+      </c>
+      <c r="GO149" t="s">
+        <v>263</v>
+      </c>
+      <c r="GP149" t="s">
+        <v>263</v>
+      </c>
+      <c r="GQ149" t="s">
+        <v>263</v>
+      </c>
+      <c r="GR149" t="s">
+        <v>263</v>
+      </c>
+      <c r="GZ149" t="s">
+        <v>1833</v>
+      </c>
+      <c r="HD149">
+        <v>22557741</v>
+      </c>
+      <c r="HE149" t="s">
+        <v>1832</v>
+      </c>
+      <c r="HF149" s="1">
+        <v>46224.675520833327</v>
+      </c>
+      <c r="HI149" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ149" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK149" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM149" t="s">
+        <v>1831</v>
+      </c>
+      <c r="HN149">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="150" spans="1:222">
+      <c r="A150" t="str">
+        <f t="shared" si="3"/>
+        <v>V2-R49</v>
+      </c>
+      <c r="B150">
+        <v>2</v>
+      </c>
+      <c r="C150" s="1">
+        <v>46221.695161331023</v>
+      </c>
+      <c r="D150" s="1">
+        <v>46224.425408078707</v>
+      </c>
+      <c r="E150" s="1">
+        <v>46221</v>
+      </c>
+      <c r="G150" t="s">
+        <v>1830</v>
+      </c>
+      <c r="H150" t="s">
+        <v>452</v>
+      </c>
+      <c r="I150" s="1">
+        <v>46221</v>
+      </c>
+      <c r="K150" t="s">
+        <v>1828</v>
+      </c>
+      <c r="L150">
+        <v>60</v>
+      </c>
+      <c r="M150" t="s">
+        <v>271</v>
+      </c>
+      <c r="O150" t="s">
+        <v>348</v>
+      </c>
+      <c r="P150" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>455</v>
+      </c>
+      <c r="R150" t="s">
+        <v>1750</v>
+      </c>
+      <c r="S150" t="s">
+        <v>672</v>
+      </c>
+      <c r="U150" t="s">
+        <v>1829</v>
+      </c>
+      <c r="V150">
+        <v>13.7399346</v>
+      </c>
+      <c r="W150">
+        <v>-88.021465300000003</v>
+      </c>
+      <c r="X150">
+        <v>603.49530029296875</v>
+      </c>
+      <c r="Y150">
+        <v>4.6349999999999998</v>
+      </c>
+      <c r="AA150" t="s">
+        <v>1828</v>
+      </c>
+      <c r="AB150" t="s">
+        <v>226</v>
+      </c>
+      <c r="AG150" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ150" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK150" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL150" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN150" t="s">
+        <v>1828</v>
+      </c>
+      <c r="AO150" t="s">
+        <v>271</v>
+      </c>
+      <c r="AP150">
+        <v>60</v>
+      </c>
+      <c r="AQ150" t="s">
+        <v>429</v>
+      </c>
+      <c r="AR150" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU150">
+        <v>2</v>
+      </c>
+      <c r="AV150">
+        <v>1</v>
+      </c>
+      <c r="AW150" t="s">
+        <v>1317</v>
+      </c>
+      <c r="AX150">
+        <v>1</v>
+      </c>
+      <c r="AY150">
+        <v>0</v>
+      </c>
+      <c r="BA150" t="s">
+        <v>1318</v>
+      </c>
+      <c r="BB150" t="s">
+        <v>460</v>
+      </c>
+      <c r="BD150" t="s">
+        <v>229</v>
+      </c>
+      <c r="BE150" t="s">
+        <v>229</v>
+      </c>
+      <c r="BF150" t="s">
+        <v>230</v>
+      </c>
+      <c r="BG150" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH150" t="s">
+        <v>282</v>
+      </c>
+      <c r="BI150" t="s">
+        <v>233</v>
+      </c>
+      <c r="BJ150" t="s">
+        <v>283</v>
+      </c>
+      <c r="BK150" t="s">
+        <v>226</v>
+      </c>
+      <c r="BL150" s="1">
+        <v>44562</v>
+      </c>
+      <c r="BM150" t="s">
+        <v>235</v>
+      </c>
+      <c r="BO150" t="s">
+        <v>386</v>
+      </c>
+      <c r="BP150" t="s">
+        <v>477</v>
+      </c>
+      <c r="BR150" t="s">
+        <v>236</v>
+      </c>
+      <c r="BS150" t="s">
+        <v>226</v>
+      </c>
+      <c r="BT150">
+        <v>30</v>
+      </c>
+      <c r="BU150" t="s">
+        <v>308</v>
+      </c>
+      <c r="BV150" t="s">
+        <v>238</v>
+      </c>
+      <c r="BX150">
+        <v>30</v>
+      </c>
+      <c r="BY150" t="s">
+        <v>239</v>
+      </c>
+      <c r="CA150">
+        <v>40</v>
+      </c>
+      <c r="CB150">
+        <v>10</v>
+      </c>
+      <c r="CC150" t="s">
+        <v>1827</v>
+      </c>
+      <c r="CD150">
+        <v>0</v>
+      </c>
+      <c r="CE150">
+        <v>0</v>
+      </c>
+      <c r="CF150">
+        <v>1</v>
+      </c>
+      <c r="CG150">
+        <v>1</v>
+      </c>
+      <c r="CH150">
+        <v>0</v>
+      </c>
+      <c r="CI150">
+        <v>1</v>
+      </c>
+      <c r="CJ150">
+        <v>1</v>
+      </c>
+      <c r="CK150">
+        <v>30</v>
+      </c>
+      <c r="CL150">
+        <v>50</v>
+      </c>
+      <c r="CM150">
+        <v>12</v>
+      </c>
+      <c r="CN150" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO150" t="s">
+        <v>1277</v>
+      </c>
+      <c r="CP150">
+        <v>1</v>
+      </c>
+      <c r="CQ150">
+        <v>0</v>
+      </c>
+      <c r="CR150">
+        <v>0</v>
+      </c>
+      <c r="CS150">
+        <v>0</v>
+      </c>
+      <c r="CT150">
+        <v>0</v>
+      </c>
+      <c r="CU150">
+        <v>0</v>
+      </c>
+      <c r="CV150">
+        <v>0</v>
+      </c>
+      <c r="CW150">
+        <v>60</v>
+      </c>
+      <c r="CX150" t="s">
+        <v>226</v>
+      </c>
+      <c r="CY150" t="s">
+        <v>359</v>
+      </c>
+      <c r="CZ150">
+        <v>0</v>
+      </c>
+      <c r="DA150">
+        <v>0</v>
+      </c>
+      <c r="DB150">
+        <v>1</v>
+      </c>
+      <c r="DC150">
+        <v>0</v>
+      </c>
+      <c r="DD150" t="s">
+        <v>244</v>
+      </c>
+      <c r="DE150">
+        <v>0</v>
+      </c>
+      <c r="DF150">
+        <v>1</v>
+      </c>
+      <c r="DG150">
+        <v>0</v>
+      </c>
+      <c r="DH150">
+        <v>0</v>
+      </c>
+      <c r="DI150">
+        <v>0</v>
+      </c>
+      <c r="DJ150">
+        <v>0</v>
+      </c>
+      <c r="DK150" t="s">
+        <v>315</v>
+      </c>
+      <c r="DL150" t="s">
+        <v>246</v>
+      </c>
+      <c r="DM150">
+        <v>4</v>
+      </c>
+      <c r="DN150" t="s">
+        <v>316</v>
+      </c>
+      <c r="DO150" t="s">
+        <v>622</v>
+      </c>
+      <c r="DP150">
+        <v>0</v>
+      </c>
+      <c r="DQ150">
+        <v>0</v>
+      </c>
+      <c r="DR150">
+        <v>0</v>
+      </c>
+      <c r="DS150">
+        <v>0</v>
+      </c>
+      <c r="DT150">
+        <v>1</v>
+      </c>
+      <c r="DU150">
+        <v>1</v>
+      </c>
+      <c r="DV150">
+        <v>1</v>
+      </c>
+      <c r="DW150">
+        <v>1</v>
+      </c>
+      <c r="DX150">
+        <v>1</v>
+      </c>
+      <c r="DY150">
+        <v>1</v>
+      </c>
+      <c r="DZ150">
+        <v>0</v>
+      </c>
+      <c r="EA150">
+        <v>0</v>
+      </c>
+      <c r="EB150" t="s">
+        <v>292</v>
+      </c>
+      <c r="EC150" t="s">
+        <v>293</v>
+      </c>
+      <c r="ED150" t="s">
+        <v>253</v>
+      </c>
+      <c r="EE150" t="s">
+        <v>363</v>
+      </c>
+      <c r="EF150">
+        <v>1</v>
+      </c>
+      <c r="EG150">
+        <v>0</v>
+      </c>
+      <c r="EH150">
+        <v>0</v>
+      </c>
+      <c r="EI150">
+        <v>0</v>
+      </c>
+      <c r="EJ150">
+        <v>0</v>
+      </c>
+      <c r="EK150">
+        <v>0</v>
+      </c>
+      <c r="EL150" t="s">
+        <v>778</v>
+      </c>
+      <c r="EM150">
+        <v>0</v>
+      </c>
+      <c r="EN150">
+        <v>1</v>
+      </c>
+      <c r="EO150">
+        <v>0</v>
+      </c>
+      <c r="EP150">
+        <v>0</v>
+      </c>
+      <c r="EQ150" t="s">
+        <v>253</v>
+      </c>
+      <c r="ER150" t="s">
+        <v>395</v>
+      </c>
+      <c r="ES150" t="s">
+        <v>255</v>
+      </c>
+      <c r="ET150">
+        <v>0</v>
+      </c>
+      <c r="EU150">
+        <v>0</v>
+      </c>
+      <c r="EV150">
+        <v>0</v>
+      </c>
+      <c r="EW150">
+        <v>0</v>
+      </c>
+      <c r="EX150">
+        <v>1</v>
+      </c>
+      <c r="EY150" t="s">
+        <v>256</v>
+      </c>
+      <c r="EZ150" t="s">
+        <v>257</v>
+      </c>
+      <c r="FA150" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB150" t="s">
+        <v>340</v>
+      </c>
+      <c r="FC150" t="s">
+        <v>259</v>
+      </c>
+      <c r="FD150">
+        <v>1</v>
+      </c>
+      <c r="FE150">
+        <v>0</v>
+      </c>
+      <c r="FF150">
+        <v>0</v>
+      </c>
+      <c r="FG150">
+        <v>0</v>
+      </c>
+      <c r="FH150">
+        <v>0</v>
+      </c>
+      <c r="FI150">
+        <v>0</v>
+      </c>
+      <c r="FJ150" t="s">
+        <v>226</v>
+      </c>
+      <c r="FK150" t="s">
+        <v>226</v>
+      </c>
+      <c r="FM150" t="s">
+        <v>546</v>
+      </c>
+      <c r="FN150">
+        <v>1</v>
+      </c>
+      <c r="FO150">
+        <v>0</v>
+      </c>
+      <c r="FP150">
+        <v>1</v>
+      </c>
+      <c r="FQ150">
+        <v>0</v>
+      </c>
+      <c r="FR150">
+        <v>0</v>
+      </c>
+      <c r="FS150">
+        <v>0</v>
+      </c>
+      <c r="FT150" t="s">
+        <v>226</v>
+      </c>
+      <c r="FU150">
+        <v>1</v>
+      </c>
+      <c r="FV150" t="s">
+        <v>261</v>
+      </c>
+      <c r="FW150">
+        <v>1</v>
+      </c>
+      <c r="FX150">
+        <v>0</v>
+      </c>
+      <c r="FY150">
+        <v>0</v>
+      </c>
+      <c r="FZ150">
+        <v>0</v>
+      </c>
+      <c r="GB150">
+        <v>1</v>
+      </c>
+      <c r="GC150" t="s">
+        <v>262</v>
+      </c>
+      <c r="GD150">
+        <v>1</v>
+      </c>
+      <c r="GE150">
+        <v>0</v>
+      </c>
+      <c r="GF150">
+        <v>0</v>
+      </c>
+      <c r="GG150">
+        <v>0</v>
+      </c>
+      <c r="GH150" t="s">
+        <v>455</v>
+      </c>
+      <c r="GJ150" t="s">
+        <v>226</v>
+      </c>
+      <c r="GK150" t="s">
+        <v>226</v>
+      </c>
+      <c r="GL150" t="s">
+        <v>226</v>
+      </c>
+      <c r="GM150" t="s">
+        <v>226</v>
+      </c>
+      <c r="GN150" t="s">
+        <v>226</v>
+      </c>
+      <c r="GO150" t="s">
+        <v>226</v>
+      </c>
+      <c r="GP150" t="s">
+        <v>226</v>
+      </c>
+      <c r="GQ150" t="s">
+        <v>226</v>
+      </c>
+      <c r="GR150" t="s">
+        <v>263</v>
+      </c>
+      <c r="HC150" t="s">
+        <v>1826</v>
+      </c>
+      <c r="HD150">
+        <v>22557742</v>
+      </c>
+      <c r="HE150" t="s">
+        <v>1825</v>
+      </c>
+      <c r="HF150" s="1">
+        <v>46224.675532407397</v>
+      </c>
+      <c r="HI150" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ150" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK150" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM150" t="s">
+        <v>1824</v>
+      </c>
+      <c r="HN150">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/scall.xlsx
+++ b/data/scall.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Velasco\Desktop\202606 - Reclima FAO - ADEPRO\2. Monitoreo\reclima-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB20534-554C-4BFD-8944-19A349E2C192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804906BD-CA63-47F8-BD26-8DFA2A91D02D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9600" windowHeight="10200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9600" yWindow="0" windowWidth="9600" windowHeight="10200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12627" uniqueCount="1846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14083" uniqueCount="2002">
   <si>
     <t>start</t>
   </si>
@@ -5581,6 +5581,474 @@
   </si>
   <si>
     <t>PAPALON</t>
+  </si>
+  <si>
+    <t>ZOILA ELIZABETH GARCIA</t>
+  </si>
+  <si>
+    <t>EL CHAHUITE</t>
+  </si>
+  <si>
+    <t>FL-711-4</t>
+  </si>
+  <si>
+    <t>ZOILA GARCIA</t>
+  </si>
+  <si>
+    <t>Ago Jul</t>
+  </si>
+  <si>
+    <t>Varas Tareas</t>
+  </si>
+  <si>
+    <t>68654806</t>
+  </si>
+  <si>
+    <t>NO SE LLEGO A LA CASA POR EL DIFICIL ACCESO SE REUNIERON TODAS EN UN MISMO PUNTO</t>
+  </si>
+  <si>
+    <t>388e90e6-ace0-454f-8b78-ea1d2a93cff6</t>
+  </si>
+  <si>
+    <t>uuid:388e90e6-ace0-454f-8b78-ea1d2a93cff6</t>
+  </si>
+  <si>
+    <t>SANTOS FIDELINA DIAZ DE MARQUEZ</t>
+  </si>
+  <si>
+    <t>LOS TORICES</t>
+  </si>
+  <si>
+    <t>XV-129-0</t>
+  </si>
+  <si>
+    <t>13.9086109 -88.1041931 704.86669921875 4.607</t>
+  </si>
+  <si>
+    <t>SANTOS DIAZ</t>
+  </si>
+  <si>
+    <t>Cocinar Lavar alimentos Higiene Limpieza Huerto Animales Beber</t>
+  </si>
+  <si>
+    <t>Instalación Reparaciones básicas Limpieza Uso</t>
+  </si>
+  <si>
+    <t>75389221</t>
+  </si>
+  <si>
+    <t>7e5e67ff-c1d0-4e4c-aeb4-e41f7e93cd1f</t>
+  </si>
+  <si>
+    <t>uuid:7e5e67ff-c1d0-4e4c-aeb4-e41f7e93cd1f</t>
+  </si>
+  <si>
+    <t>SANDRA MARISOL MARQUEZ ARGUETA</t>
+  </si>
+  <si>
+    <t>AW-325-5</t>
+  </si>
+  <si>
+    <t>13.9088325 -88.1052227 747.2021484375 4.147</t>
+  </si>
+  <si>
+    <t>SANDRA MARQUEZ</t>
+  </si>
+  <si>
+    <t>TIENE DESINSTALADO EL TANQUE PORQUE ESTAN RECONSTRUYENDO LA CASA Y AUN NO LO CONECTAN</t>
+  </si>
+  <si>
+    <t>LA FAMILIA TIENE CUATRO MESES DE NO USAR EL TANQUE PORQUE HUBO UN DERRUMBE DONDE LO TENIAN Y NO LO HAN VUELTO A CONECTAR</t>
+  </si>
+  <si>
+    <t>b51cffa3-39ac-4a97-97b6-366331191e0e</t>
+  </si>
+  <si>
+    <t>uuid:b51cffa3-39ac-4a97-97b6-366331191e0e</t>
+  </si>
+  <si>
+    <t>MIRNA ELIZABETH HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MW-970-1</t>
+  </si>
+  <si>
+    <t>13.7399161 -88.0214917 601.6 4.6</t>
+  </si>
+  <si>
+    <t>SANTOS GABRIEL ZARABIA</t>
+  </si>
+  <si>
+    <t>SANTOS GABRIEL</t>
+  </si>
+  <si>
+    <t>Huerto Preparación de alimentos Animales</t>
+  </si>
+  <si>
+    <t>72198666</t>
+  </si>
+  <si>
+    <t>0219a4a2-e217-4152-bc3b-1c3b918e4bda</t>
+  </si>
+  <si>
+    <t>uuid:0219a4a2-e217-4152-bc3b-1c3b918e4bda</t>
+  </si>
+  <si>
+    <t>OSCAR ELIAS ARAGON GARCIA</t>
+  </si>
+  <si>
+    <t>AGUA SALADA</t>
+  </si>
+  <si>
+    <t>KE-469-9</t>
+  </si>
+  <si>
+    <t>13.4767083 -88.1001033 144.50001525878906 2.533</t>
+  </si>
+  <si>
+    <t>MARIA IMELDA GARCIA</t>
+  </si>
+  <si>
+    <t>MARIA IMELDA</t>
+  </si>
+  <si>
+    <t>Comercio informal</t>
+  </si>
+  <si>
+    <t>Lavar alimentos Higiene Limpieza Cocinar Huerto Animales</t>
+  </si>
+  <si>
+    <t>Uso Limpieza Instalación</t>
+  </si>
+  <si>
+    <t>79434495</t>
+  </si>
+  <si>
+    <t>NUMERO DE LA MAMA</t>
+  </si>
+  <si>
+    <t>7081a628-3cf5-4508-a276-3977ee9b0bf9</t>
+  </si>
+  <si>
+    <t>uuid:7081a628-3cf5-4508-a276-3977ee9b0bf9</t>
+  </si>
+  <si>
+    <t>MELVIN ALMILCAR MOLINA ROMERO</t>
+  </si>
+  <si>
+    <t>VC-229-4</t>
+  </si>
+  <si>
+    <t>13.47735 -88.0972317 164.00001525878906 2.4</t>
+  </si>
+  <si>
+    <t>JOSE ERIBERTO MOLINA</t>
+  </si>
+  <si>
+    <t>MELVIN AMILCAR</t>
+  </si>
+  <si>
+    <t>Superior universitario</t>
+  </si>
+  <si>
+    <t>Agrícola Ganadero Silvícola</t>
+  </si>
+  <si>
+    <t>70608943</t>
+  </si>
+  <si>
+    <t>05e8025d-2e8f-47d5-b552-cef8394908b5</t>
+  </si>
+  <si>
+    <t>uuid:05e8025d-2e8f-47d5-b552-cef8394908b5</t>
+  </si>
+  <si>
+    <t>BERTA LETICIA SANCHEZ</t>
+  </si>
+  <si>
+    <t>YK-521-6</t>
+  </si>
+  <si>
+    <t>13.9095707 -88.1065111 857.2999877929688 4.46</t>
+  </si>
+  <si>
+    <t>BERTA SANCHEZ</t>
+  </si>
+  <si>
+    <t>BERTA LETICIA</t>
+  </si>
+  <si>
+    <t>78963274</t>
+  </si>
+  <si>
+    <t>6a294dee-bac1-4b50-8ecc-d070bb67b812</t>
+  </si>
+  <si>
+    <t>uuid:6a294dee-bac1-4b50-8ecc-d070bb67b812</t>
+  </si>
+  <si>
+    <t>HEIDY MARIBEL CLAROS SANCHEZ</t>
+  </si>
+  <si>
+    <t>PP-145-0</t>
+  </si>
+  <si>
+    <t>13.908792 -88.1057475 857.2999877929688 4.1</t>
+  </si>
+  <si>
+    <t>HEIDY MARIBEL</t>
+  </si>
+  <si>
+    <t>HEIDY MARIBEL CLAROS</t>
+  </si>
+  <si>
+    <t>Cocinar Lavar alimentos Beber Higiene Limpieza Huerto Animales</t>
+  </si>
+  <si>
+    <t>Ago Sep Oct Nov</t>
+  </si>
+  <si>
+    <t>78052714</t>
+  </si>
+  <si>
+    <t>39bce6e5-fde7-413e-89ee-8bfee2b32d6a</t>
+  </si>
+  <si>
+    <t>uuid:39bce6e5-fde7-413e-89ee-8bfee2b32d6a</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>MARIA DE LA CRUZ TORRES</t>
+  </si>
+  <si>
+    <t>HP-504-1</t>
+  </si>
+  <si>
+    <t>13.4695262 -88.1263002 111.19999694824219 4.848</t>
+  </si>
+  <si>
+    <t>Electricidad</t>
+  </si>
+  <si>
+    <t>71553081</t>
+  </si>
+  <si>
+    <t>3fdc64c9-3343-4e56-9dc9-e5126203444f</t>
+  </si>
+  <si>
+    <t>uuid:3fdc64c9-3343-4e56-9dc9-e5126203444f</t>
+  </si>
+  <si>
+    <t>ARMIDAS DEL CARMEN PEREIRA</t>
+  </si>
+  <si>
+    <t>LR-560-5</t>
+  </si>
+  <si>
+    <t>13.9006723 -88.0986823 623.17966540748 4.994</t>
+  </si>
+  <si>
+    <t>IRIS ONEIDA NOLASCO PEREIRA</t>
+  </si>
+  <si>
+    <t>ARMIDA</t>
+  </si>
+  <si>
+    <t>70231523</t>
+  </si>
+  <si>
+    <t>4def3bc8-e7fc-4151-b66a-3af6429118d6</t>
+  </si>
+  <si>
+    <t>uuid:4def3bc8-e7fc-4151-b66a-3af6429118d6</t>
+  </si>
+  <si>
+    <t>MAURA EDY PEREIRA ARGUETA</t>
+  </si>
+  <si>
+    <t>FN-436--4</t>
+  </si>
+  <si>
+    <t>13.9005388 -88.0988635 621.200927734375 4.811</t>
+  </si>
+  <si>
+    <t>MAURA</t>
+  </si>
+  <si>
+    <t>Limpieza Huerto Animales</t>
+  </si>
+  <si>
+    <t>Canaletas Tanque Base para tanque Tuberías</t>
+  </si>
+  <si>
+    <t>60646633</t>
+  </si>
+  <si>
+    <t>61a404ba-fe3f-42c3-9b36-e86c362a24bf</t>
+  </si>
+  <si>
+    <t>uuid:61a404ba-fe3f-42c3-9b36-e86c362a24bf</t>
+  </si>
+  <si>
+    <t>BASILIA DEL CARMEN CANALES BONILLA</t>
+  </si>
+  <si>
+    <t>EL CARRISAL</t>
+  </si>
+  <si>
+    <t>HV-667-4</t>
+  </si>
+  <si>
+    <t>BASILIA</t>
+  </si>
+  <si>
+    <t>NO SABE</t>
+  </si>
+  <si>
+    <t>68658191</t>
+  </si>
+  <si>
+    <t>66dab040-f38e-41db-a069-7095be4f9dea</t>
+  </si>
+  <si>
+    <t>uuid:66dab040-f38e-41db-a069-7095be4f9dea</t>
+  </si>
+  <si>
+    <t>JACQUELINE DEL ROSARIO AMAYA ALVARENGA</t>
+  </si>
+  <si>
+    <t>XN-896-2</t>
+  </si>
+  <si>
+    <t>13.462635 -88.1139383 108.5999984741211 4.666</t>
+  </si>
+  <si>
+    <t>JACQUELINE ALVARENGA</t>
+  </si>
+  <si>
+    <t>JACKY</t>
+  </si>
+  <si>
+    <t>Cocinar Beber Lavar alimentos</t>
+  </si>
+  <si>
+    <t>60396967</t>
+  </si>
+  <si>
+    <t>61566464</t>
+  </si>
+  <si>
+    <t>3a280bbc-8312-40de-a929-1368c32dae29</t>
+  </si>
+  <si>
+    <t>uuid:3a280bbc-8312-40de-a929-1368c32dae29</t>
+  </si>
+  <si>
+    <t>MARTA SOFIA SAENZ DE PEREIRA</t>
+  </si>
+  <si>
+    <t>WH-692-0</t>
+  </si>
+  <si>
+    <t>13.908131 -88.1026476 760.9000000000001 4.78</t>
+  </si>
+  <si>
+    <t>TIODOSA ARGUETA DE PEREIRA</t>
+  </si>
+  <si>
+    <t>SOFIA</t>
+  </si>
+  <si>
+    <t>77951858</t>
+  </si>
+  <si>
+    <t>75655481</t>
+  </si>
+  <si>
+    <t>6d32113e-dbbc-425c-9c7f-94569783d55e</t>
+  </si>
+  <si>
+    <t>uuid:6d32113e-dbbc-425c-9c7f-94569783d55e</t>
+  </si>
+  <si>
+    <t>MARIA DOLORES MARQUEZ</t>
+  </si>
+  <si>
+    <t>YY-554-5</t>
+  </si>
+  <si>
+    <t>13.910751 -88.1054012 720.7999877929688 4.966</t>
+  </si>
+  <si>
+    <t>LOLA</t>
+  </si>
+  <si>
+    <t>72132213</t>
+  </si>
+  <si>
+    <t>e281cee6-dd78-4358-804d-32ead4b0b7b6</t>
+  </si>
+  <si>
+    <t>uuid:e281cee6-dd78-4358-804d-32ead4b0b7b6</t>
+  </si>
+  <si>
+    <t>LOS VILLA ALTA</t>
+  </si>
+  <si>
+    <t>TEPEMECHIN</t>
+  </si>
+  <si>
+    <t>WD-468-9</t>
+  </si>
+  <si>
+    <t>ARACELY SANCHEZ</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>Limpieza Uso Instalación</t>
+  </si>
+  <si>
+    <t>72008171</t>
+  </si>
+  <si>
+    <t>LA PERSONA FUE CONVOCA A UN LUGAR POR LA DISTANCIA EN LA QUE VIVE</t>
+  </si>
+  <si>
+    <t>ac233fee-1828-4244-8495-7de342918a4c</t>
+  </si>
+  <si>
+    <t>uuid:ac233fee-1828-4244-8495-7de342918a4c</t>
+  </si>
+  <si>
+    <t>MARTA RIVERA CRUZ</t>
+  </si>
+  <si>
+    <t>EL CALIZAL</t>
+  </si>
+  <si>
+    <t>EY-611-9</t>
+  </si>
+  <si>
+    <t>Higiene Limpieza Lavar alimentos Huerto Animales</t>
+  </si>
+  <si>
+    <t>Mayor presencia de mosquitos Mayores gastos</t>
+  </si>
+  <si>
+    <t>75971774</t>
+  </si>
+  <si>
+    <t>LA PERSONA FUE CONVOCADA A UN LUGAR YA QUE ELLA SE ENCONTRABA A UNA LARGA DISTANCIA</t>
+  </si>
+  <si>
+    <t>9763c467-a0bf-43bf-924f-5c1a3143617a</t>
+  </si>
+  <si>
+    <t>uuid:9763c467-a0bf-43bf-924f-5c1a3143617a</t>
   </si>
 </sst>
 </file>
@@ -5926,7 +6394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:HN150"/>
+  <dimension ref="A1:HN167"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
@@ -84272,6 +84740,8898 @@
         <v>49</v>
       </c>
     </row>
+    <row r="151" spans="1:222">
+      <c r="A151" t="str">
+        <f t="shared" ref="A151:A167" si="4">"V"&amp;B151&amp;"-R"&amp;HN151</f>
+        <v>V2-R50</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
+      </c>
+      <c r="C151" s="1">
+        <v>46212.404680636573</v>
+      </c>
+      <c r="D151" s="1">
+        <v>46224.648692187497</v>
+      </c>
+      <c r="E151" s="1">
+        <v>46212</v>
+      </c>
+      <c r="G151" t="s">
+        <v>451</v>
+      </c>
+      <c r="H151" t="s">
+        <v>452</v>
+      </c>
+      <c r="I151" s="1">
+        <v>46212</v>
+      </c>
+      <c r="K151" t="s">
+        <v>1846</v>
+      </c>
+      <c r="L151">
+        <v>32</v>
+      </c>
+      <c r="M151" t="s">
+        <v>271</v>
+      </c>
+      <c r="O151" t="s">
+        <v>1297</v>
+      </c>
+      <c r="P151" t="s">
+        <v>1326</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>1427</v>
+      </c>
+      <c r="R151" t="s">
+        <v>1847</v>
+      </c>
+      <c r="S151" t="s">
+        <v>1768</v>
+      </c>
+      <c r="T151" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AA151" t="s">
+        <v>1849</v>
+      </c>
+      <c r="AB151" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD151" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG151" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ151" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK151" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL151" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN151" t="s">
+        <v>1849</v>
+      </c>
+      <c r="AO151" t="s">
+        <v>271</v>
+      </c>
+      <c r="AP151">
+        <v>32</v>
+      </c>
+      <c r="AQ151" t="s">
+        <v>429</v>
+      </c>
+      <c r="AR151" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU151">
+        <v>8</v>
+      </c>
+      <c r="AV151">
+        <v>3</v>
+      </c>
+      <c r="AW151" t="s">
+        <v>1668</v>
+      </c>
+      <c r="AX151">
+        <v>5</v>
+      </c>
+      <c r="AY151">
+        <v>6</v>
+      </c>
+      <c r="AZ151">
+        <v>2</v>
+      </c>
+      <c r="BA151" t="s">
+        <v>1318</v>
+      </c>
+      <c r="BB151" t="s">
+        <v>306</v>
+      </c>
+      <c r="BD151" t="s">
+        <v>278</v>
+      </c>
+      <c r="BE151" t="s">
+        <v>229</v>
+      </c>
+      <c r="BF151" t="s">
+        <v>230</v>
+      </c>
+      <c r="BG151" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH151" t="s">
+        <v>232</v>
+      </c>
+      <c r="BI151" t="s">
+        <v>553</v>
+      </c>
+      <c r="BJ151" t="s">
+        <v>283</v>
+      </c>
+      <c r="BK151" t="s">
+        <v>226</v>
+      </c>
+      <c r="BL151" s="1">
+        <v>45658</v>
+      </c>
+      <c r="BM151" t="s">
+        <v>477</v>
+      </c>
+      <c r="BO151" t="s">
+        <v>236</v>
+      </c>
+      <c r="BP151" t="s">
+        <v>477</v>
+      </c>
+      <c r="BR151" t="s">
+        <v>236</v>
+      </c>
+      <c r="BS151" t="s">
+        <v>226</v>
+      </c>
+      <c r="BT151">
+        <v>180</v>
+      </c>
+      <c r="BU151" t="s">
+        <v>387</v>
+      </c>
+      <c r="BV151" t="s">
+        <v>238</v>
+      </c>
+      <c r="BX151">
+        <v>99</v>
+      </c>
+      <c r="BY151" t="s">
+        <v>239</v>
+      </c>
+      <c r="CA151">
+        <v>30</v>
+      </c>
+      <c r="CB151">
+        <v>5</v>
+      </c>
+      <c r="CC151" t="s">
+        <v>1127</v>
+      </c>
+      <c r="CD151">
+        <v>1</v>
+      </c>
+      <c r="CE151">
+        <v>1</v>
+      </c>
+      <c r="CF151">
+        <v>1</v>
+      </c>
+      <c r="CG151">
+        <v>1</v>
+      </c>
+      <c r="CH151">
+        <v>1</v>
+      </c>
+      <c r="CI151">
+        <v>0</v>
+      </c>
+      <c r="CJ151">
+        <v>0</v>
+      </c>
+      <c r="CK151">
+        <v>0</v>
+      </c>
+      <c r="CL151">
+        <v>0</v>
+      </c>
+      <c r="CM151">
+        <v>9999</v>
+      </c>
+      <c r="CN151" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO151" t="s">
+        <v>242</v>
+      </c>
+      <c r="CP151">
+        <v>0</v>
+      </c>
+      <c r="CQ151">
+        <v>0</v>
+      </c>
+      <c r="CR151">
+        <v>0</v>
+      </c>
+      <c r="CS151">
+        <v>0</v>
+      </c>
+      <c r="CT151">
+        <v>0</v>
+      </c>
+      <c r="CU151">
+        <v>0</v>
+      </c>
+      <c r="CV151">
+        <v>1</v>
+      </c>
+      <c r="CW151">
+        <v>0</v>
+      </c>
+      <c r="CX151" t="s">
+        <v>226</v>
+      </c>
+      <c r="CY151" t="s">
+        <v>243</v>
+      </c>
+      <c r="CZ151">
+        <v>1</v>
+      </c>
+      <c r="DA151">
+        <v>1</v>
+      </c>
+      <c r="DB151">
+        <v>1</v>
+      </c>
+      <c r="DC151">
+        <v>1</v>
+      </c>
+      <c r="DD151" t="s">
+        <v>244</v>
+      </c>
+      <c r="DE151">
+        <v>0</v>
+      </c>
+      <c r="DF151">
+        <v>1</v>
+      </c>
+      <c r="DG151">
+        <v>0</v>
+      </c>
+      <c r="DH151">
+        <v>0</v>
+      </c>
+      <c r="DI151">
+        <v>0</v>
+      </c>
+      <c r="DJ151">
+        <v>0</v>
+      </c>
+      <c r="DK151" t="s">
+        <v>289</v>
+      </c>
+      <c r="DL151" t="s">
+        <v>361</v>
+      </c>
+      <c r="DM151">
+        <v>0</v>
+      </c>
+      <c r="DN151" t="s">
+        <v>316</v>
+      </c>
+      <c r="DO151" t="s">
+        <v>1850</v>
+      </c>
+      <c r="DP151">
+        <v>0</v>
+      </c>
+      <c r="DQ151">
+        <v>0</v>
+      </c>
+      <c r="DR151">
+        <v>0</v>
+      </c>
+      <c r="DS151">
+        <v>0</v>
+      </c>
+      <c r="DT151">
+        <v>0</v>
+      </c>
+      <c r="DU151">
+        <v>0</v>
+      </c>
+      <c r="DV151">
+        <v>1</v>
+      </c>
+      <c r="DW151">
+        <v>1</v>
+      </c>
+      <c r="DX151">
+        <v>0</v>
+      </c>
+      <c r="DY151">
+        <v>0</v>
+      </c>
+      <c r="DZ151">
+        <v>0</v>
+      </c>
+      <c r="EA151">
+        <v>0</v>
+      </c>
+      <c r="EB151" t="s">
+        <v>292</v>
+      </c>
+      <c r="EC151" t="s">
+        <v>293</v>
+      </c>
+      <c r="ED151" t="s">
+        <v>253</v>
+      </c>
+      <c r="EE151" t="s">
+        <v>363</v>
+      </c>
+      <c r="EF151">
+        <v>1</v>
+      </c>
+      <c r="EG151">
+        <v>0</v>
+      </c>
+      <c r="EH151">
+        <v>0</v>
+      </c>
+      <c r="EI151">
+        <v>0</v>
+      </c>
+      <c r="EJ151">
+        <v>0</v>
+      </c>
+      <c r="EK151">
+        <v>0</v>
+      </c>
+      <c r="EL151" t="s">
+        <v>1147</v>
+      </c>
+      <c r="EM151">
+        <v>1</v>
+      </c>
+      <c r="EN151">
+        <v>1</v>
+      </c>
+      <c r="EO151">
+        <v>1</v>
+      </c>
+      <c r="EP151">
+        <v>0</v>
+      </c>
+      <c r="EQ151" t="s">
+        <v>253</v>
+      </c>
+      <c r="ER151" t="s">
+        <v>338</v>
+      </c>
+      <c r="ES151" t="s">
+        <v>255</v>
+      </c>
+      <c r="ET151">
+        <v>0</v>
+      </c>
+      <c r="EU151">
+        <v>0</v>
+      </c>
+      <c r="EV151">
+        <v>0</v>
+      </c>
+      <c r="EW151">
+        <v>0</v>
+      </c>
+      <c r="EX151">
+        <v>1</v>
+      </c>
+      <c r="EY151" t="s">
+        <v>256</v>
+      </c>
+      <c r="EZ151" t="s">
+        <v>257</v>
+      </c>
+      <c r="FA151" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB151" t="s">
+        <v>447</v>
+      </c>
+      <c r="FC151" t="s">
+        <v>259</v>
+      </c>
+      <c r="FD151">
+        <v>1</v>
+      </c>
+      <c r="FE151">
+        <v>0</v>
+      </c>
+      <c r="FF151">
+        <v>0</v>
+      </c>
+      <c r="FG151">
+        <v>0</v>
+      </c>
+      <c r="FH151">
+        <v>0</v>
+      </c>
+      <c r="FI151">
+        <v>0</v>
+      </c>
+      <c r="FJ151" t="s">
+        <v>226</v>
+      </c>
+      <c r="FK151" t="s">
+        <v>263</v>
+      </c>
+      <c r="FM151" t="s">
+        <v>1647</v>
+      </c>
+      <c r="FN151">
+        <v>1</v>
+      </c>
+      <c r="FO151">
+        <v>1</v>
+      </c>
+      <c r="FP151">
+        <v>1</v>
+      </c>
+      <c r="FQ151">
+        <v>1</v>
+      </c>
+      <c r="FR151">
+        <v>0</v>
+      </c>
+      <c r="FS151">
+        <v>1</v>
+      </c>
+      <c r="FT151" t="s">
+        <v>226</v>
+      </c>
+      <c r="FU151">
+        <v>1</v>
+      </c>
+      <c r="FV151" t="s">
+        <v>261</v>
+      </c>
+      <c r="FW151">
+        <v>1</v>
+      </c>
+      <c r="FX151">
+        <v>0</v>
+      </c>
+      <c r="FY151">
+        <v>0</v>
+      </c>
+      <c r="FZ151">
+        <v>0</v>
+      </c>
+      <c r="GB151">
+        <v>14</v>
+      </c>
+      <c r="GC151" t="s">
+        <v>1851</v>
+      </c>
+      <c r="GD151">
+        <v>0</v>
+      </c>
+      <c r="GE151">
+        <v>1</v>
+      </c>
+      <c r="GF151">
+        <v>1</v>
+      </c>
+      <c r="GG151">
+        <v>0</v>
+      </c>
+      <c r="GH151" t="s">
+        <v>1427</v>
+      </c>
+      <c r="GI151" t="s">
+        <v>420</v>
+      </c>
+      <c r="GJ151" t="s">
+        <v>226</v>
+      </c>
+      <c r="GK151" t="s">
+        <v>226</v>
+      </c>
+      <c r="GL151" t="s">
+        <v>263</v>
+      </c>
+      <c r="GM151" t="s">
+        <v>226</v>
+      </c>
+      <c r="GN151" t="s">
+        <v>226</v>
+      </c>
+      <c r="GO151" t="s">
+        <v>226</v>
+      </c>
+      <c r="GP151" t="s">
+        <v>226</v>
+      </c>
+      <c r="GQ151" t="s">
+        <v>263</v>
+      </c>
+      <c r="GR151" t="s">
+        <v>226</v>
+      </c>
+      <c r="GS151" t="s">
+        <v>263</v>
+      </c>
+      <c r="GT151" t="s">
+        <v>226</v>
+      </c>
+      <c r="GU151" t="s">
+        <v>263</v>
+      </c>
+      <c r="GV151" t="s">
+        <v>226</v>
+      </c>
+      <c r="GW151" t="s">
+        <v>226</v>
+      </c>
+      <c r="GX151" t="s">
+        <v>263</v>
+      </c>
+      <c r="GY151" t="s">
+        <v>263</v>
+      </c>
+      <c r="GZ151" t="s">
+        <v>1852</v>
+      </c>
+      <c r="HC151" t="s">
+        <v>1853</v>
+      </c>
+      <c r="HD151">
+        <v>22561436</v>
+      </c>
+      <c r="HE151" t="s">
+        <v>1854</v>
+      </c>
+      <c r="HF151" s="1">
+        <v>46224.899560185193</v>
+      </c>
+      <c r="HI151" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ151" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK151" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM151" t="s">
+        <v>1855</v>
+      </c>
+      <c r="HN151">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="152" spans="1:222">
+      <c r="A152" t="str">
+        <f t="shared" si="4"/>
+        <v>V2-R51</v>
+      </c>
+      <c r="B152">
+        <v>2</v>
+      </c>
+      <c r="C152" s="1">
+        <v>46220.587623993059</v>
+      </c>
+      <c r="D152" s="1">
+        <v>46224.771735462957</v>
+      </c>
+      <c r="E152" s="1">
+        <v>46220</v>
+      </c>
+      <c r="G152" t="s">
+        <v>451</v>
+      </c>
+      <c r="H152" t="s">
+        <v>452</v>
+      </c>
+      <c r="I152" s="1">
+        <v>46220</v>
+      </c>
+      <c r="K152" t="s">
+        <v>1856</v>
+      </c>
+      <c r="L152">
+        <v>39</v>
+      </c>
+      <c r="M152" t="s">
+        <v>271</v>
+      </c>
+      <c r="O152" t="s">
+        <v>348</v>
+      </c>
+      <c r="P152" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>685</v>
+      </c>
+      <c r="R152" t="s">
+        <v>686</v>
+      </c>
+      <c r="S152" t="s">
+        <v>1857</v>
+      </c>
+      <c r="T152" t="s">
+        <v>1858</v>
+      </c>
+      <c r="U152" t="s">
+        <v>1859</v>
+      </c>
+      <c r="V152">
+        <v>13.908610899999999</v>
+      </c>
+      <c r="W152">
+        <v>-88.104193100000003</v>
+      </c>
+      <c r="X152">
+        <v>704.86669921875</v>
+      </c>
+      <c r="Y152">
+        <v>4.6070000000000002</v>
+      </c>
+      <c r="AA152" t="s">
+        <v>1860</v>
+      </c>
+      <c r="AB152" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD152" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG152" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ152" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK152" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL152" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN152" t="s">
+        <v>1860</v>
+      </c>
+      <c r="AO152" t="s">
+        <v>271</v>
+      </c>
+      <c r="AP152">
+        <v>39</v>
+      </c>
+      <c r="AQ152" t="s">
+        <v>429</v>
+      </c>
+      <c r="AR152" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU152">
+        <v>4</v>
+      </c>
+      <c r="AV152">
+        <v>2</v>
+      </c>
+      <c r="AW152" t="s">
+        <v>430</v>
+      </c>
+      <c r="AX152">
+        <v>2</v>
+      </c>
+      <c r="AY152">
+        <v>0</v>
+      </c>
+      <c r="AZ152">
+        <v>2</v>
+      </c>
+      <c r="BA152" t="s">
+        <v>1318</v>
+      </c>
+      <c r="BB152" t="s">
+        <v>306</v>
+      </c>
+      <c r="BD152" t="s">
+        <v>278</v>
+      </c>
+      <c r="BE152" t="s">
+        <v>229</v>
+      </c>
+      <c r="BF152" t="s">
+        <v>230</v>
+      </c>
+      <c r="BG152" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH152" t="s">
+        <v>232</v>
+      </c>
+      <c r="BI152" t="s">
+        <v>233</v>
+      </c>
+      <c r="BJ152" t="s">
+        <v>283</v>
+      </c>
+      <c r="BK152" t="s">
+        <v>226</v>
+      </c>
+      <c r="BL152" s="1">
+        <v>45292</v>
+      </c>
+      <c r="BM152" t="s">
+        <v>331</v>
+      </c>
+      <c r="BO152" t="s">
+        <v>236</v>
+      </c>
+      <c r="BP152" t="s">
+        <v>477</v>
+      </c>
+      <c r="BR152" t="s">
+        <v>236</v>
+      </c>
+      <c r="BS152" t="s">
+        <v>263</v>
+      </c>
+      <c r="BU152" t="s">
+        <v>255</v>
+      </c>
+      <c r="BV152" t="s">
+        <v>238</v>
+      </c>
+      <c r="BX152">
+        <v>20</v>
+      </c>
+      <c r="BY152" t="s">
+        <v>239</v>
+      </c>
+      <c r="CA152">
+        <v>9999</v>
+      </c>
+      <c r="CB152">
+        <v>4</v>
+      </c>
+      <c r="CC152" t="s">
+        <v>1861</v>
+      </c>
+      <c r="CD152">
+        <v>1</v>
+      </c>
+      <c r="CE152">
+        <v>1</v>
+      </c>
+      <c r="CF152">
+        <v>1</v>
+      </c>
+      <c r="CG152">
+        <v>1</v>
+      </c>
+      <c r="CH152">
+        <v>1</v>
+      </c>
+      <c r="CI152">
+        <v>1</v>
+      </c>
+      <c r="CJ152">
+        <v>1</v>
+      </c>
+      <c r="CK152">
+        <v>0</v>
+      </c>
+      <c r="CL152">
+        <v>0</v>
+      </c>
+      <c r="CM152">
+        <v>9999</v>
+      </c>
+      <c r="CN152" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO152" t="s">
+        <v>242</v>
+      </c>
+      <c r="CP152">
+        <v>0</v>
+      </c>
+      <c r="CQ152">
+        <v>0</v>
+      </c>
+      <c r="CR152">
+        <v>0</v>
+      </c>
+      <c r="CS152">
+        <v>0</v>
+      </c>
+      <c r="CT152">
+        <v>0</v>
+      </c>
+      <c r="CU152">
+        <v>0</v>
+      </c>
+      <c r="CV152">
+        <v>1</v>
+      </c>
+      <c r="CW152">
+        <v>0</v>
+      </c>
+      <c r="CX152" t="s">
+        <v>226</v>
+      </c>
+      <c r="CY152" t="s">
+        <v>1862</v>
+      </c>
+      <c r="CZ152">
+        <v>1</v>
+      </c>
+      <c r="DA152">
+        <v>1</v>
+      </c>
+      <c r="DB152">
+        <v>1</v>
+      </c>
+      <c r="DC152">
+        <v>1</v>
+      </c>
+      <c r="DD152" t="s">
+        <v>1714</v>
+      </c>
+      <c r="DE152">
+        <v>0</v>
+      </c>
+      <c r="DF152">
+        <v>1</v>
+      </c>
+      <c r="DG152">
+        <v>1</v>
+      </c>
+      <c r="DH152">
+        <v>0</v>
+      </c>
+      <c r="DI152">
+        <v>0</v>
+      </c>
+      <c r="DJ152">
+        <v>0</v>
+      </c>
+      <c r="DK152" t="s">
+        <v>289</v>
+      </c>
+      <c r="DL152" t="s">
+        <v>263</v>
+      </c>
+      <c r="DM152">
+        <v>0</v>
+      </c>
+      <c r="DN152" t="s">
+        <v>247</v>
+      </c>
+      <c r="DO152" t="s">
+        <v>1013</v>
+      </c>
+      <c r="DP152">
+        <v>0</v>
+      </c>
+      <c r="DQ152">
+        <v>0</v>
+      </c>
+      <c r="DR152">
+        <v>0</v>
+      </c>
+      <c r="DS152">
+        <v>0</v>
+      </c>
+      <c r="DT152">
+        <v>0</v>
+      </c>
+      <c r="DU152">
+        <v>0</v>
+      </c>
+      <c r="DV152">
+        <v>0</v>
+      </c>
+      <c r="DW152">
+        <v>1</v>
+      </c>
+      <c r="DX152">
+        <v>1</v>
+      </c>
+      <c r="DY152">
+        <v>1</v>
+      </c>
+      <c r="DZ152">
+        <v>1</v>
+      </c>
+      <c r="EA152">
+        <v>1</v>
+      </c>
+      <c r="EB152" t="s">
+        <v>245</v>
+      </c>
+      <c r="EC152" t="s">
+        <v>293</v>
+      </c>
+      <c r="ED152" t="s">
+        <v>253</v>
+      </c>
+      <c r="EE152" t="s">
+        <v>251</v>
+      </c>
+      <c r="EF152">
+        <v>0</v>
+      </c>
+      <c r="EG152">
+        <v>0</v>
+      </c>
+      <c r="EH152">
+        <v>0</v>
+      </c>
+      <c r="EI152">
+        <v>1</v>
+      </c>
+      <c r="EJ152">
+        <v>0</v>
+      </c>
+      <c r="EK152">
+        <v>0</v>
+      </c>
+      <c r="EL152" t="s">
+        <v>394</v>
+      </c>
+      <c r="EM152">
+        <v>1</v>
+      </c>
+      <c r="EN152">
+        <v>1</v>
+      </c>
+      <c r="EO152">
+        <v>1</v>
+      </c>
+      <c r="EP152">
+        <v>0</v>
+      </c>
+      <c r="EQ152" t="s">
+        <v>253</v>
+      </c>
+      <c r="ER152" t="s">
+        <v>338</v>
+      </c>
+      <c r="ES152" t="s">
+        <v>255</v>
+      </c>
+      <c r="ET152">
+        <v>0</v>
+      </c>
+      <c r="EU152">
+        <v>0</v>
+      </c>
+      <c r="EV152">
+        <v>0</v>
+      </c>
+      <c r="EW152">
+        <v>0</v>
+      </c>
+      <c r="EX152">
+        <v>1</v>
+      </c>
+      <c r="EY152" t="s">
+        <v>256</v>
+      </c>
+      <c r="EZ152" t="s">
+        <v>257</v>
+      </c>
+      <c r="FA152" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB152" t="s">
+        <v>340</v>
+      </c>
+      <c r="FC152" t="s">
+        <v>259</v>
+      </c>
+      <c r="FD152">
+        <v>1</v>
+      </c>
+      <c r="FE152">
+        <v>0</v>
+      </c>
+      <c r="FF152">
+        <v>0</v>
+      </c>
+      <c r="FG152">
+        <v>0</v>
+      </c>
+      <c r="FH152">
+        <v>0</v>
+      </c>
+      <c r="FI152">
+        <v>0</v>
+      </c>
+      <c r="FJ152" t="s">
+        <v>226</v>
+      </c>
+      <c r="FK152" t="s">
+        <v>263</v>
+      </c>
+      <c r="FM152" t="s">
+        <v>1647</v>
+      </c>
+      <c r="FN152">
+        <v>1</v>
+      </c>
+      <c r="FO152">
+        <v>1</v>
+      </c>
+      <c r="FP152">
+        <v>1</v>
+      </c>
+      <c r="FQ152">
+        <v>1</v>
+      </c>
+      <c r="FR152">
+        <v>0</v>
+      </c>
+      <c r="FS152">
+        <v>1</v>
+      </c>
+      <c r="FT152" t="s">
+        <v>226</v>
+      </c>
+      <c r="FU152">
+        <v>1</v>
+      </c>
+      <c r="FV152" t="s">
+        <v>261</v>
+      </c>
+      <c r="FW152">
+        <v>1</v>
+      </c>
+      <c r="FX152">
+        <v>0</v>
+      </c>
+      <c r="FY152">
+        <v>0</v>
+      </c>
+      <c r="FZ152">
+        <v>0</v>
+      </c>
+      <c r="GB152">
+        <v>1</v>
+      </c>
+      <c r="GC152" t="s">
+        <v>262</v>
+      </c>
+      <c r="GD152">
+        <v>1</v>
+      </c>
+      <c r="GE152">
+        <v>0</v>
+      </c>
+      <c r="GF152">
+        <v>0</v>
+      </c>
+      <c r="GG152">
+        <v>0</v>
+      </c>
+      <c r="GH152" t="s">
+        <v>685</v>
+      </c>
+      <c r="GI152" t="s">
+        <v>420</v>
+      </c>
+      <c r="GJ152" t="s">
+        <v>263</v>
+      </c>
+      <c r="GK152" t="s">
+        <v>263</v>
+      </c>
+      <c r="GL152" t="s">
+        <v>263</v>
+      </c>
+      <c r="GM152" t="s">
+        <v>263</v>
+      </c>
+      <c r="GN152" t="s">
+        <v>263</v>
+      </c>
+      <c r="GO152" t="s">
+        <v>263</v>
+      </c>
+      <c r="GP152" t="s">
+        <v>263</v>
+      </c>
+      <c r="GQ152" t="s">
+        <v>263</v>
+      </c>
+      <c r="GR152" t="s">
+        <v>263</v>
+      </c>
+      <c r="GZ152" t="s">
+        <v>1863</v>
+      </c>
+      <c r="HD152">
+        <v>22563146</v>
+      </c>
+      <c r="HE152" t="s">
+        <v>1864</v>
+      </c>
+      <c r="HF152" s="1">
+        <v>46225.02175925926</v>
+      </c>
+      <c r="HI152" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ152" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK152" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM152" t="s">
+        <v>1865</v>
+      </c>
+      <c r="HN152">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="153" spans="1:222">
+      <c r="A153" t="str">
+        <f t="shared" si="4"/>
+        <v>V2-R52</v>
+      </c>
+      <c r="B153">
+        <v>2</v>
+      </c>
+      <c r="C153" s="1">
+        <v>46220.626382685186</v>
+      </c>
+      <c r="D153" s="1">
+        <v>46224.772352893517</v>
+      </c>
+      <c r="E153" s="1">
+        <v>46220</v>
+      </c>
+      <c r="G153" t="s">
+        <v>451</v>
+      </c>
+      <c r="H153" t="s">
+        <v>452</v>
+      </c>
+      <c r="I153" s="1">
+        <v>46220</v>
+      </c>
+      <c r="K153" t="s">
+        <v>1866</v>
+      </c>
+      <c r="L153">
+        <v>27</v>
+      </c>
+      <c r="M153" t="s">
+        <v>271</v>
+      </c>
+      <c r="O153" t="s">
+        <v>348</v>
+      </c>
+      <c r="P153" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>685</v>
+      </c>
+      <c r="R153" t="s">
+        <v>686</v>
+      </c>
+      <c r="S153" t="s">
+        <v>1837</v>
+      </c>
+      <c r="T153" t="s">
+        <v>1867</v>
+      </c>
+      <c r="U153" t="s">
+        <v>1868</v>
+      </c>
+      <c r="V153">
+        <v>13.908832500000001</v>
+      </c>
+      <c r="W153">
+        <v>-88.105222699999999</v>
+      </c>
+      <c r="X153">
+        <v>747.2021484375</v>
+      </c>
+      <c r="Y153">
+        <v>4.1470000000000002</v>
+      </c>
+      <c r="AA153" t="s">
+        <v>1869</v>
+      </c>
+      <c r="AB153" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD153" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG153" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ153" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK153" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL153" t="s">
+        <v>263</v>
+      </c>
+      <c r="AM153" t="s">
+        <v>1870</v>
+      </c>
+      <c r="HC153" t="s">
+        <v>1871</v>
+      </c>
+      <c r="HD153">
+        <v>22563172</v>
+      </c>
+      <c r="HE153" t="s">
+        <v>1872</v>
+      </c>
+      <c r="HF153" s="1">
+        <v>46225.02238425926</v>
+      </c>
+      <c r="HI153" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ153" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK153" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM153" t="s">
+        <v>1873</v>
+      </c>
+      <c r="HN153">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="154" spans="1:222">
+      <c r="A154" t="str">
+        <f t="shared" si="4"/>
+        <v>V2-R53</v>
+      </c>
+      <c r="B154">
+        <v>2</v>
+      </c>
+      <c r="C154" s="1">
+        <v>46221.662219988422</v>
+      </c>
+      <c r="D154" s="1">
+        <v>46222.863325266197</v>
+      </c>
+      <c r="E154" s="1">
+        <v>46221</v>
+      </c>
+      <c r="G154" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H154" t="s">
+        <v>452</v>
+      </c>
+      <c r="I154" s="1">
+        <v>46221</v>
+      </c>
+      <c r="K154" t="s">
+        <v>1874</v>
+      </c>
+      <c r="L154">
+        <v>23</v>
+      </c>
+      <c r="M154" t="s">
+        <v>271</v>
+      </c>
+      <c r="O154" t="s">
+        <v>348</v>
+      </c>
+      <c r="P154" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>455</v>
+      </c>
+      <c r="R154" t="s">
+        <v>473</v>
+      </c>
+      <c r="S154" t="s">
+        <v>1749</v>
+      </c>
+      <c r="T154" t="s">
+        <v>1875</v>
+      </c>
+      <c r="U154" t="s">
+        <v>1876</v>
+      </c>
+      <c r="V154">
+        <v>13.7399161</v>
+      </c>
+      <c r="W154">
+        <v>-88.021491699999999</v>
+      </c>
+      <c r="X154">
+        <v>601.6</v>
+      </c>
+      <c r="Y154">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AA154" t="s">
+        <v>1877</v>
+      </c>
+      <c r="AB154" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD154" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG154" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ154" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK154" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL154" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN154" t="s">
+        <v>1878</v>
+      </c>
+      <c r="AO154" t="s">
+        <v>218</v>
+      </c>
+      <c r="AP154">
+        <v>30</v>
+      </c>
+      <c r="AQ154" t="s">
+        <v>429</v>
+      </c>
+      <c r="AR154" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU154">
+        <v>4</v>
+      </c>
+      <c r="AV154">
+        <v>3</v>
+      </c>
+      <c r="AW154" t="s">
+        <v>1317</v>
+      </c>
+      <c r="AX154">
+        <v>1</v>
+      </c>
+      <c r="AY154">
+        <v>0</v>
+      </c>
+      <c r="AZ154">
+        <v>1</v>
+      </c>
+      <c r="BA154" t="s">
+        <v>431</v>
+      </c>
+      <c r="BB154" t="s">
+        <v>227</v>
+      </c>
+      <c r="BD154" t="s">
+        <v>278</v>
+      </c>
+      <c r="BE154" t="s">
+        <v>229</v>
+      </c>
+      <c r="BF154" t="s">
+        <v>230</v>
+      </c>
+      <c r="BG154" t="s">
+        <v>281</v>
+      </c>
+      <c r="BH154" t="s">
+        <v>232</v>
+      </c>
+      <c r="BI154" t="s">
+        <v>233</v>
+      </c>
+      <c r="BJ154" t="s">
+        <v>283</v>
+      </c>
+      <c r="BK154" t="s">
+        <v>258</v>
+      </c>
+      <c r="BM154" t="s">
+        <v>331</v>
+      </c>
+      <c r="BO154" t="s">
+        <v>530</v>
+      </c>
+      <c r="BP154" t="s">
+        <v>331</v>
+      </c>
+      <c r="BR154" t="s">
+        <v>530</v>
+      </c>
+      <c r="BS154" t="s">
+        <v>226</v>
+      </c>
+      <c r="BT154">
+        <v>30</v>
+      </c>
+      <c r="BU154" t="s">
+        <v>308</v>
+      </c>
+      <c r="BV154" t="s">
+        <v>238</v>
+      </c>
+      <c r="BX154">
+        <v>30</v>
+      </c>
+      <c r="BY154" t="s">
+        <v>239</v>
+      </c>
+      <c r="CA154">
+        <v>14</v>
+      </c>
+      <c r="CB154">
+        <v>1</v>
+      </c>
+      <c r="CC154" t="s">
+        <v>589</v>
+      </c>
+      <c r="CD154">
+        <v>1</v>
+      </c>
+      <c r="CE154">
+        <v>1</v>
+      </c>
+      <c r="CF154">
+        <v>1</v>
+      </c>
+      <c r="CG154">
+        <v>1</v>
+      </c>
+      <c r="CH154">
+        <v>1</v>
+      </c>
+      <c r="CI154">
+        <v>1</v>
+      </c>
+      <c r="CJ154">
+        <v>1</v>
+      </c>
+      <c r="CK154">
+        <v>30</v>
+      </c>
+      <c r="CL154">
+        <v>0</v>
+      </c>
+      <c r="CM154">
+        <v>2500</v>
+      </c>
+      <c r="CN154" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO154" t="s">
+        <v>1277</v>
+      </c>
+      <c r="CP154">
+        <v>1</v>
+      </c>
+      <c r="CQ154">
+        <v>0</v>
+      </c>
+      <c r="CR154">
+        <v>0</v>
+      </c>
+      <c r="CS154">
+        <v>0</v>
+      </c>
+      <c r="CT154">
+        <v>0</v>
+      </c>
+      <c r="CU154">
+        <v>0</v>
+      </c>
+      <c r="CV154">
+        <v>0</v>
+      </c>
+      <c r="CW154">
+        <v>5</v>
+      </c>
+      <c r="CX154" t="s">
+        <v>226</v>
+      </c>
+      <c r="CY154" t="s">
+        <v>243</v>
+      </c>
+      <c r="CZ154">
+        <v>1</v>
+      </c>
+      <c r="DA154">
+        <v>1</v>
+      </c>
+      <c r="DB154">
+        <v>1</v>
+      </c>
+      <c r="DC154">
+        <v>1</v>
+      </c>
+      <c r="DD154" t="s">
+        <v>336</v>
+      </c>
+      <c r="DE154">
+        <v>1</v>
+      </c>
+      <c r="DF154">
+        <v>0</v>
+      </c>
+      <c r="DG154">
+        <v>0</v>
+      </c>
+      <c r="DH154">
+        <v>0</v>
+      </c>
+      <c r="DI154">
+        <v>0</v>
+      </c>
+      <c r="DJ154">
+        <v>0</v>
+      </c>
+      <c r="DK154" t="s">
+        <v>315</v>
+      </c>
+      <c r="DL154" t="s">
+        <v>361</v>
+      </c>
+      <c r="DM154">
+        <v>15</v>
+      </c>
+      <c r="DN154" t="s">
+        <v>392</v>
+      </c>
+      <c r="DO154" t="s">
+        <v>979</v>
+      </c>
+      <c r="DP154">
+        <v>0</v>
+      </c>
+      <c r="DQ154">
+        <v>0</v>
+      </c>
+      <c r="DR154">
+        <v>0</v>
+      </c>
+      <c r="DS154">
+        <v>0</v>
+      </c>
+      <c r="DT154">
+        <v>0</v>
+      </c>
+      <c r="DU154">
+        <v>0</v>
+      </c>
+      <c r="DV154">
+        <v>1</v>
+      </c>
+      <c r="DW154">
+        <v>1</v>
+      </c>
+      <c r="DX154">
+        <v>1</v>
+      </c>
+      <c r="DY154">
+        <v>1</v>
+      </c>
+      <c r="DZ154">
+        <v>0</v>
+      </c>
+      <c r="EA154">
+        <v>0</v>
+      </c>
+      <c r="EB154" t="s">
+        <v>544</v>
+      </c>
+      <c r="EC154" t="s">
+        <v>249</v>
+      </c>
+      <c r="ED154" t="s">
+        <v>253</v>
+      </c>
+      <c r="EE154" t="s">
+        <v>251</v>
+      </c>
+      <c r="EF154">
+        <v>0</v>
+      </c>
+      <c r="EG154">
+        <v>0</v>
+      </c>
+      <c r="EH154">
+        <v>0</v>
+      </c>
+      <c r="EI154">
+        <v>1</v>
+      </c>
+      <c r="EJ154">
+        <v>0</v>
+      </c>
+      <c r="EK154">
+        <v>0</v>
+      </c>
+      <c r="EL154" t="s">
+        <v>1879</v>
+      </c>
+      <c r="EM154">
+        <v>1</v>
+      </c>
+      <c r="EN154">
+        <v>1</v>
+      </c>
+      <c r="EO154">
+        <v>1</v>
+      </c>
+      <c r="EP154">
+        <v>0</v>
+      </c>
+      <c r="EQ154" t="s">
+        <v>253</v>
+      </c>
+      <c r="ER154" t="s">
+        <v>481</v>
+      </c>
+      <c r="ES154" t="s">
+        <v>255</v>
+      </c>
+      <c r="ET154">
+        <v>0</v>
+      </c>
+      <c r="EU154">
+        <v>0</v>
+      </c>
+      <c r="EV154">
+        <v>0</v>
+      </c>
+      <c r="EW154">
+        <v>0</v>
+      </c>
+      <c r="EX154">
+        <v>1</v>
+      </c>
+      <c r="EY154" t="s">
+        <v>256</v>
+      </c>
+      <c r="EZ154" t="s">
+        <v>257</v>
+      </c>
+      <c r="FA154" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB154" t="s">
+        <v>447</v>
+      </c>
+      <c r="FC154" t="s">
+        <v>320</v>
+      </c>
+      <c r="FD154">
+        <v>0</v>
+      </c>
+      <c r="FE154">
+        <v>0</v>
+      </c>
+      <c r="FF154">
+        <v>0</v>
+      </c>
+      <c r="FG154">
+        <v>0</v>
+      </c>
+      <c r="FH154">
+        <v>1</v>
+      </c>
+      <c r="FI154">
+        <v>0</v>
+      </c>
+      <c r="FJ154" t="s">
+        <v>226</v>
+      </c>
+      <c r="FK154" t="s">
+        <v>263</v>
+      </c>
+      <c r="FM154" t="s">
+        <v>342</v>
+      </c>
+      <c r="FN154">
+        <v>1</v>
+      </c>
+      <c r="FO154">
+        <v>1</v>
+      </c>
+      <c r="FP154">
+        <v>1</v>
+      </c>
+      <c r="FQ154">
+        <v>1</v>
+      </c>
+      <c r="FR154">
+        <v>1</v>
+      </c>
+      <c r="FS154">
+        <v>1</v>
+      </c>
+      <c r="FT154" t="s">
+        <v>263</v>
+      </c>
+      <c r="GJ154" t="s">
+        <v>226</v>
+      </c>
+      <c r="GK154" t="s">
+        <v>226</v>
+      </c>
+      <c r="GL154" t="s">
+        <v>226</v>
+      </c>
+      <c r="GM154" t="s">
+        <v>226</v>
+      </c>
+      <c r="GN154" t="s">
+        <v>226</v>
+      </c>
+      <c r="GO154" t="s">
+        <v>226</v>
+      </c>
+      <c r="GP154" t="s">
+        <v>263</v>
+      </c>
+      <c r="GQ154" t="s">
+        <v>263</v>
+      </c>
+      <c r="GR154" t="s">
+        <v>263</v>
+      </c>
+      <c r="GZ154" t="s">
+        <v>1880</v>
+      </c>
+      <c r="HD154">
+        <v>22563790</v>
+      </c>
+      <c r="HE154" t="s">
+        <v>1881</v>
+      </c>
+      <c r="HF154" s="1">
+        <v>46225.071655092594</v>
+      </c>
+      <c r="HI154" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ154" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK154" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM154" t="s">
+        <v>1882</v>
+      </c>
+      <c r="HN154">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="155" spans="1:222">
+      <c r="A155" t="str">
+        <f t="shared" si="4"/>
+        <v>V2-R54</v>
+      </c>
+      <c r="B155">
+        <v>2</v>
+      </c>
+      <c r="C155" s="1">
+        <v>46218.742029814814</v>
+      </c>
+      <c r="D155" s="1">
+        <v>46222.865470416669</v>
+      </c>
+      <c r="E155" s="1">
+        <v>46218</v>
+      </c>
+      <c r="G155" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H155" t="s">
+        <v>452</v>
+      </c>
+      <c r="I155" s="1">
+        <v>46218</v>
+      </c>
+      <c r="K155" t="s">
+        <v>1883</v>
+      </c>
+      <c r="L155">
+        <v>32</v>
+      </c>
+      <c r="M155" t="s">
+        <v>218</v>
+      </c>
+      <c r="O155" t="s">
+        <v>816</v>
+      </c>
+      <c r="P155" t="s">
+        <v>1700</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>816</v>
+      </c>
+      <c r="R155" t="s">
+        <v>1701</v>
+      </c>
+      <c r="S155" t="s">
+        <v>1884</v>
+      </c>
+      <c r="T155" t="s">
+        <v>1885</v>
+      </c>
+      <c r="U155" t="s">
+        <v>1886</v>
+      </c>
+      <c r="V155">
+        <v>13.4767083</v>
+      </c>
+      <c r="W155">
+        <v>-88.100103300000001</v>
+      </c>
+      <c r="X155">
+        <v>144.50001525878909</v>
+      </c>
+      <c r="Y155">
+        <v>2.5329999999999999</v>
+      </c>
+      <c r="AA155" t="s">
+        <v>1887</v>
+      </c>
+      <c r="AB155" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD155" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG155" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ155" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK155" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL155" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN155" t="s">
+        <v>1888</v>
+      </c>
+      <c r="AO155" t="s">
+        <v>271</v>
+      </c>
+      <c r="AP155">
+        <v>52</v>
+      </c>
+      <c r="AQ155" t="s">
+        <v>429</v>
+      </c>
+      <c r="AR155" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU155">
+        <v>4</v>
+      </c>
+      <c r="AV155">
+        <v>1</v>
+      </c>
+      <c r="AW155" t="s">
+        <v>1354</v>
+      </c>
+      <c r="AX155">
+        <v>3</v>
+      </c>
+      <c r="AY155">
+        <v>2</v>
+      </c>
+      <c r="AZ155">
+        <v>2</v>
+      </c>
+      <c r="BA155" t="s">
+        <v>1889</v>
+      </c>
+      <c r="BB155" t="s">
+        <v>306</v>
+      </c>
+      <c r="BD155" t="s">
+        <v>228</v>
+      </c>
+      <c r="BE155" t="s">
+        <v>279</v>
+      </c>
+      <c r="BF155" t="s">
+        <v>230</v>
+      </c>
+      <c r="BG155" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH155" t="s">
+        <v>232</v>
+      </c>
+      <c r="BI155" t="s">
+        <v>233</v>
+      </c>
+      <c r="BJ155" t="s">
+        <v>234</v>
+      </c>
+      <c r="BK155" t="s">
+        <v>258</v>
+      </c>
+      <c r="BM155" t="s">
+        <v>284</v>
+      </c>
+      <c r="BO155" t="s">
+        <v>386</v>
+      </c>
+      <c r="BP155" t="s">
+        <v>284</v>
+      </c>
+      <c r="BR155" t="s">
+        <v>386</v>
+      </c>
+      <c r="BS155" t="s">
+        <v>263</v>
+      </c>
+      <c r="BU155" t="s">
+        <v>387</v>
+      </c>
+      <c r="BV155" t="s">
+        <v>238</v>
+      </c>
+      <c r="BX155">
+        <v>30</v>
+      </c>
+      <c r="BY155" t="s">
+        <v>239</v>
+      </c>
+      <c r="CA155">
+        <v>15</v>
+      </c>
+      <c r="CB155">
+        <v>6</v>
+      </c>
+      <c r="CC155" t="s">
+        <v>1890</v>
+      </c>
+      <c r="CD155">
+        <v>0</v>
+      </c>
+      <c r="CE155">
+        <v>1</v>
+      </c>
+      <c r="CF155">
+        <v>1</v>
+      </c>
+      <c r="CG155">
+        <v>1</v>
+      </c>
+      <c r="CH155">
+        <v>1</v>
+      </c>
+      <c r="CI155">
+        <v>1</v>
+      </c>
+      <c r="CJ155">
+        <v>1</v>
+      </c>
+      <c r="CK155">
+        <v>0</v>
+      </c>
+      <c r="CL155">
+        <v>25</v>
+      </c>
+      <c r="CM155">
+        <v>2000</v>
+      </c>
+      <c r="CN155" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO155" t="s">
+        <v>242</v>
+      </c>
+      <c r="CP155">
+        <v>0</v>
+      </c>
+      <c r="CQ155">
+        <v>0</v>
+      </c>
+      <c r="CR155">
+        <v>0</v>
+      </c>
+      <c r="CS155">
+        <v>0</v>
+      </c>
+      <c r="CT155">
+        <v>0</v>
+      </c>
+      <c r="CU155">
+        <v>0</v>
+      </c>
+      <c r="CV155">
+        <v>1</v>
+      </c>
+      <c r="CW155">
+        <v>0</v>
+      </c>
+      <c r="CX155" t="s">
+        <v>226</v>
+      </c>
+      <c r="CY155" t="s">
+        <v>1891</v>
+      </c>
+      <c r="CZ155">
+        <v>1</v>
+      </c>
+      <c r="DA155">
+        <v>1</v>
+      </c>
+      <c r="DB155">
+        <v>1</v>
+      </c>
+      <c r="DC155">
+        <v>0</v>
+      </c>
+      <c r="DD155" t="s">
+        <v>390</v>
+      </c>
+      <c r="DE155">
+        <v>1</v>
+      </c>
+      <c r="DF155">
+        <v>1</v>
+      </c>
+      <c r="DG155">
+        <v>0</v>
+      </c>
+      <c r="DH155">
+        <v>0</v>
+      </c>
+      <c r="DI155">
+        <v>0</v>
+      </c>
+      <c r="DJ155">
+        <v>0</v>
+      </c>
+      <c r="DK155" t="s">
+        <v>315</v>
+      </c>
+      <c r="DL155" t="s">
+        <v>263</v>
+      </c>
+      <c r="DM155">
+        <v>0</v>
+      </c>
+      <c r="DN155" t="s">
+        <v>247</v>
+      </c>
+      <c r="DO155" t="s">
+        <v>979</v>
+      </c>
+      <c r="DP155">
+        <v>0</v>
+      </c>
+      <c r="DQ155">
+        <v>0</v>
+      </c>
+      <c r="DR155">
+        <v>0</v>
+      </c>
+      <c r="DS155">
+        <v>0</v>
+      </c>
+      <c r="DT155">
+        <v>0</v>
+      </c>
+      <c r="DU155">
+        <v>0</v>
+      </c>
+      <c r="DV155">
+        <v>1</v>
+      </c>
+      <c r="DW155">
+        <v>1</v>
+      </c>
+      <c r="DX155">
+        <v>1</v>
+      </c>
+      <c r="DY155">
+        <v>1</v>
+      </c>
+      <c r="DZ155">
+        <v>0</v>
+      </c>
+      <c r="EA155">
+        <v>0</v>
+      </c>
+      <c r="EB155" t="s">
+        <v>292</v>
+      </c>
+      <c r="EC155" t="s">
+        <v>293</v>
+      </c>
+      <c r="ED155" t="s">
+        <v>376</v>
+      </c>
+      <c r="EL155" t="s">
+        <v>394</v>
+      </c>
+      <c r="EM155">
+        <v>1</v>
+      </c>
+      <c r="EN155">
+        <v>1</v>
+      </c>
+      <c r="EO155">
+        <v>1</v>
+      </c>
+      <c r="EP155">
+        <v>0</v>
+      </c>
+      <c r="EQ155" t="s">
+        <v>253</v>
+      </c>
+      <c r="ER155" t="s">
+        <v>395</v>
+      </c>
+      <c r="ES155" t="s">
+        <v>255</v>
+      </c>
+      <c r="ET155">
+        <v>0</v>
+      </c>
+      <c r="EU155">
+        <v>0</v>
+      </c>
+      <c r="EV155">
+        <v>0</v>
+      </c>
+      <c r="EW155">
+        <v>0</v>
+      </c>
+      <c r="EX155">
+        <v>1</v>
+      </c>
+      <c r="EY155" t="s">
+        <v>256</v>
+      </c>
+      <c r="EZ155" t="s">
+        <v>257</v>
+      </c>
+      <c r="FA155" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB155" t="s">
+        <v>340</v>
+      </c>
+      <c r="FC155" t="s">
+        <v>1646</v>
+      </c>
+      <c r="FD155">
+        <v>1</v>
+      </c>
+      <c r="FE155">
+        <v>0</v>
+      </c>
+      <c r="FF155">
+        <v>0</v>
+      </c>
+      <c r="FG155">
+        <v>0</v>
+      </c>
+      <c r="FH155">
+        <v>1</v>
+      </c>
+      <c r="FI155">
+        <v>0</v>
+      </c>
+      <c r="FJ155" t="s">
+        <v>263</v>
+      </c>
+      <c r="FK155" t="s">
+        <v>226</v>
+      </c>
+      <c r="FM155" t="s">
+        <v>850</v>
+      </c>
+      <c r="FN155">
+        <v>1</v>
+      </c>
+      <c r="FO155">
+        <v>1</v>
+      </c>
+      <c r="FP155">
+        <v>1</v>
+      </c>
+      <c r="FQ155">
+        <v>1</v>
+      </c>
+      <c r="FR155">
+        <v>1</v>
+      </c>
+      <c r="FS155">
+        <v>1</v>
+      </c>
+      <c r="FT155" t="s">
+        <v>226</v>
+      </c>
+      <c r="FU155">
+        <v>1</v>
+      </c>
+      <c r="FV155" t="s">
+        <v>261</v>
+      </c>
+      <c r="FW155">
+        <v>1</v>
+      </c>
+      <c r="FX155">
+        <v>0</v>
+      </c>
+      <c r="FY155">
+        <v>0</v>
+      </c>
+      <c r="FZ155">
+        <v>0</v>
+      </c>
+      <c r="GB155">
+        <v>0.5</v>
+      </c>
+      <c r="GC155" t="s">
+        <v>262</v>
+      </c>
+      <c r="GD155">
+        <v>1</v>
+      </c>
+      <c r="GE155">
+        <v>0</v>
+      </c>
+      <c r="GF155">
+        <v>0</v>
+      </c>
+      <c r="GG155">
+        <v>0</v>
+      </c>
+      <c r="GH155" t="s">
+        <v>816</v>
+      </c>
+      <c r="GI155" t="s">
+        <v>420</v>
+      </c>
+      <c r="GJ155" t="s">
+        <v>226</v>
+      </c>
+      <c r="GK155" t="s">
+        <v>226</v>
+      </c>
+      <c r="GL155" t="s">
+        <v>226</v>
+      </c>
+      <c r="GM155" t="s">
+        <v>226</v>
+      </c>
+      <c r="GN155" t="s">
+        <v>263</v>
+      </c>
+      <c r="GO155" t="s">
+        <v>226</v>
+      </c>
+      <c r="GP155" t="s">
+        <v>263</v>
+      </c>
+      <c r="GQ155" t="s">
+        <v>263</v>
+      </c>
+      <c r="GR155" t="s">
+        <v>226</v>
+      </c>
+      <c r="GS155" t="s">
+        <v>226</v>
+      </c>
+      <c r="GT155" t="s">
+        <v>226</v>
+      </c>
+      <c r="GU155" t="s">
+        <v>263</v>
+      </c>
+      <c r="GV155" t="s">
+        <v>263</v>
+      </c>
+      <c r="GW155" t="s">
+        <v>226</v>
+      </c>
+      <c r="GX155" t="s">
+        <v>263</v>
+      </c>
+      <c r="GY155" t="s">
+        <v>263</v>
+      </c>
+      <c r="GZ155" t="s">
+        <v>1892</v>
+      </c>
+      <c r="HC155" t="s">
+        <v>1893</v>
+      </c>
+      <c r="HD155">
+        <v>22563793</v>
+      </c>
+      <c r="HE155" t="s">
+        <v>1894</v>
+      </c>
+      <c r="HF155" s="1">
+        <v>46225.071655092594</v>
+      </c>
+      <c r="HI155" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ155" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK155" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM155" t="s">
+        <v>1895</v>
+      </c>
+      <c r="HN155">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="156" spans="1:222">
+      <c r="A156" t="str">
+        <f t="shared" si="4"/>
+        <v>V2-R55</v>
+      </c>
+      <c r="B156">
+        <v>2</v>
+      </c>
+      <c r="C156" s="1">
+        <v>46218.757040671298</v>
+      </c>
+      <c r="D156" s="1">
+        <v>46224.820468321763</v>
+      </c>
+      <c r="E156" s="1">
+        <v>46218</v>
+      </c>
+      <c r="G156" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H156" t="s">
+        <v>452</v>
+      </c>
+      <c r="I156" s="1">
+        <v>46218</v>
+      </c>
+      <c r="K156" t="s">
+        <v>1896</v>
+      </c>
+      <c r="L156">
+        <v>36</v>
+      </c>
+      <c r="M156" t="s">
+        <v>218</v>
+      </c>
+      <c r="O156" t="s">
+        <v>816</v>
+      </c>
+      <c r="P156" t="s">
+        <v>1700</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>816</v>
+      </c>
+      <c r="R156" t="s">
+        <v>1701</v>
+      </c>
+      <c r="S156" t="s">
+        <v>1047</v>
+      </c>
+      <c r="T156" t="s">
+        <v>1897</v>
+      </c>
+      <c r="U156" t="s">
+        <v>1898</v>
+      </c>
+      <c r="V156">
+        <v>13.477349999999999</v>
+      </c>
+      <c r="W156">
+        <v>-88.097231699999995</v>
+      </c>
+      <c r="X156">
+        <v>164.00001525878909</v>
+      </c>
+      <c r="Y156">
+        <v>2.4</v>
+      </c>
+      <c r="AA156" t="s">
+        <v>1899</v>
+      </c>
+      <c r="AB156" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD156" t="s">
+        <v>374</v>
+      </c>
+      <c r="AG156" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ156" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK156" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL156" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN156" t="s">
+        <v>1900</v>
+      </c>
+      <c r="AO156" t="s">
+        <v>218</v>
+      </c>
+      <c r="AP156">
+        <v>36</v>
+      </c>
+      <c r="AQ156" t="s">
+        <v>1901</v>
+      </c>
+      <c r="AR156" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU156">
+        <v>2</v>
+      </c>
+      <c r="AV156">
+        <v>1</v>
+      </c>
+      <c r="AW156" t="s">
+        <v>1317</v>
+      </c>
+      <c r="AX156">
+        <v>1</v>
+      </c>
+      <c r="AY156">
+        <v>0</v>
+      </c>
+      <c r="BA156" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BB156" t="s">
+        <v>306</v>
+      </c>
+      <c r="BD156" t="s">
+        <v>404</v>
+      </c>
+      <c r="BE156" t="s">
+        <v>229</v>
+      </c>
+      <c r="BF156" t="s">
+        <v>330</v>
+      </c>
+      <c r="BG156" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH156" t="s">
+        <v>232</v>
+      </c>
+      <c r="BI156" t="s">
+        <v>233</v>
+      </c>
+      <c r="BJ156" t="s">
+        <v>234</v>
+      </c>
+      <c r="BK156" t="s">
+        <v>226</v>
+      </c>
+      <c r="BL156" s="1">
+        <v>44927</v>
+      </c>
+      <c r="BM156" t="s">
+        <v>235</v>
+      </c>
+      <c r="BO156" t="s">
+        <v>236</v>
+      </c>
+      <c r="BP156" t="s">
+        <v>284</v>
+      </c>
+      <c r="BR156" t="s">
+        <v>236</v>
+      </c>
+      <c r="BS156" t="s">
+        <v>226</v>
+      </c>
+      <c r="BT156">
+        <v>15</v>
+      </c>
+      <c r="BU156" t="s">
+        <v>308</v>
+      </c>
+      <c r="BV156" t="s">
+        <v>238</v>
+      </c>
+      <c r="BX156">
+        <v>30</v>
+      </c>
+      <c r="BY156" t="s">
+        <v>239</v>
+      </c>
+      <c r="CA156">
+        <v>7</v>
+      </c>
+      <c r="CB156">
+        <v>4</v>
+      </c>
+      <c r="CC156" t="s">
+        <v>388</v>
+      </c>
+      <c r="CD156">
+        <v>0</v>
+      </c>
+      <c r="CE156">
+        <v>1</v>
+      </c>
+      <c r="CF156">
+        <v>1</v>
+      </c>
+      <c r="CG156">
+        <v>1</v>
+      </c>
+      <c r="CH156">
+        <v>1</v>
+      </c>
+      <c r="CI156">
+        <v>1</v>
+      </c>
+      <c r="CJ156">
+        <v>1</v>
+      </c>
+      <c r="CK156">
+        <v>15</v>
+      </c>
+      <c r="CL156">
+        <v>30</v>
+      </c>
+      <c r="CM156">
+        <v>2500</v>
+      </c>
+      <c r="CN156" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO156" t="s">
+        <v>242</v>
+      </c>
+      <c r="CP156">
+        <v>0</v>
+      </c>
+      <c r="CQ156">
+        <v>0</v>
+      </c>
+      <c r="CR156">
+        <v>0</v>
+      </c>
+      <c r="CS156">
+        <v>0</v>
+      </c>
+      <c r="CT156">
+        <v>0</v>
+      </c>
+      <c r="CU156">
+        <v>0</v>
+      </c>
+      <c r="CV156">
+        <v>1</v>
+      </c>
+      <c r="CW156">
+        <v>0</v>
+      </c>
+      <c r="CX156" t="s">
+        <v>226</v>
+      </c>
+      <c r="CY156" t="s">
+        <v>243</v>
+      </c>
+      <c r="CZ156">
+        <v>1</v>
+      </c>
+      <c r="DA156">
+        <v>1</v>
+      </c>
+      <c r="DB156">
+        <v>1</v>
+      </c>
+      <c r="DC156">
+        <v>1</v>
+      </c>
+      <c r="DD156" t="s">
+        <v>244</v>
+      </c>
+      <c r="DE156">
+        <v>0</v>
+      </c>
+      <c r="DF156">
+        <v>1</v>
+      </c>
+      <c r="DG156">
+        <v>0</v>
+      </c>
+      <c r="DH156">
+        <v>0</v>
+      </c>
+      <c r="DI156">
+        <v>0</v>
+      </c>
+      <c r="DJ156">
+        <v>0</v>
+      </c>
+      <c r="DK156" t="s">
+        <v>289</v>
+      </c>
+      <c r="DL156" t="s">
+        <v>263</v>
+      </c>
+      <c r="DM156">
+        <v>15</v>
+      </c>
+      <c r="DN156" t="s">
+        <v>247</v>
+      </c>
+      <c r="DO156" t="s">
+        <v>581</v>
+      </c>
+      <c r="DP156">
+        <v>0</v>
+      </c>
+      <c r="DQ156">
+        <v>0</v>
+      </c>
+      <c r="DR156">
+        <v>0</v>
+      </c>
+      <c r="DS156">
+        <v>0</v>
+      </c>
+      <c r="DT156">
+        <v>1</v>
+      </c>
+      <c r="DU156">
+        <v>1</v>
+      </c>
+      <c r="DV156">
+        <v>1</v>
+      </c>
+      <c r="DW156">
+        <v>1</v>
+      </c>
+      <c r="DX156">
+        <v>0</v>
+      </c>
+      <c r="DY156">
+        <v>0</v>
+      </c>
+      <c r="DZ156">
+        <v>0</v>
+      </c>
+      <c r="EA156">
+        <v>0</v>
+      </c>
+      <c r="EB156" t="s">
+        <v>544</v>
+      </c>
+      <c r="EC156" t="s">
+        <v>249</v>
+      </c>
+      <c r="ED156" t="s">
+        <v>253</v>
+      </c>
+      <c r="EE156" t="s">
+        <v>363</v>
+      </c>
+      <c r="EF156">
+        <v>1</v>
+      </c>
+      <c r="EG156">
+        <v>0</v>
+      </c>
+      <c r="EH156">
+        <v>0</v>
+      </c>
+      <c r="EI156">
+        <v>0</v>
+      </c>
+      <c r="EJ156">
+        <v>0</v>
+      </c>
+      <c r="EK156">
+        <v>0</v>
+      </c>
+      <c r="EL156" t="s">
+        <v>394</v>
+      </c>
+      <c r="EM156">
+        <v>1</v>
+      </c>
+      <c r="EN156">
+        <v>1</v>
+      </c>
+      <c r="EO156">
+        <v>1</v>
+      </c>
+      <c r="EP156">
+        <v>0</v>
+      </c>
+      <c r="EQ156" t="s">
+        <v>253</v>
+      </c>
+      <c r="ER156" t="s">
+        <v>446</v>
+      </c>
+      <c r="ES156" t="s">
+        <v>255</v>
+      </c>
+      <c r="ET156">
+        <v>0</v>
+      </c>
+      <c r="EU156">
+        <v>0</v>
+      </c>
+      <c r="EV156">
+        <v>0</v>
+      </c>
+      <c r="EW156">
+        <v>0</v>
+      </c>
+      <c r="EX156">
+        <v>1</v>
+      </c>
+      <c r="EY156" t="s">
+        <v>256</v>
+      </c>
+      <c r="EZ156" t="s">
+        <v>257</v>
+      </c>
+      <c r="FA156" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB156" t="s">
+        <v>340</v>
+      </c>
+      <c r="FC156" t="s">
+        <v>378</v>
+      </c>
+      <c r="FD156">
+        <v>0</v>
+      </c>
+      <c r="FE156">
+        <v>0</v>
+      </c>
+      <c r="FF156">
+        <v>0</v>
+      </c>
+      <c r="FG156">
+        <v>1</v>
+      </c>
+      <c r="FH156">
+        <v>0</v>
+      </c>
+      <c r="FI156">
+        <v>0</v>
+      </c>
+      <c r="FJ156" t="s">
+        <v>226</v>
+      </c>
+      <c r="FK156" t="s">
+        <v>226</v>
+      </c>
+      <c r="FM156" t="s">
+        <v>297</v>
+      </c>
+      <c r="FN156">
+        <v>1</v>
+      </c>
+      <c r="FO156">
+        <v>1</v>
+      </c>
+      <c r="FP156">
+        <v>1</v>
+      </c>
+      <c r="FQ156">
+        <v>1</v>
+      </c>
+      <c r="FR156">
+        <v>1</v>
+      </c>
+      <c r="FS156">
+        <v>0</v>
+      </c>
+      <c r="FT156" t="s">
+        <v>226</v>
+      </c>
+      <c r="FU156">
+        <v>4</v>
+      </c>
+      <c r="FV156" t="s">
+        <v>1902</v>
+      </c>
+      <c r="FW156">
+        <v>1</v>
+      </c>
+      <c r="FX156">
+        <v>1</v>
+      </c>
+      <c r="FY156">
+        <v>1</v>
+      </c>
+      <c r="FZ156">
+        <v>0</v>
+      </c>
+      <c r="GB156">
+        <v>2</v>
+      </c>
+      <c r="GC156" t="s">
+        <v>262</v>
+      </c>
+      <c r="GD156">
+        <v>1</v>
+      </c>
+      <c r="GE156">
+        <v>0</v>
+      </c>
+      <c r="GF156">
+        <v>0</v>
+      </c>
+      <c r="GG156">
+        <v>0</v>
+      </c>
+      <c r="GI156" t="s">
+        <v>420</v>
+      </c>
+      <c r="GJ156" t="s">
+        <v>226</v>
+      </c>
+      <c r="GK156" t="s">
+        <v>263</v>
+      </c>
+      <c r="GL156" t="s">
+        <v>263</v>
+      </c>
+      <c r="GM156" t="s">
+        <v>226</v>
+      </c>
+      <c r="GN156" t="s">
+        <v>263</v>
+      </c>
+      <c r="GO156" t="s">
+        <v>226</v>
+      </c>
+      <c r="GP156" t="s">
+        <v>263</v>
+      </c>
+      <c r="GQ156" t="s">
+        <v>263</v>
+      </c>
+      <c r="GR156" t="s">
+        <v>226</v>
+      </c>
+      <c r="GS156" t="s">
+        <v>263</v>
+      </c>
+      <c r="GT156" t="s">
+        <v>226</v>
+      </c>
+      <c r="GU156" t="s">
+        <v>263</v>
+      </c>
+      <c r="GV156" t="s">
+        <v>263</v>
+      </c>
+      <c r="GW156" t="s">
+        <v>226</v>
+      </c>
+      <c r="GX156" t="s">
+        <v>263</v>
+      </c>
+      <c r="GY156" t="s">
+        <v>263</v>
+      </c>
+      <c r="GZ156" t="s">
+        <v>1903</v>
+      </c>
+      <c r="HD156">
+        <v>22563801</v>
+      </c>
+      <c r="HE156" t="s">
+        <v>1904</v>
+      </c>
+      <c r="HF156" s="1">
+        <v>46225.07167824074</v>
+      </c>
+      <c r="HI156" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ156" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK156" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM156" t="s">
+        <v>1905</v>
+      </c>
+      <c r="HN156">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="157" spans="1:222">
+      <c r="A157" t="str">
+        <f t="shared" si="4"/>
+        <v>V2-R56</v>
+      </c>
+      <c r="B157">
+        <v>2</v>
+      </c>
+      <c r="C157" s="1">
+        <v>46220.586617905094</v>
+      </c>
+      <c r="D157" s="1">
+        <v>46224.820978900461</v>
+      </c>
+      <c r="E157" s="1">
+        <v>46220</v>
+      </c>
+      <c r="G157" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H157" t="s">
+        <v>452</v>
+      </c>
+      <c r="I157" s="1">
+        <v>46220</v>
+      </c>
+      <c r="K157" t="s">
+        <v>1906</v>
+      </c>
+      <c r="L157">
+        <v>50</v>
+      </c>
+      <c r="M157" t="s">
+        <v>271</v>
+      </c>
+      <c r="O157" t="s">
+        <v>348</v>
+      </c>
+      <c r="P157" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>685</v>
+      </c>
+      <c r="R157" t="s">
+        <v>686</v>
+      </c>
+      <c r="S157" t="s">
+        <v>1720</v>
+      </c>
+      <c r="T157" t="s">
+        <v>1907</v>
+      </c>
+      <c r="U157" t="s">
+        <v>1908</v>
+      </c>
+      <c r="V157">
+        <v>13.9095707</v>
+      </c>
+      <c r="W157">
+        <v>-88.106511100000006</v>
+      </c>
+      <c r="X157">
+        <v>857.29998779296875</v>
+      </c>
+      <c r="Y157">
+        <v>4.46</v>
+      </c>
+      <c r="AA157" t="s">
+        <v>1909</v>
+      </c>
+      <c r="AB157" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD157" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG157" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ157" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK157" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL157" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN157" t="s">
+        <v>1910</v>
+      </c>
+      <c r="AO157" t="s">
+        <v>271</v>
+      </c>
+      <c r="AP157">
+        <v>50</v>
+      </c>
+      <c r="AQ157" t="s">
+        <v>429</v>
+      </c>
+      <c r="AR157" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU157">
+        <v>5</v>
+      </c>
+      <c r="AV157">
+        <v>2</v>
+      </c>
+      <c r="AW157" t="s">
+        <v>1354</v>
+      </c>
+      <c r="AX157">
+        <v>3</v>
+      </c>
+      <c r="AY157">
+        <v>2</v>
+      </c>
+      <c r="AZ157">
+        <v>3</v>
+      </c>
+      <c r="BA157" t="s">
+        <v>1404</v>
+      </c>
+      <c r="BB157" t="s">
+        <v>306</v>
+      </c>
+      <c r="BD157" t="s">
+        <v>404</v>
+      </c>
+      <c r="BE157" t="s">
+        <v>229</v>
+      </c>
+      <c r="BF157" t="s">
+        <v>280</v>
+      </c>
+      <c r="BG157" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH157" t="s">
+        <v>232</v>
+      </c>
+      <c r="BI157" t="s">
+        <v>233</v>
+      </c>
+      <c r="BJ157" t="s">
+        <v>234</v>
+      </c>
+      <c r="BK157" t="s">
+        <v>226</v>
+      </c>
+      <c r="BL157" s="1">
+        <v>44927</v>
+      </c>
+      <c r="BM157" t="s">
+        <v>331</v>
+      </c>
+      <c r="BO157" t="s">
+        <v>236</v>
+      </c>
+      <c r="BP157" t="s">
+        <v>331</v>
+      </c>
+      <c r="BR157" t="s">
+        <v>236</v>
+      </c>
+      <c r="BS157" t="s">
+        <v>226</v>
+      </c>
+      <c r="BT157">
+        <v>20</v>
+      </c>
+      <c r="BU157" t="s">
+        <v>308</v>
+      </c>
+      <c r="BV157" t="s">
+        <v>238</v>
+      </c>
+      <c r="BX157">
+        <v>30</v>
+      </c>
+      <c r="BY157" t="s">
+        <v>239</v>
+      </c>
+      <c r="CA157">
+        <v>14</v>
+      </c>
+      <c r="CB157">
+        <v>6</v>
+      </c>
+      <c r="CC157" t="s">
+        <v>462</v>
+      </c>
+      <c r="CD157">
+        <v>0</v>
+      </c>
+      <c r="CE157">
+        <v>1</v>
+      </c>
+      <c r="CF157">
+        <v>1</v>
+      </c>
+      <c r="CG157">
+        <v>1</v>
+      </c>
+      <c r="CH157">
+        <v>1</v>
+      </c>
+      <c r="CI157">
+        <v>1</v>
+      </c>
+      <c r="CJ157">
+        <v>1</v>
+      </c>
+      <c r="CK157">
+        <v>0</v>
+      </c>
+      <c r="CL157">
+        <v>0</v>
+      </c>
+      <c r="CM157">
+        <v>2500</v>
+      </c>
+      <c r="CN157" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO157" t="s">
+        <v>242</v>
+      </c>
+      <c r="CP157">
+        <v>0</v>
+      </c>
+      <c r="CQ157">
+        <v>0</v>
+      </c>
+      <c r="CR157">
+        <v>0</v>
+      </c>
+      <c r="CS157">
+        <v>0</v>
+      </c>
+      <c r="CT157">
+        <v>0</v>
+      </c>
+      <c r="CU157">
+        <v>0</v>
+      </c>
+      <c r="CV157">
+        <v>1</v>
+      </c>
+      <c r="CW157">
+        <v>0</v>
+      </c>
+      <c r="CX157" t="s">
+        <v>226</v>
+      </c>
+      <c r="CY157" t="s">
+        <v>798</v>
+      </c>
+      <c r="CZ157">
+        <v>1</v>
+      </c>
+      <c r="DA157">
+        <v>1</v>
+      </c>
+      <c r="DB157">
+        <v>1</v>
+      </c>
+      <c r="DC157">
+        <v>1</v>
+      </c>
+      <c r="DD157" t="s">
+        <v>336</v>
+      </c>
+      <c r="DE157">
+        <v>1</v>
+      </c>
+      <c r="DF157">
+        <v>0</v>
+      </c>
+      <c r="DG157">
+        <v>0</v>
+      </c>
+      <c r="DH157">
+        <v>0</v>
+      </c>
+      <c r="DI157">
+        <v>0</v>
+      </c>
+      <c r="DJ157">
+        <v>0</v>
+      </c>
+      <c r="DK157" t="s">
+        <v>289</v>
+      </c>
+      <c r="DL157" t="s">
+        <v>263</v>
+      </c>
+      <c r="DM157">
+        <v>3</v>
+      </c>
+      <c r="DN157" t="s">
+        <v>316</v>
+      </c>
+      <c r="DO157" t="s">
+        <v>1536</v>
+      </c>
+      <c r="DP157">
+        <v>0</v>
+      </c>
+      <c r="DQ157">
+        <v>0</v>
+      </c>
+      <c r="DR157">
+        <v>0</v>
+      </c>
+      <c r="DS157">
+        <v>0</v>
+      </c>
+      <c r="DT157">
+        <v>0</v>
+      </c>
+      <c r="DU157">
+        <v>0</v>
+      </c>
+      <c r="DV157">
+        <v>0</v>
+      </c>
+      <c r="DW157">
+        <v>1</v>
+      </c>
+      <c r="DX157">
+        <v>1</v>
+      </c>
+      <c r="DY157">
+        <v>0</v>
+      </c>
+      <c r="DZ157">
+        <v>0</v>
+      </c>
+      <c r="EA157">
+        <v>0</v>
+      </c>
+      <c r="EB157" t="s">
+        <v>245</v>
+      </c>
+      <c r="EC157" t="s">
+        <v>249</v>
+      </c>
+      <c r="ED157" t="s">
+        <v>253</v>
+      </c>
+      <c r="EE157" t="s">
+        <v>251</v>
+      </c>
+      <c r="EF157">
+        <v>0</v>
+      </c>
+      <c r="EG157">
+        <v>0</v>
+      </c>
+      <c r="EH157">
+        <v>0</v>
+      </c>
+      <c r="EI157">
+        <v>1</v>
+      </c>
+      <c r="EJ157">
+        <v>0</v>
+      </c>
+      <c r="EK157">
+        <v>0</v>
+      </c>
+      <c r="EL157" t="s">
+        <v>394</v>
+      </c>
+      <c r="EM157">
+        <v>1</v>
+      </c>
+      <c r="EN157">
+        <v>1</v>
+      </c>
+      <c r="EO157">
+        <v>1</v>
+      </c>
+      <c r="EP157">
+        <v>0</v>
+      </c>
+      <c r="EQ157" t="s">
+        <v>253</v>
+      </c>
+      <c r="ER157" t="s">
+        <v>294</v>
+      </c>
+      <c r="ES157" t="s">
+        <v>255</v>
+      </c>
+      <c r="ET157">
+        <v>0</v>
+      </c>
+      <c r="EU157">
+        <v>0</v>
+      </c>
+      <c r="EV157">
+        <v>0</v>
+      </c>
+      <c r="EW157">
+        <v>0</v>
+      </c>
+      <c r="EX157">
+        <v>1</v>
+      </c>
+      <c r="EY157" t="s">
+        <v>256</v>
+      </c>
+      <c r="EZ157" t="s">
+        <v>257</v>
+      </c>
+      <c r="FA157" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB157" t="s">
+        <v>340</v>
+      </c>
+      <c r="FC157" t="s">
+        <v>366</v>
+      </c>
+      <c r="FD157">
+        <v>0</v>
+      </c>
+      <c r="FE157">
+        <v>1</v>
+      </c>
+      <c r="FF157">
+        <v>0</v>
+      </c>
+      <c r="FG157">
+        <v>0</v>
+      </c>
+      <c r="FH157">
+        <v>0</v>
+      </c>
+      <c r="FI157">
+        <v>0</v>
+      </c>
+      <c r="FJ157" t="s">
+        <v>226</v>
+      </c>
+      <c r="FK157" t="s">
+        <v>226</v>
+      </c>
+      <c r="FM157" t="s">
+        <v>297</v>
+      </c>
+      <c r="FN157">
+        <v>1</v>
+      </c>
+      <c r="FO157">
+        <v>1</v>
+      </c>
+      <c r="FP157">
+        <v>1</v>
+      </c>
+      <c r="FQ157">
+        <v>1</v>
+      </c>
+      <c r="FR157">
+        <v>1</v>
+      </c>
+      <c r="FS157">
+        <v>0</v>
+      </c>
+      <c r="FT157" t="s">
+        <v>226</v>
+      </c>
+      <c r="FU157">
+        <v>1</v>
+      </c>
+      <c r="FV157" t="s">
+        <v>1902</v>
+      </c>
+      <c r="FW157">
+        <v>1</v>
+      </c>
+      <c r="FX157">
+        <v>1</v>
+      </c>
+      <c r="FY157">
+        <v>1</v>
+      </c>
+      <c r="FZ157">
+        <v>0</v>
+      </c>
+      <c r="GB157">
+        <v>0.5</v>
+      </c>
+      <c r="GC157" t="s">
+        <v>262</v>
+      </c>
+      <c r="GD157">
+        <v>1</v>
+      </c>
+      <c r="GE157">
+        <v>0</v>
+      </c>
+      <c r="GF157">
+        <v>0</v>
+      </c>
+      <c r="GG157">
+        <v>0</v>
+      </c>
+      <c r="GH157" t="s">
+        <v>685</v>
+      </c>
+      <c r="GI157" t="s">
+        <v>666</v>
+      </c>
+      <c r="GJ157" t="s">
+        <v>226</v>
+      </c>
+      <c r="GK157" t="s">
+        <v>263</v>
+      </c>
+      <c r="GL157" t="s">
+        <v>263</v>
+      </c>
+      <c r="GM157" t="s">
+        <v>263</v>
+      </c>
+      <c r="GN157" t="s">
+        <v>263</v>
+      </c>
+      <c r="GO157" t="s">
+        <v>226</v>
+      </c>
+      <c r="GP157" t="s">
+        <v>263</v>
+      </c>
+      <c r="GQ157" t="s">
+        <v>263</v>
+      </c>
+      <c r="GR157" t="s">
+        <v>226</v>
+      </c>
+      <c r="GS157" t="s">
+        <v>263</v>
+      </c>
+      <c r="GT157" t="s">
+        <v>263</v>
+      </c>
+      <c r="GU157" t="s">
+        <v>263</v>
+      </c>
+      <c r="GV157" t="s">
+        <v>263</v>
+      </c>
+      <c r="GW157" t="s">
+        <v>263</v>
+      </c>
+      <c r="GX157" t="s">
+        <v>263</v>
+      </c>
+      <c r="GY157" t="s">
+        <v>263</v>
+      </c>
+      <c r="GZ157" t="s">
+        <v>1911</v>
+      </c>
+      <c r="HD157">
+        <v>22563803</v>
+      </c>
+      <c r="HE157" t="s">
+        <v>1912</v>
+      </c>
+      <c r="HF157" s="1">
+        <v>46225.071689814817</v>
+      </c>
+      <c r="HI157" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ157" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK157" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM157" t="s">
+        <v>1913</v>
+      </c>
+      <c r="HN157">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="158" spans="1:222">
+      <c r="A158" t="str">
+        <f t="shared" si="4"/>
+        <v>V2-R57</v>
+      </c>
+      <c r="B158">
+        <v>2</v>
+      </c>
+      <c r="C158" s="1">
+        <v>46220.601448530091</v>
+      </c>
+      <c r="D158" s="1">
+        <v>46224.821451261567</v>
+      </c>
+      <c r="E158" s="1">
+        <v>46220</v>
+      </c>
+      <c r="G158" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H158" t="s">
+        <v>452</v>
+      </c>
+      <c r="I158" s="1">
+        <v>46220</v>
+      </c>
+      <c r="K158" t="s">
+        <v>1914</v>
+      </c>
+      <c r="L158">
+        <v>29</v>
+      </c>
+      <c r="M158" t="s">
+        <v>271</v>
+      </c>
+      <c r="O158" t="s">
+        <v>348</v>
+      </c>
+      <c r="P158" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>685</v>
+      </c>
+      <c r="R158" t="s">
+        <v>686</v>
+      </c>
+      <c r="S158" t="s">
+        <v>1720</v>
+      </c>
+      <c r="T158" t="s">
+        <v>1915</v>
+      </c>
+      <c r="U158" t="s">
+        <v>1916</v>
+      </c>
+      <c r="V158">
+        <v>13.908792</v>
+      </c>
+      <c r="W158">
+        <v>-88.105747500000007</v>
+      </c>
+      <c r="X158">
+        <v>857.29998779296875</v>
+      </c>
+      <c r="Y158">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AA158" t="s">
+        <v>1917</v>
+      </c>
+      <c r="AB158" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD158" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG158" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ158" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK158" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL158" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN158" t="s">
+        <v>1918</v>
+      </c>
+      <c r="AO158" t="s">
+        <v>271</v>
+      </c>
+      <c r="AP158">
+        <v>29</v>
+      </c>
+      <c r="AQ158" t="s">
+        <v>1343</v>
+      </c>
+      <c r="AR158" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU158">
+        <v>4</v>
+      </c>
+      <c r="AV158">
+        <v>1</v>
+      </c>
+      <c r="AW158" t="s">
+        <v>1354</v>
+      </c>
+      <c r="AX158">
+        <v>3</v>
+      </c>
+      <c r="AY158">
+        <v>2</v>
+      </c>
+      <c r="AZ158">
+        <v>1</v>
+      </c>
+      <c r="BA158" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BB158" t="s">
+        <v>306</v>
+      </c>
+      <c r="BD158" t="s">
+        <v>404</v>
+      </c>
+      <c r="BE158" t="s">
+        <v>229</v>
+      </c>
+      <c r="BF158" t="s">
+        <v>280</v>
+      </c>
+      <c r="BG158" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH158" t="s">
+        <v>232</v>
+      </c>
+      <c r="BI158" t="s">
+        <v>233</v>
+      </c>
+      <c r="BJ158" t="s">
+        <v>234</v>
+      </c>
+      <c r="BK158" t="s">
+        <v>226</v>
+      </c>
+      <c r="BL158" s="1">
+        <v>44927</v>
+      </c>
+      <c r="BM158" t="s">
+        <v>331</v>
+      </c>
+      <c r="BO158" t="s">
+        <v>236</v>
+      </c>
+      <c r="BP158" t="s">
+        <v>331</v>
+      </c>
+      <c r="BR158" t="s">
+        <v>236</v>
+      </c>
+      <c r="BS158" t="s">
+        <v>226</v>
+      </c>
+      <c r="BT158">
+        <v>15</v>
+      </c>
+      <c r="BU158" t="s">
+        <v>308</v>
+      </c>
+      <c r="BV158" t="s">
+        <v>238</v>
+      </c>
+      <c r="BX158">
+        <v>30</v>
+      </c>
+      <c r="BY158" t="s">
+        <v>239</v>
+      </c>
+      <c r="CA158">
+        <v>21</v>
+      </c>
+      <c r="CB158">
+        <v>6</v>
+      </c>
+      <c r="CC158" t="s">
+        <v>1919</v>
+      </c>
+      <c r="CD158">
+        <v>1</v>
+      </c>
+      <c r="CE158">
+        <v>1</v>
+      </c>
+      <c r="CF158">
+        <v>1</v>
+      </c>
+      <c r="CG158">
+        <v>1</v>
+      </c>
+      <c r="CH158">
+        <v>1</v>
+      </c>
+      <c r="CI158">
+        <v>1</v>
+      </c>
+      <c r="CJ158">
+        <v>1</v>
+      </c>
+      <c r="CK158">
+        <v>0</v>
+      </c>
+      <c r="CL158">
+        <v>0</v>
+      </c>
+      <c r="CM158">
+        <v>2500</v>
+      </c>
+      <c r="CN158" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO158" t="s">
+        <v>242</v>
+      </c>
+      <c r="CP158">
+        <v>0</v>
+      </c>
+      <c r="CQ158">
+        <v>0</v>
+      </c>
+      <c r="CR158">
+        <v>0</v>
+      </c>
+      <c r="CS158">
+        <v>0</v>
+      </c>
+      <c r="CT158">
+        <v>0</v>
+      </c>
+      <c r="CU158">
+        <v>0</v>
+      </c>
+      <c r="CV158">
+        <v>1</v>
+      </c>
+      <c r="CW158">
+        <v>0</v>
+      </c>
+      <c r="CX158" t="s">
+        <v>226</v>
+      </c>
+      <c r="CY158" t="s">
+        <v>243</v>
+      </c>
+      <c r="CZ158">
+        <v>1</v>
+      </c>
+      <c r="DA158">
+        <v>1</v>
+      </c>
+      <c r="DB158">
+        <v>1</v>
+      </c>
+      <c r="DC158">
+        <v>1</v>
+      </c>
+      <c r="DD158" t="s">
+        <v>244</v>
+      </c>
+      <c r="DE158">
+        <v>0</v>
+      </c>
+      <c r="DF158">
+        <v>1</v>
+      </c>
+      <c r="DG158">
+        <v>0</v>
+      </c>
+      <c r="DH158">
+        <v>0</v>
+      </c>
+      <c r="DI158">
+        <v>0</v>
+      </c>
+      <c r="DJ158">
+        <v>0</v>
+      </c>
+      <c r="DK158" t="s">
+        <v>289</v>
+      </c>
+      <c r="DL158" t="s">
+        <v>263</v>
+      </c>
+      <c r="DM158">
+        <v>40</v>
+      </c>
+      <c r="DN158" t="s">
+        <v>247</v>
+      </c>
+      <c r="DO158" t="s">
+        <v>1920</v>
+      </c>
+      <c r="DP158">
+        <v>0</v>
+      </c>
+      <c r="DQ158">
+        <v>0</v>
+      </c>
+      <c r="DR158">
+        <v>0</v>
+      </c>
+      <c r="DS158">
+        <v>0</v>
+      </c>
+      <c r="DT158">
+        <v>0</v>
+      </c>
+      <c r="DU158">
+        <v>0</v>
+      </c>
+      <c r="DV158">
+        <v>0</v>
+      </c>
+      <c r="DW158">
+        <v>1</v>
+      </c>
+      <c r="DX158">
+        <v>1</v>
+      </c>
+      <c r="DY158">
+        <v>1</v>
+      </c>
+      <c r="DZ158">
+        <v>1</v>
+      </c>
+      <c r="EA158">
+        <v>0</v>
+      </c>
+      <c r="EB158" t="s">
+        <v>245</v>
+      </c>
+      <c r="EC158" t="s">
+        <v>293</v>
+      </c>
+      <c r="ED158" t="s">
+        <v>253</v>
+      </c>
+      <c r="EE158" t="s">
+        <v>318</v>
+      </c>
+      <c r="EF158">
+        <v>1</v>
+      </c>
+      <c r="EG158">
+        <v>0</v>
+      </c>
+      <c r="EH158">
+        <v>0</v>
+      </c>
+      <c r="EI158">
+        <v>1</v>
+      </c>
+      <c r="EJ158">
+        <v>0</v>
+      </c>
+      <c r="EK158">
+        <v>0</v>
+      </c>
+      <c r="EL158" t="s">
+        <v>394</v>
+      </c>
+      <c r="EM158">
+        <v>1</v>
+      </c>
+      <c r="EN158">
+        <v>1</v>
+      </c>
+      <c r="EO158">
+        <v>1</v>
+      </c>
+      <c r="EP158">
+        <v>0</v>
+      </c>
+      <c r="EQ158" t="s">
+        <v>253</v>
+      </c>
+      <c r="ER158" t="s">
+        <v>338</v>
+      </c>
+      <c r="ES158" t="s">
+        <v>255</v>
+      </c>
+      <c r="ET158">
+        <v>0</v>
+      </c>
+      <c r="EU158">
+        <v>0</v>
+      </c>
+      <c r="EV158">
+        <v>0</v>
+      </c>
+      <c r="EW158">
+        <v>0</v>
+      </c>
+      <c r="EX158">
+        <v>1</v>
+      </c>
+      <c r="EY158" t="s">
+        <v>256</v>
+      </c>
+      <c r="EZ158" t="s">
+        <v>257</v>
+      </c>
+      <c r="FA158" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB158" t="s">
+        <v>340</v>
+      </c>
+      <c r="FC158" t="s">
+        <v>366</v>
+      </c>
+      <c r="FD158">
+        <v>0</v>
+      </c>
+      <c r="FE158">
+        <v>1</v>
+      </c>
+      <c r="FF158">
+        <v>0</v>
+      </c>
+      <c r="FG158">
+        <v>0</v>
+      </c>
+      <c r="FH158">
+        <v>0</v>
+      </c>
+      <c r="FI158">
+        <v>0</v>
+      </c>
+      <c r="FJ158" t="s">
+        <v>226</v>
+      </c>
+      <c r="FK158" t="s">
+        <v>226</v>
+      </c>
+      <c r="FM158" t="s">
+        <v>342</v>
+      </c>
+      <c r="FN158">
+        <v>1</v>
+      </c>
+      <c r="FO158">
+        <v>1</v>
+      </c>
+      <c r="FP158">
+        <v>1</v>
+      </c>
+      <c r="FQ158">
+        <v>1</v>
+      </c>
+      <c r="FR158">
+        <v>1</v>
+      </c>
+      <c r="FS158">
+        <v>1</v>
+      </c>
+      <c r="FT158" t="s">
+        <v>226</v>
+      </c>
+      <c r="FU158">
+        <v>1</v>
+      </c>
+      <c r="FV158" t="s">
+        <v>1148</v>
+      </c>
+      <c r="FW158">
+        <v>1</v>
+      </c>
+      <c r="FX158">
+        <v>0</v>
+      </c>
+      <c r="FY158">
+        <v>1</v>
+      </c>
+      <c r="FZ158">
+        <v>0</v>
+      </c>
+      <c r="GB158">
+        <v>3</v>
+      </c>
+      <c r="GC158" t="s">
+        <v>560</v>
+      </c>
+      <c r="GD158">
+        <v>0</v>
+      </c>
+      <c r="GE158">
+        <v>1</v>
+      </c>
+      <c r="GF158">
+        <v>0</v>
+      </c>
+      <c r="GG158">
+        <v>0</v>
+      </c>
+      <c r="GH158" t="s">
+        <v>685</v>
+      </c>
+      <c r="GI158" t="s">
+        <v>666</v>
+      </c>
+      <c r="GJ158" t="s">
+        <v>263</v>
+      </c>
+      <c r="GK158" t="s">
+        <v>263</v>
+      </c>
+      <c r="GL158" t="s">
+        <v>263</v>
+      </c>
+      <c r="GM158" t="s">
+        <v>263</v>
+      </c>
+      <c r="GN158" t="s">
+        <v>263</v>
+      </c>
+      <c r="GO158" t="s">
+        <v>263</v>
+      </c>
+      <c r="GP158" t="s">
+        <v>263</v>
+      </c>
+      <c r="GQ158" t="s">
+        <v>263</v>
+      </c>
+      <c r="GR158" t="s">
+        <v>226</v>
+      </c>
+      <c r="GS158" t="s">
+        <v>263</v>
+      </c>
+      <c r="GT158" t="s">
+        <v>263</v>
+      </c>
+      <c r="GU158" t="s">
+        <v>263</v>
+      </c>
+      <c r="GV158" t="s">
+        <v>263</v>
+      </c>
+      <c r="GW158" t="s">
+        <v>263</v>
+      </c>
+      <c r="GX158" t="s">
+        <v>263</v>
+      </c>
+      <c r="GY158" t="s">
+        <v>263</v>
+      </c>
+      <c r="GZ158" t="s">
+        <v>1921</v>
+      </c>
+      <c r="HD158">
+        <v>22563804</v>
+      </c>
+      <c r="HE158" t="s">
+        <v>1922</v>
+      </c>
+      <c r="HF158" s="1">
+        <v>46225.071689814817</v>
+      </c>
+      <c r="HI158" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ158" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK158" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM158" t="s">
+        <v>1923</v>
+      </c>
+      <c r="HN158">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="159" spans="1:222">
+      <c r="A159" t="str">
+        <f t="shared" si="4"/>
+        <v>V2-R58</v>
+      </c>
+      <c r="B159">
+        <v>2</v>
+      </c>
+      <c r="C159" s="1">
+        <v>46218.689767141201</v>
+      </c>
+      <c r="D159" s="1">
+        <v>46225.424357314812</v>
+      </c>
+      <c r="E159" s="1">
+        <v>46218</v>
+      </c>
+      <c r="G159" t="s">
+        <v>1924</v>
+      </c>
+      <c r="H159" t="s">
+        <v>452</v>
+      </c>
+      <c r="I159" s="1">
+        <v>46218</v>
+      </c>
+      <c r="K159" t="s">
+        <v>1925</v>
+      </c>
+      <c r="L159">
+        <v>55</v>
+      </c>
+      <c r="M159" t="s">
+        <v>271</v>
+      </c>
+      <c r="O159" t="s">
+        <v>816</v>
+      </c>
+      <c r="P159" t="s">
+        <v>1700</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>816</v>
+      </c>
+      <c r="R159" t="s">
+        <v>1701</v>
+      </c>
+      <c r="S159" t="s">
+        <v>1702</v>
+      </c>
+      <c r="T159" t="s">
+        <v>1926</v>
+      </c>
+      <c r="U159" t="s">
+        <v>1927</v>
+      </c>
+      <c r="V159">
+        <v>13.469526200000001</v>
+      </c>
+      <c r="W159">
+        <v>-88.126300200000003</v>
+      </c>
+      <c r="X159">
+        <v>111.1999969482422</v>
+      </c>
+      <c r="Y159">
+        <v>4.8479999999999999</v>
+      </c>
+      <c r="AA159" t="s">
+        <v>674</v>
+      </c>
+      <c r="AB159" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD159" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG159" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ159" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK159" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL159" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN159" t="s">
+        <v>674</v>
+      </c>
+      <c r="AO159" t="s">
+        <v>271</v>
+      </c>
+      <c r="AP159">
+        <v>55</v>
+      </c>
+      <c r="AQ159" t="s">
+        <v>429</v>
+      </c>
+      <c r="AR159" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU159">
+        <v>3</v>
+      </c>
+      <c r="AV159">
+        <v>1</v>
+      </c>
+      <c r="AW159" t="s">
+        <v>430</v>
+      </c>
+      <c r="AY159">
+        <v>0</v>
+      </c>
+      <c r="AZ159">
+        <v>0</v>
+      </c>
+      <c r="BA159" t="s">
+        <v>1404</v>
+      </c>
+      <c r="BB159" t="s">
+        <v>306</v>
+      </c>
+      <c r="BD159" t="s">
+        <v>404</v>
+      </c>
+      <c r="BE159" t="s">
+        <v>279</v>
+      </c>
+      <c r="BF159" t="s">
+        <v>280</v>
+      </c>
+      <c r="BG159" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH159" t="s">
+        <v>232</v>
+      </c>
+      <c r="BI159" t="s">
+        <v>233</v>
+      </c>
+      <c r="BJ159" t="s">
+        <v>1928</v>
+      </c>
+      <c r="BK159" t="s">
+        <v>226</v>
+      </c>
+      <c r="BL159" s="1">
+        <v>44927</v>
+      </c>
+      <c r="BM159" t="s">
+        <v>235</v>
+      </c>
+      <c r="BO159" t="s">
+        <v>236</v>
+      </c>
+      <c r="BP159" t="s">
+        <v>235</v>
+      </c>
+      <c r="BR159" t="s">
+        <v>236</v>
+      </c>
+      <c r="BS159" t="s">
+        <v>226</v>
+      </c>
+      <c r="BT159">
+        <v>10</v>
+      </c>
+      <c r="BU159" t="s">
+        <v>237</v>
+      </c>
+      <c r="BV159" t="s">
+        <v>309</v>
+      </c>
+      <c r="BW159" t="s">
+        <v>623</v>
+      </c>
+      <c r="BX159">
+        <v>20</v>
+      </c>
+      <c r="BY159" t="s">
+        <v>239</v>
+      </c>
+      <c r="CA159">
+        <v>8</v>
+      </c>
+      <c r="CB159">
+        <v>4</v>
+      </c>
+      <c r="CC159" t="s">
+        <v>359</v>
+      </c>
+      <c r="CD159">
+        <v>0</v>
+      </c>
+      <c r="CE159">
+        <v>0</v>
+      </c>
+      <c r="CF159">
+        <v>0</v>
+      </c>
+      <c r="CG159">
+        <v>0</v>
+      </c>
+      <c r="CH159">
+        <v>1</v>
+      </c>
+      <c r="CI159">
+        <v>0</v>
+      </c>
+      <c r="CJ159">
+        <v>0</v>
+      </c>
+      <c r="CK159">
+        <v>9999</v>
+      </c>
+      <c r="CL159">
+        <v>10</v>
+      </c>
+      <c r="CM159">
+        <v>9999</v>
+      </c>
+      <c r="CN159" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO159" t="s">
+        <v>1029</v>
+      </c>
+      <c r="CP159">
+        <v>0</v>
+      </c>
+      <c r="CQ159">
+        <v>0</v>
+      </c>
+      <c r="CR159">
+        <v>0</v>
+      </c>
+      <c r="CS159">
+        <v>0</v>
+      </c>
+      <c r="CT159">
+        <v>1</v>
+      </c>
+      <c r="CU159">
+        <v>0</v>
+      </c>
+      <c r="CV159">
+        <v>0</v>
+      </c>
+      <c r="CX159" t="s">
+        <v>263</v>
+      </c>
+      <c r="DD159" t="s">
+        <v>336</v>
+      </c>
+      <c r="DE159">
+        <v>1</v>
+      </c>
+      <c r="DF159">
+        <v>0</v>
+      </c>
+      <c r="DG159">
+        <v>0</v>
+      </c>
+      <c r="DH159">
+        <v>0</v>
+      </c>
+      <c r="DI159">
+        <v>0</v>
+      </c>
+      <c r="DJ159">
+        <v>0</v>
+      </c>
+      <c r="DK159" t="s">
+        <v>289</v>
+      </c>
+      <c r="DL159" t="s">
+        <v>361</v>
+      </c>
+      <c r="DN159" t="s">
+        <v>392</v>
+      </c>
+      <c r="DO159" t="s">
+        <v>248</v>
+      </c>
+      <c r="DP159">
+        <v>1</v>
+      </c>
+      <c r="DQ159">
+        <v>1</v>
+      </c>
+      <c r="DR159">
+        <v>1</v>
+      </c>
+      <c r="DS159">
+        <v>1</v>
+      </c>
+      <c r="DT159">
+        <v>1</v>
+      </c>
+      <c r="DU159">
+        <v>1</v>
+      </c>
+      <c r="DV159">
+        <v>1</v>
+      </c>
+      <c r="DW159">
+        <v>1</v>
+      </c>
+      <c r="DX159">
+        <v>1</v>
+      </c>
+      <c r="DY159">
+        <v>1</v>
+      </c>
+      <c r="DZ159">
+        <v>1</v>
+      </c>
+      <c r="EA159">
+        <v>1</v>
+      </c>
+      <c r="EB159" t="s">
+        <v>362</v>
+      </c>
+      <c r="EC159" t="s">
+        <v>623</v>
+      </c>
+      <c r="ED159" t="s">
+        <v>250</v>
+      </c>
+      <c r="EE159" t="s">
+        <v>251</v>
+      </c>
+      <c r="EF159">
+        <v>0</v>
+      </c>
+      <c r="EG159">
+        <v>0</v>
+      </c>
+      <c r="EH159">
+        <v>0</v>
+      </c>
+      <c r="EI159">
+        <v>1</v>
+      </c>
+      <c r="EJ159">
+        <v>0</v>
+      </c>
+      <c r="EK159">
+        <v>0</v>
+      </c>
+      <c r="EL159" t="s">
+        <v>778</v>
+      </c>
+      <c r="EM159">
+        <v>0</v>
+      </c>
+      <c r="EN159">
+        <v>1</v>
+      </c>
+      <c r="EO159">
+        <v>0</v>
+      </c>
+      <c r="EP159">
+        <v>0</v>
+      </c>
+      <c r="EQ159" t="s">
+        <v>250</v>
+      </c>
+      <c r="ER159" t="s">
+        <v>294</v>
+      </c>
+      <c r="EY159" t="s">
+        <v>256</v>
+      </c>
+      <c r="EZ159" t="s">
+        <v>434</v>
+      </c>
+      <c r="FA159" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB159" t="s">
+        <v>295</v>
+      </c>
+      <c r="FC159" t="s">
+        <v>412</v>
+      </c>
+      <c r="FD159">
+        <v>1</v>
+      </c>
+      <c r="FE159">
+        <v>0</v>
+      </c>
+      <c r="FF159">
+        <v>1</v>
+      </c>
+      <c r="FG159">
+        <v>0</v>
+      </c>
+      <c r="FH159">
+        <v>0</v>
+      </c>
+      <c r="FI159">
+        <v>0</v>
+      </c>
+      <c r="FJ159" t="s">
+        <v>263</v>
+      </c>
+      <c r="FK159" t="s">
+        <v>258</v>
+      </c>
+      <c r="FM159" t="s">
+        <v>1485</v>
+      </c>
+      <c r="FN159">
+        <v>1</v>
+      </c>
+      <c r="FO159">
+        <v>1</v>
+      </c>
+      <c r="FP159">
+        <v>1</v>
+      </c>
+      <c r="FQ159">
+        <v>0</v>
+      </c>
+      <c r="FR159">
+        <v>0</v>
+      </c>
+      <c r="FS159">
+        <v>0</v>
+      </c>
+      <c r="FT159" t="s">
+        <v>263</v>
+      </c>
+      <c r="GJ159" t="s">
+        <v>226</v>
+      </c>
+      <c r="GK159" t="s">
+        <v>263</v>
+      </c>
+      <c r="GL159" t="s">
+        <v>226</v>
+      </c>
+      <c r="GM159" t="s">
+        <v>226</v>
+      </c>
+      <c r="GN159" t="s">
+        <v>263</v>
+      </c>
+      <c r="GO159" t="s">
+        <v>226</v>
+      </c>
+      <c r="GP159" t="s">
+        <v>263</v>
+      </c>
+      <c r="GQ159" t="s">
+        <v>263</v>
+      </c>
+      <c r="GR159" t="s">
+        <v>226</v>
+      </c>
+      <c r="GS159" t="s">
+        <v>263</v>
+      </c>
+      <c r="GT159" t="s">
+        <v>226</v>
+      </c>
+      <c r="GU159" t="s">
+        <v>263</v>
+      </c>
+      <c r="GV159" t="s">
+        <v>263</v>
+      </c>
+      <c r="GW159" t="s">
+        <v>263</v>
+      </c>
+      <c r="GX159" t="s">
+        <v>263</v>
+      </c>
+      <c r="GY159" t="s">
+        <v>263</v>
+      </c>
+      <c r="GZ159" t="s">
+        <v>1929</v>
+      </c>
+      <c r="HD159">
+        <v>22580265</v>
+      </c>
+      <c r="HE159" t="s">
+        <v>1930</v>
+      </c>
+      <c r="HF159" s="1">
+        <v>46225.674490740741</v>
+      </c>
+      <c r="HI159" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ159" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK159" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM159" t="s">
+        <v>1931</v>
+      </c>
+      <c r="HN159">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="160" spans="1:222">
+      <c r="A160" t="str">
+        <f t="shared" si="4"/>
+        <v>V2-R59</v>
+      </c>
+      <c r="B160">
+        <v>2</v>
+      </c>
+      <c r="C160" s="1">
+        <v>46220.59256809028</v>
+      </c>
+      <c r="D160" s="1">
+        <v>46225.432065983798</v>
+      </c>
+      <c r="E160" s="1">
+        <v>46220</v>
+      </c>
+      <c r="G160" t="s">
+        <v>1924</v>
+      </c>
+      <c r="H160" t="s">
+        <v>452</v>
+      </c>
+      <c r="I160" s="1">
+        <v>46220</v>
+      </c>
+      <c r="K160" t="s">
+        <v>1932</v>
+      </c>
+      <c r="L160">
+        <v>46</v>
+      </c>
+      <c r="M160" t="s">
+        <v>271</v>
+      </c>
+      <c r="O160" t="s">
+        <v>348</v>
+      </c>
+      <c r="P160" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>685</v>
+      </c>
+      <c r="R160" t="s">
+        <v>686</v>
+      </c>
+      <c r="S160" t="s">
+        <v>1837</v>
+      </c>
+      <c r="T160" t="s">
+        <v>1933</v>
+      </c>
+      <c r="U160" t="s">
+        <v>1934</v>
+      </c>
+      <c r="V160">
+        <v>13.9006723</v>
+      </c>
+      <c r="W160">
+        <v>-88.098682299999993</v>
+      </c>
+      <c r="X160">
+        <v>623.17966540748</v>
+      </c>
+      <c r="Y160">
+        <v>4.9939999999999998</v>
+      </c>
+      <c r="AA160" t="s">
+        <v>1935</v>
+      </c>
+      <c r="AB160" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD160" t="s">
+        <v>374</v>
+      </c>
+      <c r="AG160" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ160" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK160" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL160" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN160" t="s">
+        <v>1936</v>
+      </c>
+      <c r="AO160" t="s">
+        <v>271</v>
+      </c>
+      <c r="AP160">
+        <v>46</v>
+      </c>
+      <c r="AQ160" t="s">
+        <v>429</v>
+      </c>
+      <c r="AR160" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU160">
+        <v>1</v>
+      </c>
+      <c r="AV160">
+        <v>1</v>
+      </c>
+      <c r="AW160" t="s">
+        <v>1088</v>
+      </c>
+      <c r="BA160" t="s">
+        <v>1318</v>
+      </c>
+      <c r="BB160" t="s">
+        <v>306</v>
+      </c>
+      <c r="BD160" t="s">
+        <v>404</v>
+      </c>
+      <c r="BE160" t="s">
+        <v>279</v>
+      </c>
+      <c r="BF160" t="s">
+        <v>789</v>
+      </c>
+      <c r="BG160" t="s">
+        <v>281</v>
+      </c>
+      <c r="BH160" t="s">
+        <v>282</v>
+      </c>
+      <c r="BI160" t="s">
+        <v>233</v>
+      </c>
+      <c r="BJ160" t="s">
+        <v>1928</v>
+      </c>
+      <c r="BK160" t="s">
+        <v>226</v>
+      </c>
+      <c r="BL160" s="1">
+        <v>45292</v>
+      </c>
+      <c r="BM160" t="s">
+        <v>331</v>
+      </c>
+      <c r="BO160" t="s">
+        <v>236</v>
+      </c>
+      <c r="BP160" t="s">
+        <v>331</v>
+      </c>
+      <c r="BR160" t="s">
+        <v>236</v>
+      </c>
+      <c r="BS160" t="s">
+        <v>226</v>
+      </c>
+      <c r="BT160">
+        <v>40</v>
+      </c>
+      <c r="BU160" t="s">
+        <v>308</v>
+      </c>
+      <c r="BV160" t="s">
+        <v>245</v>
+      </c>
+      <c r="BW160" t="s">
+        <v>375</v>
+      </c>
+      <c r="FM160" t="s">
+        <v>437</v>
+      </c>
+      <c r="FN160">
+        <v>0</v>
+      </c>
+      <c r="FO160">
+        <v>0</v>
+      </c>
+      <c r="FP160">
+        <v>1</v>
+      </c>
+      <c r="FQ160">
+        <v>0</v>
+      </c>
+      <c r="FR160">
+        <v>0</v>
+      </c>
+      <c r="FS160">
+        <v>0</v>
+      </c>
+      <c r="FT160" t="s">
+        <v>226</v>
+      </c>
+      <c r="FU160">
+        <v>1</v>
+      </c>
+      <c r="FV160" t="s">
+        <v>343</v>
+      </c>
+      <c r="FW160">
+        <v>1</v>
+      </c>
+      <c r="FX160">
+        <v>1</v>
+      </c>
+      <c r="FY160">
+        <v>0</v>
+      </c>
+      <c r="FZ160">
+        <v>0</v>
+      </c>
+      <c r="GJ160" t="s">
+        <v>226</v>
+      </c>
+      <c r="GK160" t="s">
+        <v>263</v>
+      </c>
+      <c r="GL160" t="s">
+        <v>226</v>
+      </c>
+      <c r="GM160" t="s">
+        <v>226</v>
+      </c>
+      <c r="GN160" t="s">
+        <v>226</v>
+      </c>
+      <c r="GO160" t="s">
+        <v>226</v>
+      </c>
+      <c r="GP160" t="s">
+        <v>226</v>
+      </c>
+      <c r="GQ160" t="s">
+        <v>263</v>
+      </c>
+      <c r="GR160" t="s">
+        <v>263</v>
+      </c>
+      <c r="GZ160" t="s">
+        <v>1937</v>
+      </c>
+      <c r="HD160">
+        <v>22580405</v>
+      </c>
+      <c r="HE160" t="s">
+        <v>1938</v>
+      </c>
+      <c r="HF160" s="1">
+        <v>46225.682141203702</v>
+      </c>
+      <c r="HI160" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ160" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK160" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM160" t="s">
+        <v>1939</v>
+      </c>
+      <c r="HN160">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="161" spans="1:222">
+      <c r="A161" t="str">
+        <f t="shared" si="4"/>
+        <v>V2-R60</v>
+      </c>
+      <c r="B161">
+        <v>2</v>
+      </c>
+      <c r="C161" s="1">
+        <v>46220.613932893517</v>
+      </c>
+      <c r="D161" s="1">
+        <v>46225.433646585647</v>
+      </c>
+      <c r="E161" s="1">
+        <v>46220</v>
+      </c>
+      <c r="G161" t="s">
+        <v>1924</v>
+      </c>
+      <c r="H161" t="s">
+        <v>452</v>
+      </c>
+      <c r="I161" s="1">
+        <v>46220</v>
+      </c>
+      <c r="K161" t="s">
+        <v>1940</v>
+      </c>
+      <c r="L161">
+        <v>49</v>
+      </c>
+      <c r="M161" t="s">
+        <v>271</v>
+      </c>
+      <c r="O161" t="s">
+        <v>348</v>
+      </c>
+      <c r="P161" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>685</v>
+      </c>
+      <c r="R161" t="s">
+        <v>686</v>
+      </c>
+      <c r="S161" t="s">
+        <v>1837</v>
+      </c>
+      <c r="T161" t="s">
+        <v>1941</v>
+      </c>
+      <c r="U161" t="s">
+        <v>1942</v>
+      </c>
+      <c r="V161">
+        <v>13.9005388</v>
+      </c>
+      <c r="W161">
+        <v>-88.098863499999993</v>
+      </c>
+      <c r="X161">
+        <v>621.200927734375</v>
+      </c>
+      <c r="Y161">
+        <v>4.8109999999999999</v>
+      </c>
+      <c r="AA161" t="s">
+        <v>1943</v>
+      </c>
+      <c r="AB161" t="s">
+        <v>226</v>
+      </c>
+      <c r="AG161" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ161" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK161" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL161" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN161" t="s">
+        <v>1943</v>
+      </c>
+      <c r="AO161" t="s">
+        <v>271</v>
+      </c>
+      <c r="AP161">
+        <v>49</v>
+      </c>
+      <c r="AQ161" t="s">
+        <v>429</v>
+      </c>
+      <c r="AR161" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU161">
+        <v>3</v>
+      </c>
+      <c r="AV161">
+        <v>3</v>
+      </c>
+      <c r="AW161" t="s">
+        <v>1088</v>
+      </c>
+      <c r="BA161" t="s">
+        <v>1506</v>
+      </c>
+      <c r="BB161" t="s">
+        <v>306</v>
+      </c>
+      <c r="BD161" t="s">
+        <v>404</v>
+      </c>
+      <c r="BE161" t="s">
+        <v>229</v>
+      </c>
+      <c r="BF161" t="s">
+        <v>280</v>
+      </c>
+      <c r="BG161" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH161" t="s">
+        <v>282</v>
+      </c>
+      <c r="BI161" t="s">
+        <v>233</v>
+      </c>
+      <c r="BJ161" t="s">
+        <v>283</v>
+      </c>
+      <c r="BK161" t="s">
+        <v>226</v>
+      </c>
+      <c r="BL161" s="1">
+        <v>45292</v>
+      </c>
+      <c r="BM161" t="s">
+        <v>331</v>
+      </c>
+      <c r="BO161" t="s">
+        <v>236</v>
+      </c>
+      <c r="BP161" t="s">
+        <v>331</v>
+      </c>
+      <c r="BR161" t="s">
+        <v>236</v>
+      </c>
+      <c r="BS161" t="s">
+        <v>226</v>
+      </c>
+      <c r="BT161">
+        <v>40</v>
+      </c>
+      <c r="BU161" t="s">
+        <v>308</v>
+      </c>
+      <c r="BV161" t="s">
+        <v>238</v>
+      </c>
+      <c r="BX161">
+        <v>30</v>
+      </c>
+      <c r="BY161" t="s">
+        <v>406</v>
+      </c>
+      <c r="CA161">
+        <v>7</v>
+      </c>
+      <c r="CB161">
+        <v>8</v>
+      </c>
+      <c r="CC161" t="s">
+        <v>1944</v>
+      </c>
+      <c r="CD161">
+        <v>0</v>
+      </c>
+      <c r="CE161">
+        <v>0</v>
+      </c>
+      <c r="CF161">
+        <v>0</v>
+      </c>
+      <c r="CG161">
+        <v>0</v>
+      </c>
+      <c r="CH161">
+        <v>1</v>
+      </c>
+      <c r="CI161">
+        <v>1</v>
+      </c>
+      <c r="CJ161">
+        <v>1</v>
+      </c>
+      <c r="CK161">
+        <v>40</v>
+      </c>
+      <c r="CM161">
+        <v>9999</v>
+      </c>
+      <c r="CN161" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO161" t="s">
+        <v>242</v>
+      </c>
+      <c r="CP161">
+        <v>0</v>
+      </c>
+      <c r="CQ161">
+        <v>0</v>
+      </c>
+      <c r="CR161">
+        <v>0</v>
+      </c>
+      <c r="CS161">
+        <v>0</v>
+      </c>
+      <c r="CT161">
+        <v>0</v>
+      </c>
+      <c r="CU161">
+        <v>0</v>
+      </c>
+      <c r="CV161">
+        <v>1</v>
+      </c>
+      <c r="CX161" t="s">
+        <v>226</v>
+      </c>
+      <c r="CY161" t="s">
+        <v>359</v>
+      </c>
+      <c r="CZ161">
+        <v>0</v>
+      </c>
+      <c r="DA161">
+        <v>0</v>
+      </c>
+      <c r="DB161">
+        <v>1</v>
+      </c>
+      <c r="DC161">
+        <v>0</v>
+      </c>
+      <c r="DD161" t="s">
+        <v>336</v>
+      </c>
+      <c r="DE161">
+        <v>1</v>
+      </c>
+      <c r="DF161">
+        <v>0</v>
+      </c>
+      <c r="DG161">
+        <v>0</v>
+      </c>
+      <c r="DH161">
+        <v>0</v>
+      </c>
+      <c r="DI161">
+        <v>0</v>
+      </c>
+      <c r="DJ161">
+        <v>0</v>
+      </c>
+      <c r="DK161" t="s">
+        <v>315</v>
+      </c>
+      <c r="DL161" t="s">
+        <v>361</v>
+      </c>
+      <c r="DN161" t="s">
+        <v>392</v>
+      </c>
+      <c r="DO161" t="s">
+        <v>248</v>
+      </c>
+      <c r="DP161">
+        <v>1</v>
+      </c>
+      <c r="DQ161">
+        <v>1</v>
+      </c>
+      <c r="DR161">
+        <v>1</v>
+      </c>
+      <c r="DS161">
+        <v>1</v>
+      </c>
+      <c r="DT161">
+        <v>1</v>
+      </c>
+      <c r="DU161">
+        <v>1</v>
+      </c>
+      <c r="DV161">
+        <v>1</v>
+      </c>
+      <c r="DW161">
+        <v>1</v>
+      </c>
+      <c r="DX161">
+        <v>1</v>
+      </c>
+      <c r="DY161">
+        <v>1</v>
+      </c>
+      <c r="DZ161">
+        <v>1</v>
+      </c>
+      <c r="EA161">
+        <v>1</v>
+      </c>
+      <c r="EB161" t="s">
+        <v>245</v>
+      </c>
+      <c r="EC161" t="s">
+        <v>293</v>
+      </c>
+      <c r="ED161" t="s">
+        <v>376</v>
+      </c>
+      <c r="EL161" t="s">
+        <v>410</v>
+      </c>
+      <c r="EM161">
+        <v>0</v>
+      </c>
+      <c r="EN161">
+        <v>1</v>
+      </c>
+      <c r="EO161">
+        <v>1</v>
+      </c>
+      <c r="EP161">
+        <v>0</v>
+      </c>
+      <c r="EQ161" t="s">
+        <v>253</v>
+      </c>
+      <c r="ER161" t="s">
+        <v>294</v>
+      </c>
+      <c r="ES161" t="s">
+        <v>255</v>
+      </c>
+      <c r="ET161">
+        <v>0</v>
+      </c>
+      <c r="EU161">
+        <v>0</v>
+      </c>
+      <c r="EV161">
+        <v>0</v>
+      </c>
+      <c r="EW161">
+        <v>0</v>
+      </c>
+      <c r="EX161">
+        <v>1</v>
+      </c>
+      <c r="EY161" t="s">
+        <v>256</v>
+      </c>
+      <c r="EZ161" t="s">
+        <v>257</v>
+      </c>
+      <c r="FA161" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB161" t="s">
+        <v>340</v>
+      </c>
+      <c r="FC161" t="s">
+        <v>259</v>
+      </c>
+      <c r="FD161">
+        <v>1</v>
+      </c>
+      <c r="FE161">
+        <v>0</v>
+      </c>
+      <c r="FF161">
+        <v>0</v>
+      </c>
+      <c r="FG161">
+        <v>0</v>
+      </c>
+      <c r="FH161">
+        <v>0</v>
+      </c>
+      <c r="FI161">
+        <v>0</v>
+      </c>
+      <c r="FJ161" t="s">
+        <v>258</v>
+      </c>
+      <c r="FK161" t="s">
+        <v>226</v>
+      </c>
+      <c r="FM161" t="s">
+        <v>1945</v>
+      </c>
+      <c r="FN161">
+        <v>1</v>
+      </c>
+      <c r="FO161">
+        <v>1</v>
+      </c>
+      <c r="FP161">
+        <v>1</v>
+      </c>
+      <c r="FQ161">
+        <v>0</v>
+      </c>
+      <c r="FR161">
+        <v>0</v>
+      </c>
+      <c r="FS161">
+        <v>1</v>
+      </c>
+      <c r="FT161" t="s">
+        <v>226</v>
+      </c>
+      <c r="FU161">
+        <v>1</v>
+      </c>
+      <c r="FV161" t="s">
+        <v>261</v>
+      </c>
+      <c r="FW161">
+        <v>1</v>
+      </c>
+      <c r="FX161">
+        <v>0</v>
+      </c>
+      <c r="FY161">
+        <v>0</v>
+      </c>
+      <c r="FZ161">
+        <v>0</v>
+      </c>
+      <c r="GJ161" t="s">
+        <v>226</v>
+      </c>
+      <c r="GK161" t="s">
+        <v>226</v>
+      </c>
+      <c r="GL161" t="s">
+        <v>226</v>
+      </c>
+      <c r="GM161" t="s">
+        <v>226</v>
+      </c>
+      <c r="GN161" t="s">
+        <v>226</v>
+      </c>
+      <c r="GO161" t="s">
+        <v>226</v>
+      </c>
+      <c r="GP161" t="s">
+        <v>263</v>
+      </c>
+      <c r="GQ161" t="s">
+        <v>226</v>
+      </c>
+      <c r="GR161" t="s">
+        <v>226</v>
+      </c>
+      <c r="GS161" t="s">
+        <v>226</v>
+      </c>
+      <c r="GT161" t="s">
+        <v>226</v>
+      </c>
+      <c r="GU161" t="s">
+        <v>226</v>
+      </c>
+      <c r="GV161" t="s">
+        <v>226</v>
+      </c>
+      <c r="GW161" t="s">
+        <v>226</v>
+      </c>
+      <c r="GX161" t="s">
+        <v>263</v>
+      </c>
+      <c r="GY161" t="s">
+        <v>263</v>
+      </c>
+      <c r="GZ161" t="s">
+        <v>1946</v>
+      </c>
+      <c r="HD161">
+        <v>22580436</v>
+      </c>
+      <c r="HE161" t="s">
+        <v>1947</v>
+      </c>
+      <c r="HF161" s="1">
+        <v>46225.68372685185</v>
+      </c>
+      <c r="HI161" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ161" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK161" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM161" t="s">
+        <v>1948</v>
+      </c>
+      <c r="HN161">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="162" spans="1:222">
+      <c r="A162" t="str">
+        <f t="shared" si="4"/>
+        <v>V2-R61</v>
+      </c>
+      <c r="B162">
+        <v>2</v>
+      </c>
+      <c r="C162" s="1">
+        <v>46221.722839178241</v>
+      </c>
+      <c r="D162" s="1">
+        <v>46225.440359942128</v>
+      </c>
+      <c r="E162" s="1">
+        <v>46221</v>
+      </c>
+      <c r="G162" t="s">
+        <v>1924</v>
+      </c>
+      <c r="H162" t="s">
+        <v>452</v>
+      </c>
+      <c r="I162" s="1">
+        <v>46221</v>
+      </c>
+      <c r="K162" t="s">
+        <v>1949</v>
+      </c>
+      <c r="L162">
+        <v>26</v>
+      </c>
+      <c r="M162" t="s">
+        <v>271</v>
+      </c>
+      <c r="O162" t="s">
+        <v>348</v>
+      </c>
+      <c r="P162" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>455</v>
+      </c>
+      <c r="S162" t="s">
+        <v>1950</v>
+      </c>
+      <c r="T162" t="s">
+        <v>1951</v>
+      </c>
+      <c r="AA162" t="s">
+        <v>1952</v>
+      </c>
+      <c r="AB162" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD162" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG162" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ162" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK162" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL162" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN162" t="s">
+        <v>1952</v>
+      </c>
+      <c r="AO162" t="s">
+        <v>271</v>
+      </c>
+      <c r="AP162">
+        <v>26</v>
+      </c>
+      <c r="AQ162" t="s">
+        <v>429</v>
+      </c>
+      <c r="AR162" t="s">
+        <v>226</v>
+      </c>
+      <c r="AS162" t="s">
+        <v>519</v>
+      </c>
+      <c r="AT162" t="s">
+        <v>1953</v>
+      </c>
+      <c r="AU162">
+        <v>4</v>
+      </c>
+      <c r="AV162">
+        <v>1</v>
+      </c>
+      <c r="AW162" t="s">
+        <v>1354</v>
+      </c>
+      <c r="AY162">
+        <v>2</v>
+      </c>
+      <c r="AZ162">
+        <v>1</v>
+      </c>
+      <c r="BA162" t="s">
+        <v>431</v>
+      </c>
+      <c r="BB162" t="s">
+        <v>306</v>
+      </c>
+      <c r="BD162" t="s">
+        <v>278</v>
+      </c>
+      <c r="BE162" t="s">
+        <v>279</v>
+      </c>
+      <c r="BF162" t="s">
+        <v>230</v>
+      </c>
+      <c r="BG162" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH162" t="s">
+        <v>837</v>
+      </c>
+      <c r="BI162" t="s">
+        <v>553</v>
+      </c>
+      <c r="BJ162" t="s">
+        <v>283</v>
+      </c>
+      <c r="BK162" t="s">
+        <v>226</v>
+      </c>
+      <c r="BL162" s="1">
+        <v>44927</v>
+      </c>
+      <c r="BM162" t="s">
+        <v>331</v>
+      </c>
+      <c r="BO162" t="s">
+        <v>386</v>
+      </c>
+      <c r="BP162" t="s">
+        <v>331</v>
+      </c>
+      <c r="BR162" t="s">
+        <v>386</v>
+      </c>
+      <c r="BS162" t="s">
+        <v>226</v>
+      </c>
+      <c r="BT162">
+        <v>40</v>
+      </c>
+      <c r="BU162" t="s">
+        <v>287</v>
+      </c>
+      <c r="BV162" t="s">
+        <v>238</v>
+      </c>
+      <c r="BX162">
+        <v>15</v>
+      </c>
+      <c r="BY162" t="s">
+        <v>239</v>
+      </c>
+      <c r="CA162">
+        <v>60</v>
+      </c>
+      <c r="CB162">
+        <v>4</v>
+      </c>
+      <c r="CC162" t="s">
+        <v>359</v>
+      </c>
+      <c r="CD162">
+        <v>0</v>
+      </c>
+      <c r="CE162">
+        <v>0</v>
+      </c>
+      <c r="CF162">
+        <v>0</v>
+      </c>
+      <c r="CG162">
+        <v>0</v>
+      </c>
+      <c r="CH162">
+        <v>1</v>
+      </c>
+      <c r="CI162">
+        <v>0</v>
+      </c>
+      <c r="CJ162">
+        <v>0</v>
+      </c>
+      <c r="CK162">
+        <v>40</v>
+      </c>
+      <c r="CM162">
+        <v>9999</v>
+      </c>
+      <c r="CN162" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO162" t="s">
+        <v>242</v>
+      </c>
+      <c r="CP162">
+        <v>0</v>
+      </c>
+      <c r="CQ162">
+        <v>0</v>
+      </c>
+      <c r="CR162">
+        <v>0</v>
+      </c>
+      <c r="CS162">
+        <v>0</v>
+      </c>
+      <c r="CT162">
+        <v>0</v>
+      </c>
+      <c r="CU162">
+        <v>0</v>
+      </c>
+      <c r="CV162">
+        <v>1</v>
+      </c>
+      <c r="CX162" t="s">
+        <v>226</v>
+      </c>
+      <c r="CY162" t="s">
+        <v>590</v>
+      </c>
+      <c r="CZ162">
+        <v>1</v>
+      </c>
+      <c r="DA162">
+        <v>1</v>
+      </c>
+      <c r="DB162">
+        <v>1</v>
+      </c>
+      <c r="DC162">
+        <v>0</v>
+      </c>
+      <c r="DD162" t="s">
+        <v>244</v>
+      </c>
+      <c r="DE162">
+        <v>0</v>
+      </c>
+      <c r="DF162">
+        <v>1</v>
+      </c>
+      <c r="DG162">
+        <v>0</v>
+      </c>
+      <c r="DH162">
+        <v>0</v>
+      </c>
+      <c r="DI162">
+        <v>0</v>
+      </c>
+      <c r="DJ162">
+        <v>0</v>
+      </c>
+      <c r="DK162" t="s">
+        <v>391</v>
+      </c>
+      <c r="DL162" t="s">
+        <v>361</v>
+      </c>
+      <c r="DN162" t="s">
+        <v>392</v>
+      </c>
+      <c r="DO162" t="s">
+        <v>1013</v>
+      </c>
+      <c r="DP162">
+        <v>0</v>
+      </c>
+      <c r="DQ162">
+        <v>0</v>
+      </c>
+      <c r="DR162">
+        <v>0</v>
+      </c>
+      <c r="DS162">
+        <v>0</v>
+      </c>
+      <c r="DT162">
+        <v>0</v>
+      </c>
+      <c r="DU162">
+        <v>0</v>
+      </c>
+      <c r="DV162">
+        <v>0</v>
+      </c>
+      <c r="DW162">
+        <v>1</v>
+      </c>
+      <c r="DX162">
+        <v>1</v>
+      </c>
+      <c r="DY162">
+        <v>1</v>
+      </c>
+      <c r="DZ162">
+        <v>1</v>
+      </c>
+      <c r="EA162">
+        <v>1</v>
+      </c>
+      <c r="EB162" t="s">
+        <v>292</v>
+      </c>
+      <c r="EC162" t="s">
+        <v>623</v>
+      </c>
+      <c r="ED162" t="s">
+        <v>253</v>
+      </c>
+      <c r="EE162" t="s">
+        <v>363</v>
+      </c>
+      <c r="EF162">
+        <v>1</v>
+      </c>
+      <c r="EG162">
+        <v>0</v>
+      </c>
+      <c r="EH162">
+        <v>0</v>
+      </c>
+      <c r="EI162">
+        <v>0</v>
+      </c>
+      <c r="EJ162">
+        <v>0</v>
+      </c>
+      <c r="EK162">
+        <v>0</v>
+      </c>
+      <c r="EL162" t="s">
+        <v>255</v>
+      </c>
+      <c r="EM162">
+        <v>0</v>
+      </c>
+      <c r="EN162">
+        <v>0</v>
+      </c>
+      <c r="EO162">
+        <v>0</v>
+      </c>
+      <c r="EP162">
+        <v>1</v>
+      </c>
+      <c r="EQ162" t="s">
+        <v>253</v>
+      </c>
+      <c r="ER162" t="s">
+        <v>338</v>
+      </c>
+      <c r="ES162" t="s">
+        <v>811</v>
+      </c>
+      <c r="ET162">
+        <v>1</v>
+      </c>
+      <c r="EU162">
+        <v>0</v>
+      </c>
+      <c r="EV162">
+        <v>0</v>
+      </c>
+      <c r="EW162">
+        <v>0</v>
+      </c>
+      <c r="EX162">
+        <v>0</v>
+      </c>
+      <c r="EY162" t="s">
+        <v>256</v>
+      </c>
+      <c r="EZ162" t="s">
+        <v>257</v>
+      </c>
+      <c r="FA162" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB162" t="s">
+        <v>447</v>
+      </c>
+      <c r="FC162" t="s">
+        <v>259</v>
+      </c>
+      <c r="FD162">
+        <v>1</v>
+      </c>
+      <c r="FE162">
+        <v>0</v>
+      </c>
+      <c r="FF162">
+        <v>0</v>
+      </c>
+      <c r="FG162">
+        <v>0</v>
+      </c>
+      <c r="FH162">
+        <v>0</v>
+      </c>
+      <c r="FI162">
+        <v>0</v>
+      </c>
+      <c r="FJ162" t="s">
+        <v>263</v>
+      </c>
+      <c r="FK162" t="s">
+        <v>258</v>
+      </c>
+      <c r="FM162" t="s">
+        <v>850</v>
+      </c>
+      <c r="FN162">
+        <v>1</v>
+      </c>
+      <c r="FO162">
+        <v>1</v>
+      </c>
+      <c r="FP162">
+        <v>1</v>
+      </c>
+      <c r="FQ162">
+        <v>1</v>
+      </c>
+      <c r="FR162">
+        <v>1</v>
+      </c>
+      <c r="FS162">
+        <v>1</v>
+      </c>
+      <c r="FT162" t="s">
+        <v>226</v>
+      </c>
+      <c r="FU162">
+        <v>1</v>
+      </c>
+      <c r="FV162" t="s">
+        <v>261</v>
+      </c>
+      <c r="FW162">
+        <v>1</v>
+      </c>
+      <c r="FX162">
+        <v>0</v>
+      </c>
+      <c r="FY162">
+        <v>0</v>
+      </c>
+      <c r="FZ162">
+        <v>0</v>
+      </c>
+      <c r="GB162">
+        <v>1</v>
+      </c>
+      <c r="GC162" t="s">
+        <v>560</v>
+      </c>
+      <c r="GD162">
+        <v>0</v>
+      </c>
+      <c r="GE162">
+        <v>1</v>
+      </c>
+      <c r="GF162">
+        <v>0</v>
+      </c>
+      <c r="GG162">
+        <v>0</v>
+      </c>
+      <c r="GH162" t="s">
+        <v>455</v>
+      </c>
+      <c r="GJ162" t="s">
+        <v>226</v>
+      </c>
+      <c r="GK162" t="s">
+        <v>226</v>
+      </c>
+      <c r="GL162" t="s">
+        <v>226</v>
+      </c>
+      <c r="GM162" t="s">
+        <v>226</v>
+      </c>
+      <c r="GN162" t="s">
+        <v>226</v>
+      </c>
+      <c r="GO162" t="s">
+        <v>226</v>
+      </c>
+      <c r="GP162" t="s">
+        <v>226</v>
+      </c>
+      <c r="GQ162" t="s">
+        <v>226</v>
+      </c>
+      <c r="GR162" t="s">
+        <v>226</v>
+      </c>
+      <c r="GS162" t="s">
+        <v>226</v>
+      </c>
+      <c r="GT162" t="s">
+        <v>226</v>
+      </c>
+      <c r="GU162" t="s">
+        <v>226</v>
+      </c>
+      <c r="GV162" t="s">
+        <v>226</v>
+      </c>
+      <c r="GW162" t="s">
+        <v>226</v>
+      </c>
+      <c r="GX162" t="s">
+        <v>226</v>
+      </c>
+      <c r="GY162" t="s">
+        <v>226</v>
+      </c>
+      <c r="GZ162" t="s">
+        <v>1954</v>
+      </c>
+      <c r="HD162">
+        <v>22580619</v>
+      </c>
+      <c r="HE162" t="s">
+        <v>1955</v>
+      </c>
+      <c r="HF162" s="1">
+        <v>46225.690428240741</v>
+      </c>
+      <c r="HI162" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ162" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK162" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM162" t="s">
+        <v>1956</v>
+      </c>
+      <c r="HN162">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="163" spans="1:222">
+      <c r="A163" t="str">
+        <f t="shared" si="4"/>
+        <v>V2-R62</v>
+      </c>
+      <c r="B163">
+        <v>2</v>
+      </c>
+      <c r="C163" s="1">
+        <v>46218.753557951393</v>
+      </c>
+      <c r="D163" s="1">
+        <v>46222.863759490741</v>
+      </c>
+      <c r="E163" s="1">
+        <v>46218</v>
+      </c>
+      <c r="G163" t="s">
+        <v>1603</v>
+      </c>
+      <c r="H163" t="s">
+        <v>452</v>
+      </c>
+      <c r="I163" s="1">
+        <v>46218</v>
+      </c>
+      <c r="K163" t="s">
+        <v>1957</v>
+      </c>
+      <c r="L163">
+        <v>26</v>
+      </c>
+      <c r="M163" t="s">
+        <v>271</v>
+      </c>
+      <c r="O163" t="s">
+        <v>816</v>
+      </c>
+      <c r="P163" t="s">
+        <v>1700</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>816</v>
+      </c>
+      <c r="R163" t="s">
+        <v>1845</v>
+      </c>
+      <c r="S163" t="s">
+        <v>1844</v>
+      </c>
+      <c r="T163" t="s">
+        <v>1958</v>
+      </c>
+      <c r="U163" t="s">
+        <v>1959</v>
+      </c>
+      <c r="V163">
+        <v>13.462635000000001</v>
+      </c>
+      <c r="W163">
+        <v>-88.113938300000001</v>
+      </c>
+      <c r="X163">
+        <v>108.59999847412109</v>
+      </c>
+      <c r="Y163">
+        <v>4.6660000000000004</v>
+      </c>
+      <c r="AA163" t="s">
+        <v>1960</v>
+      </c>
+      <c r="AB163" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD163" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG163" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ163" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK163" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL163" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN163" t="s">
+        <v>1961</v>
+      </c>
+      <c r="AO163" t="s">
+        <v>271</v>
+      </c>
+      <c r="AP163">
+        <v>26</v>
+      </c>
+      <c r="AQ163" t="s">
+        <v>429</v>
+      </c>
+      <c r="AR163" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU163">
+        <v>3</v>
+      </c>
+      <c r="AV163">
+        <v>1</v>
+      </c>
+      <c r="AW163" t="s">
+        <v>430</v>
+      </c>
+      <c r="AX163">
+        <v>2</v>
+      </c>
+      <c r="AY163">
+        <v>1</v>
+      </c>
+      <c r="AZ163">
+        <v>2</v>
+      </c>
+      <c r="BA163" t="s">
+        <v>1318</v>
+      </c>
+      <c r="BB163" t="s">
+        <v>306</v>
+      </c>
+      <c r="BD163" t="s">
+        <v>278</v>
+      </c>
+      <c r="BE163" t="s">
+        <v>229</v>
+      </c>
+      <c r="BF163" t="s">
+        <v>280</v>
+      </c>
+      <c r="BG163" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH163" t="s">
+        <v>282</v>
+      </c>
+      <c r="BI163" t="s">
+        <v>233</v>
+      </c>
+      <c r="BJ163" t="s">
+        <v>234</v>
+      </c>
+      <c r="BK163" t="s">
+        <v>226</v>
+      </c>
+      <c r="BL163" s="1">
+        <v>44562</v>
+      </c>
+      <c r="BM163" t="s">
+        <v>235</v>
+      </c>
+      <c r="BO163" t="s">
+        <v>307</v>
+      </c>
+      <c r="BP163" t="s">
+        <v>477</v>
+      </c>
+      <c r="BR163" t="s">
+        <v>286</v>
+      </c>
+      <c r="BS163" t="s">
+        <v>226</v>
+      </c>
+      <c r="BT163">
+        <v>3</v>
+      </c>
+      <c r="BU163" t="s">
+        <v>387</v>
+      </c>
+      <c r="BV163" t="s">
+        <v>238</v>
+      </c>
+      <c r="BX163">
+        <v>22</v>
+      </c>
+      <c r="BY163" t="s">
+        <v>239</v>
+      </c>
+      <c r="CA163">
+        <v>8</v>
+      </c>
+      <c r="CB163">
+        <v>6</v>
+      </c>
+      <c r="CC163" t="s">
+        <v>1962</v>
+      </c>
+      <c r="CD163">
+        <v>1</v>
+      </c>
+      <c r="CE163">
+        <v>1</v>
+      </c>
+      <c r="CF163">
+        <v>1</v>
+      </c>
+      <c r="CG163">
+        <v>0</v>
+      </c>
+      <c r="CH163">
+        <v>0</v>
+      </c>
+      <c r="CI163">
+        <v>0</v>
+      </c>
+      <c r="CJ163">
+        <v>0</v>
+      </c>
+      <c r="CK163">
+        <v>9999</v>
+      </c>
+      <c r="CL163">
+        <v>12</v>
+      </c>
+      <c r="CM163">
+        <v>2000</v>
+      </c>
+      <c r="CN163" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO163" t="s">
+        <v>375</v>
+      </c>
+      <c r="CP163">
+        <v>0</v>
+      </c>
+      <c r="CQ163">
+        <v>0</v>
+      </c>
+      <c r="CR163">
+        <v>0</v>
+      </c>
+      <c r="CS163">
+        <v>0</v>
+      </c>
+      <c r="CT163">
+        <v>0</v>
+      </c>
+      <c r="CU163">
+        <v>1</v>
+      </c>
+      <c r="CV163">
+        <v>0</v>
+      </c>
+      <c r="CW163">
+        <v>29</v>
+      </c>
+      <c r="CX163" t="s">
+        <v>226</v>
+      </c>
+      <c r="CY163" t="s">
+        <v>590</v>
+      </c>
+      <c r="CZ163">
+        <v>1</v>
+      </c>
+      <c r="DA163">
+        <v>1</v>
+      </c>
+      <c r="DB163">
+        <v>1</v>
+      </c>
+      <c r="DC163">
+        <v>0</v>
+      </c>
+      <c r="DD163" t="s">
+        <v>244</v>
+      </c>
+      <c r="DE163">
+        <v>0</v>
+      </c>
+      <c r="DF163">
+        <v>1</v>
+      </c>
+      <c r="DG163">
+        <v>0</v>
+      </c>
+      <c r="DH163">
+        <v>0</v>
+      </c>
+      <c r="DI163">
+        <v>0</v>
+      </c>
+      <c r="DJ163">
+        <v>0</v>
+      </c>
+      <c r="DK163" t="s">
+        <v>289</v>
+      </c>
+      <c r="DL163" t="s">
+        <v>246</v>
+      </c>
+      <c r="DM163">
+        <v>25</v>
+      </c>
+      <c r="DN163" t="s">
+        <v>392</v>
+      </c>
+      <c r="DO163" t="s">
+        <v>522</v>
+      </c>
+      <c r="DP163">
+        <v>0</v>
+      </c>
+      <c r="DQ163">
+        <v>0</v>
+      </c>
+      <c r="DR163">
+        <v>0</v>
+      </c>
+      <c r="DS163">
+        <v>0</v>
+      </c>
+      <c r="DT163">
+        <v>0</v>
+      </c>
+      <c r="DU163">
+        <v>0</v>
+      </c>
+      <c r="DV163">
+        <v>0</v>
+      </c>
+      <c r="DW163">
+        <v>1</v>
+      </c>
+      <c r="DX163">
+        <v>1</v>
+      </c>
+      <c r="DY163">
+        <v>0</v>
+      </c>
+      <c r="DZ163">
+        <v>0</v>
+      </c>
+      <c r="EA163">
+        <v>0</v>
+      </c>
+      <c r="EB163" t="s">
+        <v>245</v>
+      </c>
+      <c r="EC163" t="s">
+        <v>293</v>
+      </c>
+      <c r="ED163" t="s">
+        <v>253</v>
+      </c>
+      <c r="EE163" t="s">
+        <v>363</v>
+      </c>
+      <c r="EF163">
+        <v>1</v>
+      </c>
+      <c r="EG163">
+        <v>0</v>
+      </c>
+      <c r="EH163">
+        <v>0</v>
+      </c>
+      <c r="EI163">
+        <v>0</v>
+      </c>
+      <c r="EJ163">
+        <v>0</v>
+      </c>
+      <c r="EK163">
+        <v>0</v>
+      </c>
+      <c r="EL163" t="s">
+        <v>252</v>
+      </c>
+      <c r="EM163">
+        <v>1</v>
+      </c>
+      <c r="EN163">
+        <v>0</v>
+      </c>
+      <c r="EO163">
+        <v>0</v>
+      </c>
+      <c r="EP163">
+        <v>0</v>
+      </c>
+      <c r="EQ163" t="s">
+        <v>253</v>
+      </c>
+      <c r="ER163" t="s">
+        <v>395</v>
+      </c>
+      <c r="ES163" t="s">
+        <v>255</v>
+      </c>
+      <c r="ET163">
+        <v>0</v>
+      </c>
+      <c r="EU163">
+        <v>0</v>
+      </c>
+      <c r="EV163">
+        <v>0</v>
+      </c>
+      <c r="EW163">
+        <v>0</v>
+      </c>
+      <c r="EX163">
+        <v>1</v>
+      </c>
+      <c r="EY163" t="s">
+        <v>256</v>
+      </c>
+      <c r="EZ163" t="s">
+        <v>257</v>
+      </c>
+      <c r="FA163" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB163" t="s">
+        <v>365</v>
+      </c>
+      <c r="FC163" t="s">
+        <v>1022</v>
+      </c>
+      <c r="FD163">
+        <v>1</v>
+      </c>
+      <c r="FE163">
+        <v>1</v>
+      </c>
+      <c r="FF163">
+        <v>1</v>
+      </c>
+      <c r="FG163">
+        <v>1</v>
+      </c>
+      <c r="FH163">
+        <v>0</v>
+      </c>
+      <c r="FI163">
+        <v>0</v>
+      </c>
+      <c r="FJ163" t="s">
+        <v>226</v>
+      </c>
+      <c r="FK163" t="s">
+        <v>226</v>
+      </c>
+      <c r="FM163" t="s">
+        <v>625</v>
+      </c>
+      <c r="FN163">
+        <v>1</v>
+      </c>
+      <c r="FO163">
+        <v>1</v>
+      </c>
+      <c r="FP163">
+        <v>1</v>
+      </c>
+      <c r="FQ163">
+        <v>0</v>
+      </c>
+      <c r="FR163">
+        <v>1</v>
+      </c>
+      <c r="FS163">
+        <v>1</v>
+      </c>
+      <c r="FT163" t="s">
+        <v>226</v>
+      </c>
+      <c r="FU163">
+        <v>2</v>
+      </c>
+      <c r="FV163" t="s">
+        <v>261</v>
+      </c>
+      <c r="FW163">
+        <v>1</v>
+      </c>
+      <c r="FX163">
+        <v>0</v>
+      </c>
+      <c r="FY163">
+        <v>0</v>
+      </c>
+      <c r="FZ163">
+        <v>0</v>
+      </c>
+      <c r="GB163">
+        <v>1</v>
+      </c>
+      <c r="GC163" t="s">
+        <v>262</v>
+      </c>
+      <c r="GD163">
+        <v>1</v>
+      </c>
+      <c r="GE163">
+        <v>0</v>
+      </c>
+      <c r="GF163">
+        <v>0</v>
+      </c>
+      <c r="GG163">
+        <v>0</v>
+      </c>
+      <c r="GH163" t="s">
+        <v>816</v>
+      </c>
+      <c r="GI163" t="s">
+        <v>420</v>
+      </c>
+      <c r="GJ163" t="s">
+        <v>226</v>
+      </c>
+      <c r="GK163" t="s">
+        <v>263</v>
+      </c>
+      <c r="GL163" t="s">
+        <v>263</v>
+      </c>
+      <c r="GM163" t="s">
+        <v>263</v>
+      </c>
+      <c r="GN163" t="s">
+        <v>263</v>
+      </c>
+      <c r="GO163" t="s">
+        <v>263</v>
+      </c>
+      <c r="GP163" t="s">
+        <v>263</v>
+      </c>
+      <c r="GQ163" t="s">
+        <v>263</v>
+      </c>
+      <c r="GR163" t="s">
+        <v>226</v>
+      </c>
+      <c r="GS163" t="s">
+        <v>263</v>
+      </c>
+      <c r="GT163" t="s">
+        <v>263</v>
+      </c>
+      <c r="GU163" t="s">
+        <v>263</v>
+      </c>
+      <c r="GV163" t="s">
+        <v>263</v>
+      </c>
+      <c r="GW163" t="s">
+        <v>263</v>
+      </c>
+      <c r="GX163" t="s">
+        <v>263</v>
+      </c>
+      <c r="GY163" t="s">
+        <v>263</v>
+      </c>
+      <c r="GZ163" t="s">
+        <v>1963</v>
+      </c>
+      <c r="HA163" t="s">
+        <v>1964</v>
+      </c>
+      <c r="HD163">
+        <v>22582002</v>
+      </c>
+      <c r="HE163" t="s">
+        <v>1965</v>
+      </c>
+      <c r="HF163" s="1">
+        <v>46225.746712962973</v>
+      </c>
+      <c r="HI163" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ163" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK163" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM163" t="s">
+        <v>1966</v>
+      </c>
+      <c r="HN163">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="164" spans="1:222">
+      <c r="A164" t="str">
+        <f t="shared" si="4"/>
+        <v>V2-R63</v>
+      </c>
+      <c r="B164">
+        <v>2</v>
+      </c>
+      <c r="C164" s="1">
+        <v>46220.592544479157</v>
+      </c>
+      <c r="D164" s="1">
+        <v>46224.89525065972</v>
+      </c>
+      <c r="E164" s="1">
+        <v>46220</v>
+      </c>
+      <c r="G164" t="s">
+        <v>1603</v>
+      </c>
+      <c r="H164" t="s">
+        <v>452</v>
+      </c>
+      <c r="I164" s="1">
+        <v>46220</v>
+      </c>
+      <c r="K164" t="s">
+        <v>1967</v>
+      </c>
+      <c r="L164">
+        <v>33</v>
+      </c>
+      <c r="M164" t="s">
+        <v>271</v>
+      </c>
+      <c r="O164" t="s">
+        <v>348</v>
+      </c>
+      <c r="P164" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>685</v>
+      </c>
+      <c r="R164" t="s">
+        <v>686</v>
+      </c>
+      <c r="S164" t="s">
+        <v>1837</v>
+      </c>
+      <c r="T164" t="s">
+        <v>1968</v>
+      </c>
+      <c r="U164" t="s">
+        <v>1969</v>
+      </c>
+      <c r="V164">
+        <v>13.908130999999999</v>
+      </c>
+      <c r="W164">
+        <v>-88.102647599999997</v>
+      </c>
+      <c r="X164">
+        <v>760.90000000000009</v>
+      </c>
+      <c r="Y164">
+        <v>4.78</v>
+      </c>
+      <c r="AA164" t="s">
+        <v>1970</v>
+      </c>
+      <c r="AB164" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD164" t="s">
+        <v>374</v>
+      </c>
+      <c r="AG164" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ164" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK164" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL164" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN164" t="s">
+        <v>1971</v>
+      </c>
+      <c r="AO164" t="s">
+        <v>271</v>
+      </c>
+      <c r="AP164">
+        <v>33</v>
+      </c>
+      <c r="AQ164" t="s">
+        <v>1343</v>
+      </c>
+      <c r="AR164" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU164">
+        <v>4</v>
+      </c>
+      <c r="AV164">
+        <v>3</v>
+      </c>
+      <c r="AW164" t="s">
+        <v>1317</v>
+      </c>
+      <c r="AX164">
+        <v>1</v>
+      </c>
+      <c r="AY164">
+        <v>2</v>
+      </c>
+      <c r="BA164" t="s">
+        <v>1506</v>
+      </c>
+      <c r="BB164" t="s">
+        <v>306</v>
+      </c>
+      <c r="BD164" t="s">
+        <v>404</v>
+      </c>
+      <c r="BE164" t="s">
+        <v>229</v>
+      </c>
+      <c r="BF164" t="s">
+        <v>330</v>
+      </c>
+      <c r="BG164" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH164" t="s">
+        <v>232</v>
+      </c>
+      <c r="BI164" t="s">
+        <v>233</v>
+      </c>
+      <c r="BJ164" t="s">
+        <v>234</v>
+      </c>
+      <c r="BK164" t="s">
+        <v>226</v>
+      </c>
+      <c r="BL164" s="1">
+        <v>45292</v>
+      </c>
+      <c r="BM164" t="s">
+        <v>235</v>
+      </c>
+      <c r="BO164" t="s">
+        <v>386</v>
+      </c>
+      <c r="BP164" t="s">
+        <v>284</v>
+      </c>
+      <c r="BR164" t="s">
+        <v>386</v>
+      </c>
+      <c r="BS164" t="s">
+        <v>226</v>
+      </c>
+      <c r="BT164">
+        <v>4</v>
+      </c>
+      <c r="BU164" t="s">
+        <v>255</v>
+      </c>
+      <c r="BV164" t="s">
+        <v>238</v>
+      </c>
+      <c r="BX164">
+        <v>15</v>
+      </c>
+      <c r="BY164" t="s">
+        <v>239</v>
+      </c>
+      <c r="CA164">
+        <v>15</v>
+      </c>
+      <c r="CB164">
+        <v>6</v>
+      </c>
+      <c r="CC164" t="s">
+        <v>691</v>
+      </c>
+      <c r="CD164">
+        <v>0</v>
+      </c>
+      <c r="CE164">
+        <v>0</v>
+      </c>
+      <c r="CF164">
+        <v>1</v>
+      </c>
+      <c r="CG164">
+        <v>1</v>
+      </c>
+      <c r="CH164">
+        <v>1</v>
+      </c>
+      <c r="CI164">
+        <v>0</v>
+      </c>
+      <c r="CJ164">
+        <v>1</v>
+      </c>
+      <c r="CK164">
+        <v>2</v>
+      </c>
+      <c r="CL164">
+        <v>8</v>
+      </c>
+      <c r="CM164">
+        <v>9999</v>
+      </c>
+      <c r="CN164" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO164" t="s">
+        <v>242</v>
+      </c>
+      <c r="CP164">
+        <v>0</v>
+      </c>
+      <c r="CQ164">
+        <v>0</v>
+      </c>
+      <c r="CR164">
+        <v>0</v>
+      </c>
+      <c r="CS164">
+        <v>0</v>
+      </c>
+      <c r="CT164">
+        <v>0</v>
+      </c>
+      <c r="CU164">
+        <v>0</v>
+      </c>
+      <c r="CV164">
+        <v>1</v>
+      </c>
+      <c r="CW164">
+        <v>2</v>
+      </c>
+      <c r="CX164" t="s">
+        <v>226</v>
+      </c>
+      <c r="CY164" t="s">
+        <v>590</v>
+      </c>
+      <c r="CZ164">
+        <v>1</v>
+      </c>
+      <c r="DA164">
+        <v>1</v>
+      </c>
+      <c r="DB164">
+        <v>1</v>
+      </c>
+      <c r="DC164">
+        <v>0</v>
+      </c>
+      <c r="DD164" t="s">
+        <v>244</v>
+      </c>
+      <c r="DE164">
+        <v>0</v>
+      </c>
+      <c r="DF164">
+        <v>1</v>
+      </c>
+      <c r="DG164">
+        <v>0</v>
+      </c>
+      <c r="DH164">
+        <v>0</v>
+      </c>
+      <c r="DI164">
+        <v>0</v>
+      </c>
+      <c r="DJ164">
+        <v>0</v>
+      </c>
+      <c r="DK164" t="s">
+        <v>315</v>
+      </c>
+      <c r="DL164" t="s">
+        <v>361</v>
+      </c>
+      <c r="DM164">
+        <v>0</v>
+      </c>
+      <c r="DN164" t="s">
+        <v>316</v>
+      </c>
+      <c r="DO164" t="s">
+        <v>291</v>
+      </c>
+      <c r="DP164">
+        <v>0</v>
+      </c>
+      <c r="DQ164">
+        <v>0</v>
+      </c>
+      <c r="DR164">
+        <v>0</v>
+      </c>
+      <c r="DS164">
+        <v>0</v>
+      </c>
+      <c r="DT164">
+        <v>0</v>
+      </c>
+      <c r="DU164">
+        <v>0</v>
+      </c>
+      <c r="DV164">
+        <v>0</v>
+      </c>
+      <c r="DW164">
+        <v>1</v>
+      </c>
+      <c r="DX164">
+        <v>1</v>
+      </c>
+      <c r="DY164">
+        <v>1</v>
+      </c>
+      <c r="DZ164">
+        <v>0</v>
+      </c>
+      <c r="EA164">
+        <v>0</v>
+      </c>
+      <c r="EB164" t="s">
+        <v>245</v>
+      </c>
+      <c r="EC164" t="s">
+        <v>293</v>
+      </c>
+      <c r="ED164" t="s">
+        <v>253</v>
+      </c>
+      <c r="EE164" t="s">
+        <v>363</v>
+      </c>
+      <c r="EF164">
+        <v>1</v>
+      </c>
+      <c r="EG164">
+        <v>0</v>
+      </c>
+      <c r="EH164">
+        <v>0</v>
+      </c>
+      <c r="EI164">
+        <v>0</v>
+      </c>
+      <c r="EJ164">
+        <v>0</v>
+      </c>
+      <c r="EK164">
+        <v>0</v>
+      </c>
+      <c r="EL164" t="s">
+        <v>494</v>
+      </c>
+      <c r="EM164">
+        <v>1</v>
+      </c>
+      <c r="EN164">
+        <v>0</v>
+      </c>
+      <c r="EO164">
+        <v>1</v>
+      </c>
+      <c r="EP164">
+        <v>0</v>
+      </c>
+      <c r="EQ164" t="s">
+        <v>253</v>
+      </c>
+      <c r="ER164" t="s">
+        <v>395</v>
+      </c>
+      <c r="ES164" t="s">
+        <v>255</v>
+      </c>
+      <c r="ET164">
+        <v>0</v>
+      </c>
+      <c r="EU164">
+        <v>0</v>
+      </c>
+      <c r="EV164">
+        <v>0</v>
+      </c>
+      <c r="EW164">
+        <v>0</v>
+      </c>
+      <c r="EX164">
+        <v>1</v>
+      </c>
+      <c r="EY164" t="s">
+        <v>256</v>
+      </c>
+      <c r="EZ164" t="s">
+        <v>257</v>
+      </c>
+      <c r="FA164" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB164" t="s">
+        <v>365</v>
+      </c>
+      <c r="FC164" t="s">
+        <v>1022</v>
+      </c>
+      <c r="FD164">
+        <v>1</v>
+      </c>
+      <c r="FE164">
+        <v>1</v>
+      </c>
+      <c r="FF164">
+        <v>1</v>
+      </c>
+      <c r="FG164">
+        <v>1</v>
+      </c>
+      <c r="FH164">
+        <v>0</v>
+      </c>
+      <c r="FI164">
+        <v>0</v>
+      </c>
+      <c r="FJ164" t="s">
+        <v>226</v>
+      </c>
+      <c r="FK164" t="s">
+        <v>226</v>
+      </c>
+      <c r="FM164" t="s">
+        <v>625</v>
+      </c>
+      <c r="FN164">
+        <v>1</v>
+      </c>
+      <c r="FO164">
+        <v>1</v>
+      </c>
+      <c r="FP164">
+        <v>1</v>
+      </c>
+      <c r="FQ164">
+        <v>0</v>
+      </c>
+      <c r="FR164">
+        <v>1</v>
+      </c>
+      <c r="FS164">
+        <v>1</v>
+      </c>
+      <c r="FT164" t="s">
+        <v>226</v>
+      </c>
+      <c r="FU164">
+        <v>1</v>
+      </c>
+      <c r="FV164" t="s">
+        <v>1902</v>
+      </c>
+      <c r="FW164">
+        <v>1</v>
+      </c>
+      <c r="FX164">
+        <v>1</v>
+      </c>
+      <c r="FY164">
+        <v>1</v>
+      </c>
+      <c r="FZ164">
+        <v>0</v>
+      </c>
+      <c r="GB164">
+        <v>1</v>
+      </c>
+      <c r="GC164" t="s">
+        <v>262</v>
+      </c>
+      <c r="GD164">
+        <v>1</v>
+      </c>
+      <c r="GE164">
+        <v>0</v>
+      </c>
+      <c r="GF164">
+        <v>0</v>
+      </c>
+      <c r="GG164">
+        <v>0</v>
+      </c>
+      <c r="GH164" t="s">
+        <v>685</v>
+      </c>
+      <c r="GI164" t="s">
+        <v>420</v>
+      </c>
+      <c r="GJ164" t="s">
+        <v>263</v>
+      </c>
+      <c r="GK164" t="s">
+        <v>263</v>
+      </c>
+      <c r="GL164" t="s">
+        <v>263</v>
+      </c>
+      <c r="GM164" t="s">
+        <v>263</v>
+      </c>
+      <c r="GN164" t="s">
+        <v>263</v>
+      </c>
+      <c r="GO164" t="s">
+        <v>263</v>
+      </c>
+      <c r="GP164" t="s">
+        <v>263</v>
+      </c>
+      <c r="GQ164" t="s">
+        <v>263</v>
+      </c>
+      <c r="GR164" t="s">
+        <v>226</v>
+      </c>
+      <c r="GS164" t="s">
+        <v>263</v>
+      </c>
+      <c r="GT164" t="s">
+        <v>263</v>
+      </c>
+      <c r="GU164" t="s">
+        <v>263</v>
+      </c>
+      <c r="GV164" t="s">
+        <v>263</v>
+      </c>
+      <c r="GW164" t="s">
+        <v>263</v>
+      </c>
+      <c r="GX164" t="s">
+        <v>263</v>
+      </c>
+      <c r="GY164" t="s">
+        <v>263</v>
+      </c>
+      <c r="GZ164" t="s">
+        <v>1972</v>
+      </c>
+      <c r="HA164" t="s">
+        <v>1973</v>
+      </c>
+      <c r="HD164">
+        <v>22582003</v>
+      </c>
+      <c r="HE164" t="s">
+        <v>1974</v>
+      </c>
+      <c r="HF164" s="1">
+        <v>46225.746712962973</v>
+      </c>
+      <c r="HI164" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ164" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK164" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM164" t="s">
+        <v>1975</v>
+      </c>
+      <c r="HN164">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="165" spans="1:222">
+      <c r="A165" t="str">
+        <f t="shared" si="4"/>
+        <v>V2-R64</v>
+      </c>
+      <c r="B165">
+        <v>2</v>
+      </c>
+      <c r="C165" s="1">
+        <v>46220.650191620371</v>
+      </c>
+      <c r="D165" s="1">
+        <v>46224.89933359954</v>
+      </c>
+      <c r="E165" s="1">
+        <v>46220</v>
+      </c>
+      <c r="G165" t="s">
+        <v>1603</v>
+      </c>
+      <c r="H165" t="s">
+        <v>452</v>
+      </c>
+      <c r="I165" s="1">
+        <v>46220</v>
+      </c>
+      <c r="K165" t="s">
+        <v>1976</v>
+      </c>
+      <c r="L165">
+        <v>39</v>
+      </c>
+      <c r="M165" t="s">
+        <v>271</v>
+      </c>
+      <c r="O165" t="s">
+        <v>348</v>
+      </c>
+      <c r="P165" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>685</v>
+      </c>
+      <c r="R165" t="s">
+        <v>686</v>
+      </c>
+      <c r="S165" t="s">
+        <v>1837</v>
+      </c>
+      <c r="T165" t="s">
+        <v>1977</v>
+      </c>
+      <c r="U165" t="s">
+        <v>1978</v>
+      </c>
+      <c r="V165">
+        <v>13.910750999999999</v>
+      </c>
+      <c r="W165">
+        <v>-88.105401200000003</v>
+      </c>
+      <c r="X165">
+        <v>720.79998779296875</v>
+      </c>
+      <c r="Y165">
+        <v>4.9660000000000002</v>
+      </c>
+      <c r="AA165" t="s">
+        <v>1976</v>
+      </c>
+      <c r="AB165" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD165" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG165" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ165" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK165" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL165" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN165" t="s">
+        <v>1979</v>
+      </c>
+      <c r="AO165" t="s">
+        <v>271</v>
+      </c>
+      <c r="AP165">
+        <v>39</v>
+      </c>
+      <c r="AQ165" t="s">
+        <v>1422</v>
+      </c>
+      <c r="AR165" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU165">
+        <v>3</v>
+      </c>
+      <c r="AV165">
+        <v>2</v>
+      </c>
+      <c r="AW165" t="s">
+        <v>1317</v>
+      </c>
+      <c r="AX165">
+        <v>1</v>
+      </c>
+      <c r="AY165">
+        <v>2</v>
+      </c>
+      <c r="AZ165">
+        <v>1</v>
+      </c>
+      <c r="BA165" t="s">
+        <v>431</v>
+      </c>
+      <c r="BB165" t="s">
+        <v>306</v>
+      </c>
+      <c r="BD165" t="s">
+        <v>229</v>
+      </c>
+      <c r="BE165" t="s">
+        <v>229</v>
+      </c>
+      <c r="BF165" t="s">
+        <v>280</v>
+      </c>
+      <c r="BG165" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH165" t="s">
+        <v>356</v>
+      </c>
+      <c r="BI165" t="s">
+        <v>233</v>
+      </c>
+      <c r="BJ165" t="s">
+        <v>234</v>
+      </c>
+      <c r="BK165" t="s">
+        <v>226</v>
+      </c>
+      <c r="BL165" s="1">
+        <v>45292</v>
+      </c>
+      <c r="BM165" t="s">
+        <v>331</v>
+      </c>
+      <c r="BO165" t="s">
+        <v>307</v>
+      </c>
+      <c r="BP165" t="s">
+        <v>331</v>
+      </c>
+      <c r="BR165" t="s">
+        <v>530</v>
+      </c>
+      <c r="BS165" t="s">
+        <v>263</v>
+      </c>
+      <c r="BU165" t="s">
+        <v>333</v>
+      </c>
+      <c r="BV165" t="s">
+        <v>309</v>
+      </c>
+      <c r="BW165" t="s">
+        <v>421</v>
+      </c>
+      <c r="BX165">
+        <v>3</v>
+      </c>
+      <c r="BY165" t="s">
+        <v>239</v>
+      </c>
+      <c r="CA165">
+        <v>3</v>
+      </c>
+      <c r="CB165">
+        <v>99</v>
+      </c>
+      <c r="CC165" t="s">
+        <v>1276</v>
+      </c>
+      <c r="CD165">
+        <v>0</v>
+      </c>
+      <c r="CE165">
+        <v>0</v>
+      </c>
+      <c r="CF165">
+        <v>0</v>
+      </c>
+      <c r="CG165">
+        <v>1</v>
+      </c>
+      <c r="CH165">
+        <v>1</v>
+      </c>
+      <c r="CI165">
+        <v>0</v>
+      </c>
+      <c r="CJ165">
+        <v>0</v>
+      </c>
+      <c r="CK165">
+        <v>60</v>
+      </c>
+      <c r="CL165">
+        <v>10</v>
+      </c>
+      <c r="CM165">
+        <v>450</v>
+      </c>
+      <c r="CN165" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO165" t="s">
+        <v>242</v>
+      </c>
+      <c r="CP165">
+        <v>0</v>
+      </c>
+      <c r="CQ165">
+        <v>0</v>
+      </c>
+      <c r="CR165">
+        <v>0</v>
+      </c>
+      <c r="CS165">
+        <v>0</v>
+      </c>
+      <c r="CT165">
+        <v>0</v>
+      </c>
+      <c r="CU165">
+        <v>0</v>
+      </c>
+      <c r="CV165">
+        <v>1</v>
+      </c>
+      <c r="CW165">
+        <v>29</v>
+      </c>
+      <c r="CX165" t="s">
+        <v>263</v>
+      </c>
+      <c r="DD165" t="s">
+        <v>336</v>
+      </c>
+      <c r="DE165">
+        <v>1</v>
+      </c>
+      <c r="DF165">
+        <v>0</v>
+      </c>
+      <c r="DG165">
+        <v>0</v>
+      </c>
+      <c r="DH165">
+        <v>0</v>
+      </c>
+      <c r="DI165">
+        <v>0</v>
+      </c>
+      <c r="DJ165">
+        <v>0</v>
+      </c>
+      <c r="DK165" t="s">
+        <v>391</v>
+      </c>
+      <c r="DL165" t="s">
+        <v>361</v>
+      </c>
+      <c r="DM165">
+        <v>10</v>
+      </c>
+      <c r="DN165" t="s">
+        <v>290</v>
+      </c>
+      <c r="DO165" t="s">
+        <v>291</v>
+      </c>
+      <c r="DP165">
+        <v>0</v>
+      </c>
+      <c r="DQ165">
+        <v>0</v>
+      </c>
+      <c r="DR165">
+        <v>0</v>
+      </c>
+      <c r="DS165">
+        <v>0</v>
+      </c>
+      <c r="DT165">
+        <v>0</v>
+      </c>
+      <c r="DU165">
+        <v>0</v>
+      </c>
+      <c r="DV165">
+        <v>0</v>
+      </c>
+      <c r="DW165">
+        <v>1</v>
+      </c>
+      <c r="DX165">
+        <v>1</v>
+      </c>
+      <c r="DY165">
+        <v>1</v>
+      </c>
+      <c r="DZ165">
+        <v>0</v>
+      </c>
+      <c r="EA165">
+        <v>0</v>
+      </c>
+      <c r="EB165" t="s">
+        <v>362</v>
+      </c>
+      <c r="EC165" t="s">
+        <v>293</v>
+      </c>
+      <c r="ED165" t="s">
+        <v>253</v>
+      </c>
+      <c r="EE165" t="s">
+        <v>251</v>
+      </c>
+      <c r="EF165">
+        <v>0</v>
+      </c>
+      <c r="EG165">
+        <v>0</v>
+      </c>
+      <c r="EH165">
+        <v>0</v>
+      </c>
+      <c r="EI165">
+        <v>1</v>
+      </c>
+      <c r="EJ165">
+        <v>0</v>
+      </c>
+      <c r="EK165">
+        <v>0</v>
+      </c>
+      <c r="EL165" t="s">
+        <v>394</v>
+      </c>
+      <c r="EM165">
+        <v>1</v>
+      </c>
+      <c r="EN165">
+        <v>1</v>
+      </c>
+      <c r="EO165">
+        <v>1</v>
+      </c>
+      <c r="EP165">
+        <v>0</v>
+      </c>
+      <c r="EQ165" t="s">
+        <v>253</v>
+      </c>
+      <c r="ER165" t="s">
+        <v>294</v>
+      </c>
+      <c r="ES165" t="s">
+        <v>255</v>
+      </c>
+      <c r="ET165">
+        <v>0</v>
+      </c>
+      <c r="EU165">
+        <v>0</v>
+      </c>
+      <c r="EV165">
+        <v>0</v>
+      </c>
+      <c r="EW165">
+        <v>0</v>
+      </c>
+      <c r="EX165">
+        <v>1</v>
+      </c>
+      <c r="EY165" t="s">
+        <v>256</v>
+      </c>
+      <c r="EZ165" t="s">
+        <v>257</v>
+      </c>
+      <c r="FA165" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB165" t="s">
+        <v>255</v>
+      </c>
+      <c r="FC165" t="s">
+        <v>519</v>
+      </c>
+      <c r="FD165">
+        <v>0</v>
+      </c>
+      <c r="FE165">
+        <v>0</v>
+      </c>
+      <c r="FF165">
+        <v>0</v>
+      </c>
+      <c r="FG165">
+        <v>0</v>
+      </c>
+      <c r="FH165">
+        <v>0</v>
+      </c>
+      <c r="FI165">
+        <v>1</v>
+      </c>
+      <c r="FJ165" t="s">
+        <v>226</v>
+      </c>
+      <c r="FK165" t="s">
+        <v>263</v>
+      </c>
+      <c r="FM165" t="s">
+        <v>625</v>
+      </c>
+      <c r="FN165">
+        <v>1</v>
+      </c>
+      <c r="FO165">
+        <v>1</v>
+      </c>
+      <c r="FP165">
+        <v>1</v>
+      </c>
+      <c r="FQ165">
+        <v>0</v>
+      </c>
+      <c r="FR165">
+        <v>1</v>
+      </c>
+      <c r="FS165">
+        <v>1</v>
+      </c>
+      <c r="FT165" t="s">
+        <v>263</v>
+      </c>
+      <c r="GJ165" t="s">
+        <v>263</v>
+      </c>
+      <c r="GK165" t="s">
+        <v>263</v>
+      </c>
+      <c r="GL165" t="s">
+        <v>263</v>
+      </c>
+      <c r="GM165" t="s">
+        <v>263</v>
+      </c>
+      <c r="GN165" t="s">
+        <v>263</v>
+      </c>
+      <c r="GO165" t="s">
+        <v>263</v>
+      </c>
+      <c r="GP165" t="s">
+        <v>263</v>
+      </c>
+      <c r="GQ165" t="s">
+        <v>263</v>
+      </c>
+      <c r="GR165" t="s">
+        <v>226</v>
+      </c>
+      <c r="GS165" t="s">
+        <v>263</v>
+      </c>
+      <c r="GT165" t="s">
+        <v>263</v>
+      </c>
+      <c r="GU165" t="s">
+        <v>263</v>
+      </c>
+      <c r="GV165" t="s">
+        <v>263</v>
+      </c>
+      <c r="GW165" t="s">
+        <v>263</v>
+      </c>
+      <c r="GX165" t="s">
+        <v>263</v>
+      </c>
+      <c r="GY165" t="s">
+        <v>263</v>
+      </c>
+      <c r="GZ165" t="s">
+        <v>1980</v>
+      </c>
+      <c r="HD165">
+        <v>22582004</v>
+      </c>
+      <c r="HE165" t="s">
+        <v>1981</v>
+      </c>
+      <c r="HF165" s="1">
+        <v>46225.746724537043</v>
+      </c>
+      <c r="HI165" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ165" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK165" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM165" t="s">
+        <v>1982</v>
+      </c>
+      <c r="HN165">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="166" spans="1:222">
+      <c r="A166" t="str">
+        <f t="shared" si="4"/>
+        <v>V2-R65</v>
+      </c>
+      <c r="B166">
+        <v>2</v>
+      </c>
+      <c r="C166" s="1">
+        <v>46221.695741932868</v>
+      </c>
+      <c r="D166" s="1">
+        <v>46224.901688958344</v>
+      </c>
+      <c r="E166" s="1">
+        <v>46221</v>
+      </c>
+      <c r="G166" t="s">
+        <v>1603</v>
+      </c>
+      <c r="H166" t="s">
+        <v>452</v>
+      </c>
+      <c r="I166" s="1">
+        <v>46221</v>
+      </c>
+      <c r="K166" t="s">
+        <v>613</v>
+      </c>
+      <c r="L166">
+        <v>49</v>
+      </c>
+      <c r="M166" t="s">
+        <v>271</v>
+      </c>
+      <c r="O166" t="s">
+        <v>348</v>
+      </c>
+      <c r="P166" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>455</v>
+      </c>
+      <c r="R166" t="s">
+        <v>1983</v>
+      </c>
+      <c r="S166" t="s">
+        <v>1984</v>
+      </c>
+      <c r="T166" t="s">
+        <v>1985</v>
+      </c>
+      <c r="AA166" t="s">
+        <v>1986</v>
+      </c>
+      <c r="AB166" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD166" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG166" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ166" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK166" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL166" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN166" t="s">
+        <v>1987</v>
+      </c>
+      <c r="AO166" t="s">
+        <v>271</v>
+      </c>
+      <c r="AP166">
+        <v>49</v>
+      </c>
+      <c r="AQ166" t="s">
+        <v>429</v>
+      </c>
+      <c r="AR166" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU166">
+        <v>3</v>
+      </c>
+      <c r="AV166">
+        <v>2</v>
+      </c>
+      <c r="AW166" t="s">
+        <v>1317</v>
+      </c>
+      <c r="AX166">
+        <v>1</v>
+      </c>
+      <c r="AY166">
+        <v>1</v>
+      </c>
+      <c r="AZ166">
+        <v>1</v>
+      </c>
+      <c r="BA166" t="s">
+        <v>431</v>
+      </c>
+      <c r="BB166" t="s">
+        <v>227</v>
+      </c>
+      <c r="BD166" t="s">
+        <v>229</v>
+      </c>
+      <c r="BE166" t="s">
+        <v>279</v>
+      </c>
+      <c r="BF166" t="s">
+        <v>230</v>
+      </c>
+      <c r="BG166" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH166" t="s">
+        <v>232</v>
+      </c>
+      <c r="BI166" t="s">
+        <v>618</v>
+      </c>
+      <c r="BJ166" t="s">
+        <v>283</v>
+      </c>
+      <c r="BK166" t="s">
+        <v>258</v>
+      </c>
+      <c r="BM166" t="s">
+        <v>331</v>
+      </c>
+      <c r="BO166" t="s">
+        <v>307</v>
+      </c>
+      <c r="BP166" t="s">
+        <v>331</v>
+      </c>
+      <c r="BR166" t="s">
+        <v>530</v>
+      </c>
+      <c r="BS166" t="s">
+        <v>226</v>
+      </c>
+      <c r="BT166">
+        <v>60</v>
+      </c>
+      <c r="BU166" t="s">
+        <v>308</v>
+      </c>
+      <c r="BV166" t="s">
+        <v>309</v>
+      </c>
+      <c r="BW166" t="s">
+        <v>375</v>
+      </c>
+      <c r="BX166">
+        <v>29</v>
+      </c>
+      <c r="BY166" t="s">
+        <v>406</v>
+      </c>
+      <c r="CA166">
+        <v>9999</v>
+      </c>
+      <c r="CB166">
+        <v>1</v>
+      </c>
+      <c r="CC166" t="s">
+        <v>808</v>
+      </c>
+      <c r="CD166">
+        <v>0</v>
+      </c>
+      <c r="CE166">
+        <v>0</v>
+      </c>
+      <c r="CF166">
+        <v>0</v>
+      </c>
+      <c r="CG166">
+        <v>1</v>
+      </c>
+      <c r="CH166">
+        <v>1</v>
+      </c>
+      <c r="CI166">
+        <v>1</v>
+      </c>
+      <c r="CJ166">
+        <v>1</v>
+      </c>
+      <c r="CK166">
+        <v>2</v>
+      </c>
+      <c r="CL166">
+        <v>0</v>
+      </c>
+      <c r="CM166">
+        <v>9999</v>
+      </c>
+      <c r="CN166" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO166" t="s">
+        <v>242</v>
+      </c>
+      <c r="CP166">
+        <v>0</v>
+      </c>
+      <c r="CQ166">
+        <v>0</v>
+      </c>
+      <c r="CR166">
+        <v>0</v>
+      </c>
+      <c r="CS166">
+        <v>0</v>
+      </c>
+      <c r="CT166">
+        <v>0</v>
+      </c>
+      <c r="CU166">
+        <v>0</v>
+      </c>
+      <c r="CV166">
+        <v>1</v>
+      </c>
+      <c r="CW166">
+        <v>120</v>
+      </c>
+      <c r="CX166" t="s">
+        <v>226</v>
+      </c>
+      <c r="CY166" t="s">
+        <v>1988</v>
+      </c>
+      <c r="CZ166">
+        <v>1</v>
+      </c>
+      <c r="DA166">
+        <v>1</v>
+      </c>
+      <c r="DB166">
+        <v>1</v>
+      </c>
+      <c r="DC166">
+        <v>0</v>
+      </c>
+      <c r="DD166" t="s">
+        <v>390</v>
+      </c>
+      <c r="DE166">
+        <v>1</v>
+      </c>
+      <c r="DF166">
+        <v>1</v>
+      </c>
+      <c r="DG166">
+        <v>0</v>
+      </c>
+      <c r="DH166">
+        <v>0</v>
+      </c>
+      <c r="DI166">
+        <v>0</v>
+      </c>
+      <c r="DJ166">
+        <v>0</v>
+      </c>
+      <c r="DK166" t="s">
+        <v>289</v>
+      </c>
+      <c r="DL166" t="s">
+        <v>361</v>
+      </c>
+      <c r="DM166">
+        <v>10</v>
+      </c>
+      <c r="DN166" t="s">
+        <v>290</v>
+      </c>
+      <c r="DO166" t="s">
+        <v>291</v>
+      </c>
+      <c r="DP166">
+        <v>0</v>
+      </c>
+      <c r="DQ166">
+        <v>0</v>
+      </c>
+      <c r="DR166">
+        <v>0</v>
+      </c>
+      <c r="DS166">
+        <v>0</v>
+      </c>
+      <c r="DT166">
+        <v>0</v>
+      </c>
+      <c r="DU166">
+        <v>0</v>
+      </c>
+      <c r="DV166">
+        <v>0</v>
+      </c>
+      <c r="DW166">
+        <v>1</v>
+      </c>
+      <c r="DX166">
+        <v>1</v>
+      </c>
+      <c r="DY166">
+        <v>1</v>
+      </c>
+      <c r="DZ166">
+        <v>0</v>
+      </c>
+      <c r="EA166">
+        <v>0</v>
+      </c>
+      <c r="EB166" t="s">
+        <v>292</v>
+      </c>
+      <c r="EC166" t="s">
+        <v>293</v>
+      </c>
+      <c r="ED166" t="s">
+        <v>253</v>
+      </c>
+      <c r="EE166" t="s">
+        <v>838</v>
+      </c>
+      <c r="EF166">
+        <v>1</v>
+      </c>
+      <c r="EG166">
+        <v>0</v>
+      </c>
+      <c r="EH166">
+        <v>0</v>
+      </c>
+      <c r="EI166">
+        <v>1</v>
+      </c>
+      <c r="EJ166">
+        <v>0</v>
+      </c>
+      <c r="EK166">
+        <v>0</v>
+      </c>
+      <c r="EL166" t="s">
+        <v>410</v>
+      </c>
+      <c r="EM166">
+        <v>0</v>
+      </c>
+      <c r="EN166">
+        <v>1</v>
+      </c>
+      <c r="EO166">
+        <v>1</v>
+      </c>
+      <c r="EP166">
+        <v>0</v>
+      </c>
+      <c r="EQ166" t="s">
+        <v>253</v>
+      </c>
+      <c r="ER166" t="s">
+        <v>294</v>
+      </c>
+      <c r="ES166" t="s">
+        <v>255</v>
+      </c>
+      <c r="ET166">
+        <v>0</v>
+      </c>
+      <c r="EU166">
+        <v>0</v>
+      </c>
+      <c r="EV166">
+        <v>0</v>
+      </c>
+      <c r="EW166">
+        <v>0</v>
+      </c>
+      <c r="EX166">
+        <v>1</v>
+      </c>
+      <c r="EY166" t="s">
+        <v>256</v>
+      </c>
+      <c r="EZ166" t="s">
+        <v>257</v>
+      </c>
+      <c r="FA166" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB166" t="s">
+        <v>365</v>
+      </c>
+      <c r="FC166" t="s">
+        <v>646</v>
+      </c>
+      <c r="FD166">
+        <v>1</v>
+      </c>
+      <c r="FE166">
+        <v>1</v>
+      </c>
+      <c r="FF166">
+        <v>0</v>
+      </c>
+      <c r="FG166">
+        <v>0</v>
+      </c>
+      <c r="FH166">
+        <v>0</v>
+      </c>
+      <c r="FI166">
+        <v>0</v>
+      </c>
+      <c r="FJ166" t="s">
+        <v>226</v>
+      </c>
+      <c r="FK166" t="s">
+        <v>226</v>
+      </c>
+      <c r="FM166" t="s">
+        <v>625</v>
+      </c>
+      <c r="FN166">
+        <v>1</v>
+      </c>
+      <c r="FO166">
+        <v>1</v>
+      </c>
+      <c r="FP166">
+        <v>1</v>
+      </c>
+      <c r="FQ166">
+        <v>0</v>
+      </c>
+      <c r="FR166">
+        <v>1</v>
+      </c>
+      <c r="FS166">
+        <v>1</v>
+      </c>
+      <c r="FT166" t="s">
+        <v>226</v>
+      </c>
+      <c r="FU166">
+        <v>1</v>
+      </c>
+      <c r="FV166" t="s">
+        <v>1148</v>
+      </c>
+      <c r="FW166">
+        <v>1</v>
+      </c>
+      <c r="FX166">
+        <v>0</v>
+      </c>
+      <c r="FY166">
+        <v>1</v>
+      </c>
+      <c r="FZ166">
+        <v>0</v>
+      </c>
+      <c r="GB166">
+        <v>1</v>
+      </c>
+      <c r="GC166" t="s">
+        <v>560</v>
+      </c>
+      <c r="GD166">
+        <v>0</v>
+      </c>
+      <c r="GE166">
+        <v>1</v>
+      </c>
+      <c r="GF166">
+        <v>0</v>
+      </c>
+      <c r="GG166">
+        <v>0</v>
+      </c>
+      <c r="GH166" t="s">
+        <v>455</v>
+      </c>
+      <c r="GI166" t="s">
+        <v>666</v>
+      </c>
+      <c r="GJ166" t="s">
+        <v>226</v>
+      </c>
+      <c r="GK166" t="s">
+        <v>226</v>
+      </c>
+      <c r="GL166" t="s">
+        <v>263</v>
+      </c>
+      <c r="GM166" t="s">
+        <v>226</v>
+      </c>
+      <c r="GN166" t="s">
+        <v>226</v>
+      </c>
+      <c r="GO166" t="s">
+        <v>226</v>
+      </c>
+      <c r="GP166" t="s">
+        <v>263</v>
+      </c>
+      <c r="GQ166" t="s">
+        <v>263</v>
+      </c>
+      <c r="GR166" t="s">
+        <v>226</v>
+      </c>
+      <c r="GS166" t="s">
+        <v>263</v>
+      </c>
+      <c r="GT166" t="s">
+        <v>226</v>
+      </c>
+      <c r="GU166" t="s">
+        <v>263</v>
+      </c>
+      <c r="GV166" t="s">
+        <v>263</v>
+      </c>
+      <c r="GW166" t="s">
+        <v>263</v>
+      </c>
+      <c r="GX166" t="s">
+        <v>263</v>
+      </c>
+      <c r="GY166" t="s">
+        <v>263</v>
+      </c>
+      <c r="GZ166" t="s">
+        <v>1989</v>
+      </c>
+      <c r="HC166" t="s">
+        <v>1990</v>
+      </c>
+      <c r="HD166">
+        <v>22582005</v>
+      </c>
+      <c r="HE166" t="s">
+        <v>1991</v>
+      </c>
+      <c r="HF166" s="1">
+        <v>46225.746724537043</v>
+      </c>
+      <c r="HI166" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ166" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK166" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM166" t="s">
+        <v>1992</v>
+      </c>
+      <c r="HN166">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="167" spans="1:222">
+      <c r="A167" t="str">
+        <f t="shared" si="4"/>
+        <v>V2-R66</v>
+      </c>
+      <c r="B167">
+        <v>2</v>
+      </c>
+      <c r="C167" s="1">
+        <v>46221.73673045139</v>
+      </c>
+      <c r="D167" s="1">
+        <v>46224.90520966435</v>
+      </c>
+      <c r="E167" s="1">
+        <v>46221</v>
+      </c>
+      <c r="G167" t="s">
+        <v>1603</v>
+      </c>
+      <c r="H167" t="s">
+        <v>452</v>
+      </c>
+      <c r="I167" s="1">
+        <v>46221</v>
+      </c>
+      <c r="K167" t="s">
+        <v>1993</v>
+      </c>
+      <c r="L167">
+        <v>52</v>
+      </c>
+      <c r="M167" t="s">
+        <v>271</v>
+      </c>
+      <c r="O167" t="s">
+        <v>348</v>
+      </c>
+      <c r="P167" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>455</v>
+      </c>
+      <c r="R167" t="s">
+        <v>1027</v>
+      </c>
+      <c r="S167" t="s">
+        <v>1994</v>
+      </c>
+      <c r="T167" t="s">
+        <v>1995</v>
+      </c>
+      <c r="AA167" t="s">
+        <v>1993</v>
+      </c>
+      <c r="AB167" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD167" t="s">
+        <v>276</v>
+      </c>
+      <c r="AG167" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ167" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK167" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL167" t="s">
+        <v>226</v>
+      </c>
+      <c r="AN167" t="s">
+        <v>1272</v>
+      </c>
+      <c r="AO167" t="s">
+        <v>271</v>
+      </c>
+      <c r="AP167">
+        <v>52</v>
+      </c>
+      <c r="AQ167" t="s">
+        <v>429</v>
+      </c>
+      <c r="AR167" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU167">
+        <v>3</v>
+      </c>
+      <c r="AV167">
+        <v>2</v>
+      </c>
+      <c r="AW167" t="s">
+        <v>1317</v>
+      </c>
+      <c r="AX167">
+        <v>1</v>
+      </c>
+      <c r="AY167">
+        <v>0</v>
+      </c>
+      <c r="AZ167">
+        <v>3</v>
+      </c>
+      <c r="BA167" t="s">
+        <v>431</v>
+      </c>
+      <c r="BB167" t="s">
+        <v>227</v>
+      </c>
+      <c r="BD167" t="s">
+        <v>237</v>
+      </c>
+      <c r="BE167" t="s">
+        <v>229</v>
+      </c>
+      <c r="BF167" t="s">
+        <v>230</v>
+      </c>
+      <c r="BG167" t="s">
+        <v>281</v>
+      </c>
+      <c r="BH167" t="s">
+        <v>282</v>
+      </c>
+      <c r="BI167" t="s">
+        <v>553</v>
+      </c>
+      <c r="BJ167" t="s">
+        <v>283</v>
+      </c>
+      <c r="BK167" t="s">
+        <v>258</v>
+      </c>
+      <c r="BM167" t="s">
+        <v>331</v>
+      </c>
+      <c r="BO167" t="s">
+        <v>307</v>
+      </c>
+      <c r="BP167" t="s">
+        <v>331</v>
+      </c>
+      <c r="BR167" t="s">
+        <v>236</v>
+      </c>
+      <c r="BS167" t="s">
+        <v>226</v>
+      </c>
+      <c r="BT167">
+        <v>30</v>
+      </c>
+      <c r="BU167" t="s">
+        <v>308</v>
+      </c>
+      <c r="BV167" t="s">
+        <v>238</v>
+      </c>
+      <c r="BX167">
+        <v>29</v>
+      </c>
+      <c r="BY167" t="s">
+        <v>406</v>
+      </c>
+      <c r="CA167">
+        <v>90</v>
+      </c>
+      <c r="CB167">
+        <v>3</v>
+      </c>
+      <c r="CC167" t="s">
+        <v>1996</v>
+      </c>
+      <c r="CD167">
+        <v>0</v>
+      </c>
+      <c r="CE167">
+        <v>0</v>
+      </c>
+      <c r="CF167">
+        <v>1</v>
+      </c>
+      <c r="CG167">
+        <v>1</v>
+      </c>
+      <c r="CH167">
+        <v>1</v>
+      </c>
+      <c r="CI167">
+        <v>1</v>
+      </c>
+      <c r="CJ167">
+        <v>1</v>
+      </c>
+      <c r="CK167">
+        <v>9999</v>
+      </c>
+      <c r="CL167">
+        <v>10</v>
+      </c>
+      <c r="CM167">
+        <v>9999</v>
+      </c>
+      <c r="CN167" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO167" t="s">
+        <v>242</v>
+      </c>
+      <c r="CP167">
+        <v>0</v>
+      </c>
+      <c r="CQ167">
+        <v>0</v>
+      </c>
+      <c r="CR167">
+        <v>0</v>
+      </c>
+      <c r="CS167">
+        <v>0</v>
+      </c>
+      <c r="CT167">
+        <v>0</v>
+      </c>
+      <c r="CU167">
+        <v>0</v>
+      </c>
+      <c r="CV167">
+        <v>1</v>
+      </c>
+      <c r="CW167">
+        <v>120</v>
+      </c>
+      <c r="CX167" t="s">
+        <v>226</v>
+      </c>
+      <c r="CY167" t="s">
+        <v>590</v>
+      </c>
+      <c r="CZ167">
+        <v>1</v>
+      </c>
+      <c r="DA167">
+        <v>1</v>
+      </c>
+      <c r="DB167">
+        <v>1</v>
+      </c>
+      <c r="DC167">
+        <v>0</v>
+      </c>
+      <c r="DD167" t="s">
+        <v>390</v>
+      </c>
+      <c r="DE167">
+        <v>1</v>
+      </c>
+      <c r="DF167">
+        <v>1</v>
+      </c>
+      <c r="DG167">
+        <v>0</v>
+      </c>
+      <c r="DH167">
+        <v>0</v>
+      </c>
+      <c r="DI167">
+        <v>0</v>
+      </c>
+      <c r="DJ167">
+        <v>0</v>
+      </c>
+      <c r="DK167" t="s">
+        <v>391</v>
+      </c>
+      <c r="DL167" t="s">
+        <v>361</v>
+      </c>
+      <c r="DM167">
+        <v>40</v>
+      </c>
+      <c r="DN167" t="s">
+        <v>392</v>
+      </c>
+      <c r="DO167" t="s">
+        <v>291</v>
+      </c>
+      <c r="DP167">
+        <v>0</v>
+      </c>
+      <c r="DQ167">
+        <v>0</v>
+      </c>
+      <c r="DR167">
+        <v>0</v>
+      </c>
+      <c r="DS167">
+        <v>0</v>
+      </c>
+      <c r="DT167">
+        <v>0</v>
+      </c>
+      <c r="DU167">
+        <v>0</v>
+      </c>
+      <c r="DV167">
+        <v>0</v>
+      </c>
+      <c r="DW167">
+        <v>1</v>
+      </c>
+      <c r="DX167">
+        <v>1</v>
+      </c>
+      <c r="DY167">
+        <v>1</v>
+      </c>
+      <c r="DZ167">
+        <v>0</v>
+      </c>
+      <c r="EA167">
+        <v>0</v>
+      </c>
+      <c r="EB167" t="s">
+        <v>292</v>
+      </c>
+      <c r="EC167" t="s">
+        <v>293</v>
+      </c>
+      <c r="ED167" t="s">
+        <v>253</v>
+      </c>
+      <c r="EE167" t="s">
+        <v>838</v>
+      </c>
+      <c r="EF167">
+        <v>1</v>
+      </c>
+      <c r="EG167">
+        <v>0</v>
+      </c>
+      <c r="EH167">
+        <v>0</v>
+      </c>
+      <c r="EI167">
+        <v>1</v>
+      </c>
+      <c r="EJ167">
+        <v>0</v>
+      </c>
+      <c r="EK167">
+        <v>0</v>
+      </c>
+      <c r="EL167" t="s">
+        <v>1147</v>
+      </c>
+      <c r="EM167">
+        <v>1</v>
+      </c>
+      <c r="EN167">
+        <v>1</v>
+      </c>
+      <c r="EO167">
+        <v>1</v>
+      </c>
+      <c r="EP167">
+        <v>0</v>
+      </c>
+      <c r="EQ167" t="s">
+        <v>253</v>
+      </c>
+      <c r="ER167" t="s">
+        <v>395</v>
+      </c>
+      <c r="ES167" t="s">
+        <v>1997</v>
+      </c>
+      <c r="ET167">
+        <v>1</v>
+      </c>
+      <c r="EU167">
+        <v>1</v>
+      </c>
+      <c r="EV167">
+        <v>0</v>
+      </c>
+      <c r="EW167">
+        <v>0</v>
+      </c>
+      <c r="EX167">
+        <v>0</v>
+      </c>
+      <c r="EY167" t="s">
+        <v>256</v>
+      </c>
+      <c r="EZ167" t="s">
+        <v>257</v>
+      </c>
+      <c r="FA167" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB167" t="s">
+        <v>365</v>
+      </c>
+      <c r="FC167" t="s">
+        <v>436</v>
+      </c>
+      <c r="FD167">
+        <v>1</v>
+      </c>
+      <c r="FE167">
+        <v>1</v>
+      </c>
+      <c r="FF167">
+        <v>1</v>
+      </c>
+      <c r="FG167">
+        <v>0</v>
+      </c>
+      <c r="FH167">
+        <v>0</v>
+      </c>
+      <c r="FI167">
+        <v>0</v>
+      </c>
+      <c r="FJ167" t="s">
+        <v>226</v>
+      </c>
+      <c r="FK167" t="s">
+        <v>226</v>
+      </c>
+      <c r="FM167" t="s">
+        <v>625</v>
+      </c>
+      <c r="FN167">
+        <v>1</v>
+      </c>
+      <c r="FO167">
+        <v>1</v>
+      </c>
+      <c r="FP167">
+        <v>1</v>
+      </c>
+      <c r="FQ167">
+        <v>0</v>
+      </c>
+      <c r="FR167">
+        <v>1</v>
+      </c>
+      <c r="FS167">
+        <v>1</v>
+      </c>
+      <c r="FT167" t="s">
+        <v>226</v>
+      </c>
+      <c r="FU167">
+        <v>1</v>
+      </c>
+      <c r="FV167" t="s">
+        <v>1902</v>
+      </c>
+      <c r="FW167">
+        <v>1</v>
+      </c>
+      <c r="FX167">
+        <v>1</v>
+      </c>
+      <c r="FY167">
+        <v>1</v>
+      </c>
+      <c r="FZ167">
+        <v>0</v>
+      </c>
+      <c r="GB167">
+        <v>4</v>
+      </c>
+      <c r="GC167" t="s">
+        <v>262</v>
+      </c>
+      <c r="GD167">
+        <v>1</v>
+      </c>
+      <c r="GE167">
+        <v>0</v>
+      </c>
+      <c r="GF167">
+        <v>0</v>
+      </c>
+      <c r="GG167">
+        <v>0</v>
+      </c>
+      <c r="GH167" t="s">
+        <v>455</v>
+      </c>
+      <c r="GI167" t="s">
+        <v>666</v>
+      </c>
+      <c r="GJ167" t="s">
+        <v>226</v>
+      </c>
+      <c r="GK167" t="s">
+        <v>226</v>
+      </c>
+      <c r="GL167" t="s">
+        <v>226</v>
+      </c>
+      <c r="GM167" t="s">
+        <v>226</v>
+      </c>
+      <c r="GN167" t="s">
+        <v>226</v>
+      </c>
+      <c r="GO167" t="s">
+        <v>226</v>
+      </c>
+      <c r="GP167" t="s">
+        <v>263</v>
+      </c>
+      <c r="GQ167" t="s">
+        <v>226</v>
+      </c>
+      <c r="GR167" t="s">
+        <v>263</v>
+      </c>
+      <c r="GZ167" t="s">
+        <v>1998</v>
+      </c>
+      <c r="HC167" t="s">
+        <v>1999</v>
+      </c>
+      <c r="HD167">
+        <v>22582006</v>
+      </c>
+      <c r="HE167" t="s">
+        <v>2000</v>
+      </c>
+      <c r="HF167" s="1">
+        <v>46225.746736111112</v>
+      </c>
+      <c r="HI167" t="s">
+        <v>266</v>
+      </c>
+      <c r="HJ167" t="s">
+        <v>267</v>
+      </c>
+      <c r="HK167" t="s">
+        <v>1308</v>
+      </c>
+      <c r="HM167" t="s">
+        <v>2001</v>
+      </c>
+      <c r="HN167">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
